--- a/ORCL.xlsx
+++ b/ORCL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F296CF0-57A8-4665-8711-2030B70B2263}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0969C933-4841-4D34-AA76-13A1BBFD0DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{AD2507E4-7809-4EA5-A8F6-6E64402326AB}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{AD2507E4-7809-4EA5-A8F6-6E64402326AB}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="76">
   <si>
     <t>Oracle</t>
   </si>
@@ -162,12 +162,6 @@
     <t>EPS</t>
   </si>
   <si>
-    <t>Cloud Services Growth</t>
-  </si>
-  <si>
-    <t>Licenses Growth</t>
-  </si>
-  <si>
     <t>Hardware Growth</t>
   </si>
   <si>
@@ -243,10 +237,34 @@
     <t>OpenAi is to buy 300$ billion in computing power over 5 years</t>
   </si>
   <si>
-    <t>FQ426</t>
+    <t>FY26</t>
   </si>
   <si>
-    <t>FY26</t>
+    <t>FQ127</t>
+  </si>
+  <si>
+    <t>Q127</t>
+  </si>
+  <si>
+    <t>Q227</t>
+  </si>
+  <si>
+    <t>Q327</t>
+  </si>
+  <si>
+    <t>Q427</t>
+  </si>
+  <si>
+    <t>Cloud</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Cloud Growth</t>
+  </si>
+  <si>
+    <t>Service Growth</t>
   </si>
 </sst>
 </file>
@@ -257,13 +275,19 @@
     <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -476,46 +500,50 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -875,7 +903,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="2">
-        <v>183.94</v>
+        <v>143.88</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -886,10 +914,10 @@
         <v>5</v>
       </c>
       <c r="H4" s="4">
-        <v>2878</v>
-      </c>
-      <c r="I4" s="27" t="s">
-        <v>68</v>
+        <v>3023.7359999999999</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -901,7 +929,7 @@
       </c>
       <c r="H5" s="4">
         <f>+H3*H4</f>
-        <v>529379.31999999995</v>
+        <v>435055.13567999995</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -909,16 +937,16 @@
         <v>7</v>
       </c>
       <c r="H6" s="4">
-        <f>31289+605</f>
-        <v>31894</v>
-      </c>
-      <c r="I6" s="27" t="s">
-        <v>68</v>
+        <f>36369+708</f>
+        <v>37077</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B7" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -927,10 +955,11 @@
         <v>8</v>
       </c>
       <c r="H7" s="4">
-        <v>122342</v>
-      </c>
-      <c r="I7" s="27" t="s">
-        <v>68</v>
+        <f>7625+117712</f>
+        <v>125337</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -945,7 +974,7 @@
       </c>
       <c r="H8" s="4">
         <f>+H5-H6+H7</f>
-        <v>619827.31999999995</v>
+        <v>523315.13567999995</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -970,34 +999,34 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="G12" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B13" s="17" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I13" s="22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B14" s="26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I14" s="22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B15" s="26" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{386309C5-8495-4DC2-9B35-753E45A4595B}">
-  <dimension ref="A1:AS518"/>
+  <dimension ref="A1:AW518"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1018,12 +1047,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.2">
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
@@ -1049,42 +1078,54 @@
         <v>18</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="L2" s="25" t="s">
+      <c r="N2" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="M2" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="N2" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="P2" s="21" t="s">
+      <c r="O2" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="R2" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="T2" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="Q2" s="21" t="s">
+      <c r="W2" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="R2" s="21" t="s">
+      <c r="X2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="S2" s="21" t="s">
+      <c r="Y2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="T2" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="U2" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="V2" s="27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
-        <v>19</v>
+      <c r="Z2" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="B3" s="29" t="s">
+        <v>72</v>
       </c>
       <c r="C3" s="4">
         <v>9547</v>
@@ -1118,26 +1159,28 @@
       <c r="N3" s="4">
         <v>9913</v>
       </c>
-      <c r="O3" s="4"/>
+      <c r="O3" s="4">
+        <v>11607</v>
+      </c>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
-      <c r="S3" s="4">
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4">
         <v>35307</v>
       </c>
-      <c r="T3" s="4">
+      <c r="X3" s="4">
         <v>39383</v>
       </c>
-      <c r="U3" s="4">
+      <c r="Y3" s="4">
         <v>44029</v>
       </c>
-      <c r="V3" s="4">
+      <c r="Z3" s="4">
         <v>33989</v>
       </c>
-      <c r="W3" s="4"/>
-      <c r="X3" s="4"/>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="4"/>
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
@@ -1157,10 +1200,14 @@
       <c r="AQ3" s="4"/>
       <c r="AR3" s="4"/>
       <c r="AS3" s="4"/>
-    </row>
-    <row r="4" spans="1:45" x14ac:dyDescent="0.2">
-      <c r="B4" s="2" t="s">
-        <v>20</v>
+      <c r="AT3" s="4"/>
+      <c r="AU3" s="4"/>
+      <c r="AV3" s="4"/>
+      <c r="AW3" s="4"/>
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
+      <c r="B4" s="29" t="s">
+        <v>73</v>
       </c>
       <c r="C4" s="4">
         <v>809</v>
@@ -1194,26 +1241,28 @@
       <c r="N4" s="4">
         <v>6824</v>
       </c>
-      <c r="O4" s="4"/>
+      <c r="O4" s="4">
+        <v>5550</v>
+      </c>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
       <c r="R4" s="4"/>
-      <c r="S4" s="4">
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4">
         <v>5779</v>
       </c>
-      <c r="T4" s="4">
+      <c r="X4" s="4">
         <v>5081</v>
       </c>
-      <c r="U4" s="4">
+      <c r="Y4" s="4">
         <v>5201</v>
       </c>
-      <c r="V4" s="4">
+      <c r="Z4" s="4">
         <v>24541</v>
       </c>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
       <c r="AA4" s="4"/>
       <c r="AB4" s="4"/>
       <c r="AC4" s="4"/>
@@ -1233,8 +1282,12 @@
       <c r="AQ4" s="4"/>
       <c r="AR4" s="4"/>
       <c r="AS4" s="4"/>
-    </row>
-    <row r="5" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT4" s="4"/>
+      <c r="AU4" s="4"/>
+      <c r="AV4" s="4"/>
+      <c r="AW4" s="4"/>
+    </row>
+    <row r="5" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
@@ -1270,26 +1323,28 @@
       <c r="N5" s="4">
         <v>924</v>
       </c>
-      <c r="O5" s="4"/>
+      <c r="O5" s="4">
+        <v>774</v>
+      </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
       <c r="R5" s="4"/>
-      <c r="S5" s="4">
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4">
         <v>3274</v>
       </c>
-      <c r="T5" s="4">
+      <c r="X5" s="4">
         <v>3066</v>
       </c>
-      <c r="U5" s="4">
+      <c r="Y5" s="4">
         <v>2936</v>
       </c>
-      <c r="V5" s="4">
+      <c r="Z5" s="4">
         <v>3084</v>
       </c>
-      <c r="W5" s="4"/>
-      <c r="X5" s="4"/>
-      <c r="Y5" s="4"/>
-      <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
       <c r="AC5" s="4"/>
@@ -1309,8 +1364,12 @@
       <c r="AQ5" s="4"/>
       <c r="AR5" s="4"/>
       <c r="AS5" s="4"/>
-    </row>
-    <row r="6" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT5" s="4"/>
+      <c r="AU5" s="4"/>
+      <c r="AV5" s="4"/>
+      <c r="AW5" s="4"/>
+    </row>
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
@@ -1346,26 +1405,28 @@
       <c r="N6" s="4">
         <v>1523</v>
       </c>
-      <c r="O6" s="4"/>
+      <c r="O6" s="4">
+        <v>1414</v>
+      </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
-      <c r="S6" s="4">
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4">
         <v>5594</v>
       </c>
-      <c r="T6" s="4">
+      <c r="X6" s="4">
         <v>5431</v>
       </c>
-      <c r="U6" s="4">
+      <c r="Y6" s="4">
         <v>5233</v>
       </c>
-      <c r="V6" s="4">
+      <c r="Z6" s="4">
         <v>5743</v>
       </c>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
       <c r="AA6" s="4"/>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
@@ -1385,8 +1446,12 @@
       <c r="AQ6" s="4"/>
       <c r="AR6" s="4"/>
       <c r="AS6" s="4"/>
-    </row>
-    <row r="7" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT6" s="4"/>
+      <c r="AU6" s="4"/>
+      <c r="AV6" s="4"/>
+      <c r="AW6" s="4"/>
+    </row>
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
@@ -1434,26 +1499,28 @@
       <c r="N7" s="18">
         <v>19184</v>
       </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="18">
+      <c r="O7" s="18">
+        <v>19345</v>
+      </c>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="18">
         <v>49954</v>
       </c>
-      <c r="T7" s="18">
+      <c r="X7" s="18">
         <v>52961</v>
       </c>
-      <c r="U7" s="18">
+      <c r="Y7" s="18">
         <v>57399</v>
       </c>
-      <c r="V7" s="18">
+      <c r="Z7" s="18">
         <v>67357</v>
       </c>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
@@ -1473,8 +1540,12 @@
       <c r="AQ7" s="4"/>
       <c r="AR7" s="4"/>
       <c r="AS7" s="4"/>
-    </row>
-    <row r="8" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT7" s="4"/>
+      <c r="AU7" s="4"/>
+      <c r="AV7" s="4"/>
+      <c r="AW7" s="4"/>
+    </row>
+    <row r="8" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
@@ -1510,26 +1581,28 @@
       <c r="N8" s="4">
         <v>5224</v>
       </c>
-      <c r="O8" s="4"/>
+      <c r="O8" s="4">
+        <v>6400</v>
+      </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
-      <c r="S8" s="4">
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4">
         <v>7763</v>
       </c>
-      <c r="T8" s="4">
+      <c r="X8" s="4">
         <v>9427</v>
       </c>
-      <c r="U8" s="4">
+      <c r="Y8" s="4">
         <v>11569</v>
       </c>
-      <c r="V8" s="4">
+      <c r="Z8" s="4">
         <v>17597</v>
       </c>
-      <c r="W8" s="4"/>
-      <c r="X8" s="4"/>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
@@ -1549,8 +1622,12 @@
       <c r="AQ8" s="4"/>
       <c r="AR8" s="4"/>
       <c r="AS8" s="4"/>
-    </row>
-    <row r="9" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT8" s="4"/>
+      <c r="AU8" s="4"/>
+      <c r="AV8" s="4"/>
+      <c r="AW8" s="4"/>
+    </row>
+    <row r="9" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
@@ -1586,26 +1663,28 @@
       <c r="N9" s="4">
         <v>293</v>
       </c>
-      <c r="O9" s="4"/>
+      <c r="O9" s="4">
+        <v>281</v>
+      </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
-      <c r="S9" s="4">
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4">
         <v>1040</v>
       </c>
-      <c r="T9" s="4">
+      <c r="X9" s="4">
         <v>891</v>
       </c>
-      <c r="U9" s="4">
+      <c r="Y9" s="4">
         <v>782</v>
       </c>
-      <c r="V9" s="4">
+      <c r="Z9" s="4">
         <v>868</v>
       </c>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4"/>
-      <c r="Z9" s="4"/>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
       <c r="AC9" s="4"/>
@@ -1625,8 +1704,12 @@
       <c r="AQ9" s="4"/>
       <c r="AR9" s="4"/>
       <c r="AS9" s="4"/>
-    </row>
-    <row r="10" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT9" s="4"/>
+      <c r="AU9" s="4"/>
+      <c r="AV9" s="4"/>
+      <c r="AW9" s="4"/>
+    </row>
+    <row r="10" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
@@ -1662,26 +1745,28 @@
       <c r="N10" s="4">
         <v>1155</v>
       </c>
-      <c r="O10" s="4"/>
+      <c r="O10" s="4">
+        <v>1052</v>
+      </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
-      <c r="S10" s="4">
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4">
         <v>4761</v>
       </c>
-      <c r="T10" s="4">
+      <c r="X10" s="4">
         <v>4825</v>
       </c>
-      <c r="U10" s="4">
+      <c r="Y10" s="4">
         <v>4576</v>
       </c>
-      <c r="V10" s="4">
+      <c r="Z10" s="4">
         <v>4556</v>
       </c>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
       <c r="AA10" s="4"/>
       <c r="AB10" s="4"/>
       <c r="AC10" s="4"/>
@@ -1701,8 +1786,12 @@
       <c r="AQ10" s="4"/>
       <c r="AR10" s="4"/>
       <c r="AS10" s="4"/>
-    </row>
-    <row r="11" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT10" s="4"/>
+      <c r="AU10" s="4"/>
+      <c r="AV10" s="4"/>
+      <c r="AW10" s="4"/>
+    </row>
+    <row r="11" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
@@ -1727,7 +1816,7 @@
         <v>9401</v>
       </c>
       <c r="H11" s="4">
-        <f t="shared" ref="H11:N11" si="3">+H7-SUM(H8:H10)</f>
+        <f t="shared" ref="H11:O11" si="3">+H7-SUM(H8:H10)</f>
         <v>9974</v>
       </c>
       <c r="I11" s="4">
@@ -1754,39 +1843,42 @@
         <f t="shared" si="3"/>
         <v>12512</v>
       </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4">
-        <f t="shared" ref="P11:T11" si="4">+P7-SUM(P8:P10)</f>
+      <c r="O11" s="4">
+        <f t="shared" si="3"/>
+        <v>11612</v>
+      </c>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4">
+        <f t="shared" ref="T11:X11" si="4">+T7-SUM(T8:T10)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="U11" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="R11" s="4">
+      <c r="V11" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="S11" s="4">
+      <c r="W11" s="4">
         <f t="shared" si="4"/>
         <v>36390</v>
       </c>
-      <c r="T11" s="4">
+      <c r="X11" s="4">
         <f t="shared" si="4"/>
         <v>37818</v>
       </c>
-      <c r="U11" s="4">
-        <f>+U7-SUM(U8:U10)</f>
+      <c r="Y11" s="4">
+        <f>+Y7-SUM(Y8:Y10)</f>
         <v>40472</v>
       </c>
-      <c r="V11" s="4">
-        <f>+V7-SUM(V8:V10)</f>
+      <c r="Z11" s="4">
+        <f>+Z7-SUM(Z8:Z10)</f>
         <v>44336</v>
       </c>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4"/>
-      <c r="Z11" s="4"/>
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
@@ -1806,8 +1898,12 @@
       <c r="AQ11" s="4"/>
       <c r="AR11" s="4"/>
       <c r="AS11" s="4"/>
-    </row>
-    <row r="12" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT11" s="4"/>
+      <c r="AU11" s="4"/>
+      <c r="AV11" s="4"/>
+      <c r="AW11" s="4"/>
+    </row>
+    <row r="12" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1843,26 +1939,28 @@
       <c r="N12" s="4">
         <v>2068</v>
       </c>
-      <c r="O12" s="4"/>
+      <c r="O12" s="4">
+        <v>1811</v>
+      </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
-      <c r="S12" s="4">
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4">
         <v>8833</v>
       </c>
-      <c r="T12" s="4">
+      <c r="X12" s="4">
         <v>8274</v>
       </c>
-      <c r="U12" s="23">
+      <c r="Y12" s="23">
         <v>8651</v>
       </c>
-      <c r="V12" s="4">
+      <c r="Z12" s="4">
         <v>8331</v>
       </c>
-      <c r="W12" s="4"/>
-      <c r="X12" s="4"/>
-      <c r="Y12" s="4"/>
-      <c r="Z12" s="4"/>
       <c r="AA12" s="4"/>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
@@ -1882,8 +1980,12 @@
       <c r="AQ12" s="4"/>
       <c r="AR12" s="4"/>
       <c r="AS12" s="4"/>
-    </row>
-    <row r="13" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT12" s="4"/>
+      <c r="AU12" s="4"/>
+      <c r="AV12" s="4"/>
+      <c r="AW12" s="4"/>
+    </row>
+    <row r="13" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1919,26 +2021,28 @@
       <c r="N13" s="4">
         <v>2613</v>
       </c>
-      <c r="O13" s="4"/>
+      <c r="O13" s="4">
+        <v>2401</v>
+      </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
-      <c r="S13" s="4">
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4">
         <v>8623</v>
       </c>
-      <c r="T13" s="4">
+      <c r="X13" s="4">
         <v>8915</v>
       </c>
-      <c r="U13" s="4">
+      <c r="Y13" s="4">
         <v>9860</v>
       </c>
-      <c r="V13" s="4">
+      <c r="Z13" s="4">
         <v>10272</v>
       </c>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="4"/>
-      <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
@@ -1958,8 +2062,12 @@
       <c r="AQ13" s="4"/>
       <c r="AR13" s="4"/>
       <c r="AS13" s="4"/>
-    </row>
-    <row r="14" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT13" s="4"/>
+      <c r="AU13" s="4"/>
+      <c r="AV13" s="4"/>
+      <c r="AW13" s="4"/>
+    </row>
+    <row r="14" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>30</v>
       </c>
@@ -1995,26 +2103,28 @@
       <c r="N14" s="4">
         <v>444</v>
       </c>
-      <c r="O14" s="4"/>
+      <c r="O14" s="4">
+        <v>376</v>
+      </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
-      <c r="S14" s="4">
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4">
         <v>1579</v>
       </c>
-      <c r="T14" s="4">
+      <c r="X14" s="4">
         <v>1548</v>
       </c>
-      <c r="U14" s="4">
+      <c r="Y14" s="4">
         <v>1602</v>
       </c>
-      <c r="V14" s="4">
+      <c r="Z14" s="4">
         <v>1618</v>
       </c>
-      <c r="W14" s="4"/>
-      <c r="X14" s="4"/>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="4"/>
       <c r="AA14" s="4"/>
       <c r="AB14" s="4"/>
       <c r="AC14" s="4"/>
@@ -2034,8 +2144,12 @@
       <c r="AQ14" s="4"/>
       <c r="AR14" s="4"/>
       <c r="AS14" s="4"/>
-    </row>
-    <row r="15" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT14" s="4"/>
+      <c r="AU14" s="4"/>
+      <c r="AV14" s="4"/>
+      <c r="AW14" s="4"/>
+    </row>
+    <row r="15" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>31</v>
       </c>
@@ -2071,26 +2185,28 @@
       <c r="N15" s="4">
         <v>431</v>
       </c>
-      <c r="O15" s="4"/>
+      <c r="O15" s="4">
+        <v>202</v>
+      </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
-      <c r="S15" s="4">
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4">
         <v>3582</v>
       </c>
-      <c r="T15" s="4">
+      <c r="X15" s="4">
         <v>3010</v>
       </c>
-      <c r="U15" s="4">
+      <c r="Y15" s="4">
         <v>2307</v>
       </c>
-      <c r="V15" s="4">
+      <c r="Z15" s="4">
         <v>1671</v>
       </c>
-      <c r="W15" s="4"/>
-      <c r="X15" s="4"/>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="4"/>
       <c r="AA15" s="4"/>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
@@ -2110,8 +2226,12 @@
       <c r="AQ15" s="4"/>
       <c r="AR15" s="4"/>
       <c r="AS15" s="4"/>
-    </row>
-    <row r="16" spans="1:45" x14ac:dyDescent="0.2">
+      <c r="AT15" s="4"/>
+      <c r="AU15" s="4"/>
+      <c r="AV15" s="4"/>
+      <c r="AW15" s="4"/>
+    </row>
+    <row r="16" spans="1:49" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>32</v>
       </c>
@@ -2147,26 +2267,28 @@
       <c r="N16" s="4">
         <v>0</v>
       </c>
-      <c r="O16" s="4"/>
+      <c r="O16" s="4">
+        <v>0</v>
+      </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
-      <c r="S16" s="4">
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4">
         <v>190</v>
       </c>
-      <c r="T16" s="4">
+      <c r="X16" s="4">
         <v>314</v>
       </c>
-      <c r="U16" s="4">
+      <c r="Y16" s="4">
         <v>75</v>
       </c>
-      <c r="V16" s="4">
+      <c r="Z16" s="4">
         <v>0</v>
       </c>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
       <c r="AA16" s="4"/>
       <c r="AB16" s="4"/>
       <c r="AC16" s="4"/>
@@ -2186,8 +2308,12 @@
       <c r="AQ16" s="4"/>
       <c r="AR16" s="4"/>
       <c r="AS16" s="4"/>
-    </row>
-    <row r="17" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT16" s="4"/>
+      <c r="AU16" s="4"/>
+      <c r="AV16" s="4"/>
+      <c r="AW16" s="4"/>
+    </row>
+    <row r="17" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
@@ -2223,26 +2349,28 @@
       <c r="N17" s="4">
         <v>823</v>
       </c>
-      <c r="O17" s="4"/>
+      <c r="O17" s="4">
+        <v>94</v>
+      </c>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
-      <c r="S17" s="4">
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4">
         <v>490</v>
       </c>
-      <c r="T17" s="4">
+      <c r="X17" s="4">
         <v>404</v>
       </c>
-      <c r="U17" s="4">
+      <c r="Y17" s="4">
         <v>299</v>
       </c>
-      <c r="V17" s="4">
+      <c r="Z17" s="4">
         <v>1838</v>
       </c>
-      <c r="W17" s="4"/>
-      <c r="X17" s="4"/>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="4"/>
       <c r="AA17" s="4"/>
       <c r="AB17" s="4"/>
       <c r="AC17" s="4"/>
@@ -2262,8 +2390,12 @@
       <c r="AQ17" s="4"/>
       <c r="AR17" s="4"/>
       <c r="AS17" s="4"/>
-    </row>
-    <row r="18" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT17" s="4"/>
+      <c r="AU17" s="4"/>
+      <c r="AV17" s="4"/>
+      <c r="AW17" s="4"/>
+    </row>
+    <row r="18" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
@@ -2288,7 +2420,7 @@
         <v>3991</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" ref="H18:V18" si="6">+H11-SUM(H12:H17)</f>
+        <f t="shared" ref="H18:Z18" si="6">+H11-SUM(H12:H17)</f>
         <v>4220</v>
       </c>
       <c r="I18" s="4">
@@ -2315,39 +2447,42 @@
         <f t="shared" si="6"/>
         <v>6133</v>
       </c>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4">
+      <c r="O18" s="4">
+        <f t="shared" si="6"/>
+        <v>6728</v>
+      </c>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="U18" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R18" s="4">
+      <c r="V18" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S18" s="4">
+      <c r="W18" s="4">
         <f t="shared" si="6"/>
         <v>13093</v>
       </c>
-      <c r="T18" s="4">
+      <c r="X18" s="4">
         <f t="shared" si="6"/>
         <v>15353</v>
       </c>
-      <c r="U18" s="4">
+      <c r="Y18" s="4">
         <f t="shared" si="6"/>
         <v>17678</v>
       </c>
-      <c r="V18" s="4">
+      <c r="Z18" s="4">
         <f t="shared" si="6"/>
         <v>20606</v>
       </c>
-      <c r="W18" s="4"/>
-      <c r="X18" s="4"/>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="4"/>
       <c r="AA18" s="4"/>
       <c r="AB18" s="4"/>
       <c r="AC18" s="4"/>
@@ -2367,8 +2502,12 @@
       <c r="AQ18" s="4"/>
       <c r="AR18" s="4"/>
       <c r="AS18" s="4"/>
-    </row>
-    <row r="19" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT18" s="4"/>
+      <c r="AU18" s="4"/>
+      <c r="AV18" s="4"/>
+      <c r="AW18" s="4"/>
+    </row>
+    <row r="19" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>35</v>
       </c>
@@ -2404,26 +2543,28 @@
       <c r="N19" s="4">
         <v>1438</v>
       </c>
-      <c r="O19" s="4"/>
+      <c r="O19" s="4">
+        <v>1428</v>
+      </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
-      <c r="S19" s="4">
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4">
         <v>3505</v>
       </c>
-      <c r="T19" s="4">
+      <c r="X19" s="4">
         <v>3514</v>
       </c>
-      <c r="U19" s="4">
+      <c r="Y19" s="4">
         <v>3578</v>
       </c>
-      <c r="V19" s="4">
+      <c r="Z19" s="4">
         <v>4599</v>
       </c>
-      <c r="W19" s="4"/>
-      <c r="X19" s="4"/>
-      <c r="Y19" s="4"/>
-      <c r="Z19" s="4"/>
       <c r="AA19" s="4"/>
       <c r="AB19" s="4"/>
       <c r="AC19" s="4"/>
@@ -2443,8 +2584,12 @@
       <c r="AQ19" s="4"/>
       <c r="AR19" s="4"/>
       <c r="AS19" s="4"/>
-    </row>
-    <row r="20" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT19" s="4"/>
+      <c r="AU19" s="4"/>
+      <c r="AV19" s="4"/>
+      <c r="AW19" s="4"/>
+    </row>
+    <row r="20" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>36</v>
       </c>
@@ -2480,26 +2625,28 @@
       <c r="N20" s="4">
         <v>675</v>
       </c>
-      <c r="O20" s="4"/>
+      <c r="O20" s="4">
+        <v>307</v>
+      </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
-      <c r="S20" s="4">
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4">
         <v>-462</v>
       </c>
-      <c r="T20" s="4">
+      <c r="X20" s="4">
         <v>-98</v>
       </c>
-      <c r="U20" s="4">
+      <c r="Y20" s="4">
         <v>60</v>
       </c>
-      <c r="V20" s="4">
+      <c r="Z20" s="4">
         <v>3547</v>
       </c>
-      <c r="W20" s="4"/>
-      <c r="X20" s="4"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
       <c r="AA20" s="4"/>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -2519,8 +2666,12 @@
       <c r="AQ20" s="4"/>
       <c r="AR20" s="4"/>
       <c r="AS20" s="4"/>
-    </row>
-    <row r="21" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT20" s="4"/>
+      <c r="AU20" s="4"/>
+      <c r="AV20" s="4"/>
+      <c r="AW20" s="4"/>
+    </row>
+    <row r="21" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>37</v>
       </c>
@@ -2545,7 +2696,7 @@
         <v>3169</v>
       </c>
       <c r="H21" s="4">
-        <f t="shared" ref="H21:V21" si="8">+H18-H19+H20</f>
+        <f t="shared" ref="H21:Z21" si="8">+H18-H19+H20</f>
         <v>3390</v>
       </c>
       <c r="I21" s="4">
@@ -2572,39 +2723,42 @@
         <f t="shared" si="8"/>
         <v>5370</v>
       </c>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4">
+      <c r="O21" s="4">
+        <f t="shared" si="8"/>
+        <v>5607</v>
+      </c>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="U21" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="R21" s="4">
+      <c r="V21" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="S21" s="4">
+      <c r="W21" s="4">
         <f t="shared" si="8"/>
         <v>9126</v>
       </c>
-      <c r="T21" s="4">
+      <c r="X21" s="4">
         <f t="shared" si="8"/>
         <v>11741</v>
       </c>
-      <c r="U21" s="4">
+      <c r="Y21" s="4">
         <f t="shared" si="8"/>
         <v>14160</v>
       </c>
-      <c r="V21" s="4">
+      <c r="Z21" s="4">
         <f t="shared" si="8"/>
         <v>19554</v>
       </c>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="4"/>
       <c r="AA21" s="4"/>
       <c r="AB21" s="4"/>
       <c r="AC21" s="4"/>
@@ -2624,8 +2778,12 @@
       <c r="AQ21" s="4"/>
       <c r="AR21" s="4"/>
       <c r="AS21" s="4"/>
-    </row>
-    <row r="22" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT21" s="4"/>
+      <c r="AU21" s="4"/>
+      <c r="AV21" s="4"/>
+      <c r="AW21" s="4"/>
+    </row>
+    <row r="22" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>38</v>
       </c>
@@ -2663,27 +2821,30 @@
         <f>1066+81</f>
         <v>1147</v>
       </c>
-      <c r="O22" s="4"/>
+      <c r="O22" s="4">
+        <f>847+81</f>
+        <v>928</v>
+      </c>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
-      <c r="S22" s="4">
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4">
         <v>623</v>
       </c>
-      <c r="T22" s="4">
+      <c r="X22" s="4">
         <v>1274</v>
       </c>
-      <c r="U22" s="4">
+      <c r="Y22" s="4">
         <v>1717</v>
       </c>
-      <c r="V22" s="4">
+      <c r="Z22" s="4">
         <f>2467+103</f>
         <v>2570</v>
       </c>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
-      <c r="Z22" s="4"/>
       <c r="AA22" s="4"/>
       <c r="AB22" s="4"/>
       <c r="AC22" s="4"/>
@@ -2703,8 +2864,12 @@
       <c r="AQ22" s="4"/>
       <c r="AR22" s="4"/>
       <c r="AS22" s="4"/>
-    </row>
-    <row r="23" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT22" s="4"/>
+      <c r="AU22" s="4"/>
+      <c r="AV22" s="4"/>
+      <c r="AW22" s="4"/>
+    </row>
+    <row r="23" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>39</v>
       </c>
@@ -2729,7 +2894,7 @@
         <v>2929</v>
       </c>
       <c r="H23" s="4">
-        <f t="shared" ref="H23:V23" si="10">+H21-H22</f>
+        <f t="shared" ref="H23:Z23" si="10">+H21-H22</f>
         <v>3151</v>
       </c>
       <c r="I23" s="4">
@@ -2756,39 +2921,42 @@
         <f t="shared" si="10"/>
         <v>4223</v>
       </c>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4">
+      <c r="O23" s="4">
+        <f t="shared" si="10"/>
+        <v>4679</v>
+      </c>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="U23" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="R23" s="4">
+      <c r="V23" s="4">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="S23" s="4">
+      <c r="W23" s="4">
         <f t="shared" si="10"/>
         <v>8503</v>
       </c>
-      <c r="T23" s="4">
+      <c r="X23" s="4">
         <f t="shared" si="10"/>
         <v>10467</v>
       </c>
-      <c r="U23" s="4">
+      <c r="Y23" s="4">
         <f t="shared" si="10"/>
         <v>12443</v>
       </c>
-      <c r="V23" s="4">
+      <c r="Z23" s="4">
         <f t="shared" si="10"/>
         <v>16984</v>
       </c>
-      <c r="W23" s="4"/>
-      <c r="X23" s="4"/>
-      <c r="Y23" s="4"/>
-      <c r="Z23" s="4"/>
       <c r="AA23" s="4"/>
       <c r="AB23" s="4"/>
       <c r="AC23" s="4"/>
@@ -2808,8 +2976,12 @@
       <c r="AQ23" s="4"/>
       <c r="AR23" s="4"/>
       <c r="AS23" s="4"/>
-    </row>
-    <row r="24" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT23" s="4"/>
+      <c r="AU23" s="4"/>
+      <c r="AV23" s="4"/>
+      <c r="AW23" s="4"/>
+    </row>
+    <row r="24" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -2853,8 +3025,12 @@
       <c r="AQ24" s="4"/>
       <c r="AR24" s="4"/>
       <c r="AS24" s="4"/>
-    </row>
-    <row r="25" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT24" s="4"/>
+      <c r="AU24" s="4"/>
+      <c r="AV24" s="4"/>
+      <c r="AW24" s="4"/>
+    </row>
+    <row r="25" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>40</v>
       </c>
@@ -2879,7 +3055,7 @@
         <v>1.0736803519061584</v>
       </c>
       <c r="H25" s="19">
-        <f t="shared" ref="H25:V25" si="12">+H23/H26</f>
+        <f t="shared" ref="H25:Z25" si="12">+H23/H26</f>
         <v>1.1293906810035843</v>
       </c>
       <c r="I25" s="19">
@@ -2906,39 +3082,42 @@
         <f t="shared" si="12"/>
         <v>1.4673384294649061</v>
       </c>
-      <c r="O25" s="4"/>
-      <c r="P25" s="19" t="e">
+      <c r="O25" s="19">
+        <f t="shared" si="12"/>
+        <v>1.5775455158462577</v>
+      </c>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="19"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="19" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q25" s="19" t="e">
+      <c r="U25" s="19" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R25" s="19" t="e">
+      <c r="V25" s="19" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S25" s="19">
+      <c r="W25" s="19">
         <f t="shared" si="12"/>
         <v>3.1539317507418398</v>
       </c>
-      <c r="T25" s="19">
+      <c r="X25" s="19">
         <f t="shared" si="12"/>
         <v>3.8145043731778427</v>
       </c>
-      <c r="U25" s="19">
+      <c r="Y25" s="19">
         <f t="shared" si="12"/>
         <v>4.4614557188956612</v>
       </c>
-      <c r="V25" s="19">
+      <c r="Z25" s="19">
         <f t="shared" si="12"/>
         <v>5.9384615384615387</v>
       </c>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
-      <c r="Z25" s="4"/>
       <c r="AA25" s="4"/>
       <c r="AB25" s="4"/>
       <c r="AC25" s="4"/>
@@ -2958,8 +3137,12 @@
       <c r="AQ25" s="4"/>
       <c r="AR25" s="4"/>
       <c r="AS25" s="4"/>
-    </row>
-    <row r="26" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT25" s="4"/>
+      <c r="AU25" s="4"/>
+      <c r="AV25" s="4"/>
+      <c r="AW25" s="4"/>
+    </row>
+    <row r="26" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>5</v>
       </c>
@@ -2995,26 +3178,28 @@
       <c r="N26" s="4">
         <v>2878</v>
       </c>
-      <c r="O26" s="4"/>
+      <c r="O26" s="4">
+        <v>2966</v>
+      </c>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
-      <c r="S26" s="4">
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4">
         <v>2696</v>
       </c>
-      <c r="T26" s="4">
+      <c r="X26" s="4">
         <v>2744</v>
       </c>
-      <c r="U26" s="4">
+      <c r="Y26" s="4">
         <v>2789</v>
       </c>
-      <c r="V26" s="4">
+      <c r="Z26" s="4">
         <v>2860</v>
       </c>
-      <c r="W26" s="4"/>
-      <c r="X26" s="4"/>
-      <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
       <c r="AA26" s="4"/>
       <c r="AB26" s="4"/>
       <c r="AC26" s="4"/>
@@ -3034,8 +3219,12 @@
       <c r="AQ26" s="4"/>
       <c r="AR26" s="4"/>
       <c r="AS26" s="4"/>
-    </row>
-    <row r="27" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT26" s="4"/>
+      <c r="AU26" s="4"/>
+      <c r="AV26" s="4"/>
+      <c r="AW26" s="4"/>
+    </row>
+    <row r="27" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -3079,8 +3268,12 @@
       <c r="AQ27" s="4"/>
       <c r="AR27" s="4"/>
       <c r="AS27" s="4"/>
-    </row>
-    <row r="28" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT27" s="4"/>
+      <c r="AU27" s="4"/>
+      <c r="AV27" s="4"/>
+      <c r="AW27" s="4"/>
+    </row>
+    <row r="28" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -3098,10 +3291,10 @@
       <c r="Q28" s="4"/>
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
       <c r="AA28" s="4"/>
       <c r="AB28" s="4"/>
@@ -3122,10 +3315,14 @@
       <c r="AQ28" s="4"/>
       <c r="AR28" s="4"/>
       <c r="AS28" s="4"/>
-    </row>
-    <row r="29" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B29" s="2" t="s">
-        <v>41</v>
+      <c r="AT28" s="4"/>
+      <c r="AU28" s="4"/>
+      <c r="AV28" s="4"/>
+      <c r="AW28" s="4"/>
+    </row>
+    <row r="29" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="B29" s="29" t="s">
+        <v>74</v>
       </c>
       <c r="C29" s="4"/>
       <c r="D29" s="4"/>
@@ -3136,7 +3333,7 @@
         <v>0.10181208756677496</v>
       </c>
       <c r="H29" s="20">
-        <f t="shared" ref="H29:N33" si="13">+H3/D3-1</f>
+        <f t="shared" ref="H29:O33" si="13">+H3/D3-1</f>
         <v>0.12107065048241528</v>
       </c>
       <c r="I29" s="20">
@@ -3163,27 +3360,30 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
-      <c r="R29" s="4"/>
+      <c r="O29" s="20">
+        <f t="shared" si="13"/>
+        <v>0.61522404675758424</v>
+      </c>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
       <c r="S29" s="4"/>
-      <c r="T29" s="20">
-        <f t="shared" ref="T29:V33" si="14">+T3/S3-1</f>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="20">
+        <f t="shared" ref="X29:Z33" si="14">+X3/W3-1</f>
         <v>0.11544452941343075</v>
       </c>
-      <c r="U29" s="20">
+      <c r="Y29" s="20">
         <f t="shared" si="14"/>
         <v>0.11796968235025274</v>
       </c>
-      <c r="V29" s="20">
+      <c r="Z29" s="20">
         <f t="shared" si="14"/>
         <v>-0.22803152467691745</v>
       </c>
-      <c r="W29" s="4"/>
-      <c r="X29" s="4"/>
-      <c r="Y29" s="4"/>
-      <c r="Z29" s="4"/>
       <c r="AA29" s="4"/>
       <c r="AB29" s="4"/>
       <c r="AC29" s="4"/>
@@ -3203,9 +3403,13 @@
       <c r="AQ29" s="4"/>
       <c r="AR29" s="4"/>
       <c r="AS29" s="4"/>
-    </row>
-    <row r="30" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
+      <c r="AT29" s="4"/>
+      <c r="AU29" s="4"/>
+      <c r="AV29" s="4"/>
+      <c r="AW29" s="4"/>
+    </row>
+    <row r="30" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="B30" s="29" t="s">
         <v>42</v>
       </c>
       <c r="C30" s="4"/>
@@ -3244,27 +3448,30 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-      <c r="Q30" s="4"/>
-      <c r="R30" s="4"/>
+      <c r="O30" s="20">
+        <f t="shared" si="13"/>
+        <v>-2.9889879391714724E-2</v>
+      </c>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
       <c r="S30" s="4"/>
-      <c r="T30" s="20">
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="20">
         <f t="shared" si="14"/>
         <v>-0.12078214223914174</v>
       </c>
-      <c r="U30" s="20">
+      <c r="Y30" s="20">
         <f t="shared" si="14"/>
         <v>2.3617398149970548E-2</v>
       </c>
-      <c r="V30" s="20">
+      <c r="Z30" s="20">
         <f t="shared" si="14"/>
         <v>3.7185156700634492</v>
       </c>
-      <c r="W30" s="4"/>
-      <c r="X30" s="4"/>
-      <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
       <c r="AA30" s="4"/>
       <c r="AB30" s="4"/>
       <c r="AC30" s="4"/>
@@ -3284,10 +3491,14 @@
       <c r="AQ30" s="4"/>
       <c r="AR30" s="4"/>
       <c r="AS30" s="4"/>
-    </row>
-    <row r="31" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT30" s="4"/>
+      <c r="AU30" s="4"/>
+      <c r="AV30" s="4"/>
+      <c r="AW30" s="4"/>
+    </row>
+    <row r="31" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -3325,27 +3536,30 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
+      <c r="O31" s="20">
+        <f t="shared" si="13"/>
+        <v>0.15522388059701497</v>
+      </c>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
       <c r="S31" s="4"/>
-      <c r="T31" s="20">
+      <c r="T31" s="4"/>
+      <c r="U31" s="4"/>
+      <c r="V31" s="4"/>
+      <c r="W31" s="4"/>
+      <c r="X31" s="20">
         <f t="shared" si="14"/>
         <v>-6.3530849114233345E-2</v>
       </c>
-      <c r="U31" s="20">
+      <c r="Y31" s="20">
         <f t="shared" si="14"/>
         <v>-4.24005218525767E-2</v>
       </c>
-      <c r="V31" s="20">
+      <c r="Z31" s="20">
         <f t="shared" si="14"/>
         <v>5.0408719346048958E-2</v>
       </c>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
       <c r="AA31" s="4"/>
       <c r="AB31" s="4"/>
       <c r="AC31" s="4"/>
@@ -3365,10 +3579,14 @@
       <c r="AQ31" s="4"/>
       <c r="AR31" s="4"/>
       <c r="AS31" s="4"/>
-    </row>
-    <row r="32" spans="2:45" x14ac:dyDescent="0.2">
-      <c r="B32" s="2" t="s">
-        <v>44</v>
+      <c r="AT31" s="4"/>
+      <c r="AU31" s="4"/>
+      <c r="AV31" s="4"/>
+      <c r="AW31" s="4"/>
+    </row>
+    <row r="32" spans="2:49" x14ac:dyDescent="0.2">
+      <c r="B32" s="29" t="s">
+        <v>75</v>
       </c>
       <c r="C32" s="4"/>
       <c r="D32" s="4"/>
@@ -3406,27 +3624,30 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
+      <c r="O32" s="20">
+        <f t="shared" si="13"/>
+        <v>4.8183839881393631E-2</v>
+      </c>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
       <c r="S32" s="4"/>
-      <c r="T32" s="20">
+      <c r="T32" s="4"/>
+      <c r="U32" s="4"/>
+      <c r="V32" s="4"/>
+      <c r="W32" s="4"/>
+      <c r="X32" s="20">
         <f t="shared" si="14"/>
         <v>-2.9138362531283546E-2</v>
       </c>
-      <c r="U32" s="20">
+      <c r="Y32" s="20">
         <f t="shared" si="14"/>
         <v>-3.6457374332535486E-2</v>
       </c>
-      <c r="V32" s="20">
+      <c r="Z32" s="20">
         <f t="shared" si="14"/>
         <v>9.7458436843111063E-2</v>
       </c>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
       <c r="AA32" s="4"/>
       <c r="AB32" s="4"/>
       <c r="AC32" s="4"/>
@@ -3446,10 +3667,14 @@
       <c r="AQ32" s="4"/>
       <c r="AR32" s="4"/>
       <c r="AS32" s="4"/>
-    </row>
-    <row r="33" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT32" s="4"/>
+      <c r="AU32" s="4"/>
+      <c r="AV32" s="4"/>
+      <c r="AW32" s="4"/>
+    </row>
+    <row r="33" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B33" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
@@ -3487,27 +3712,30 @@
         <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O33" s="18"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="18"/>
+      <c r="O33" s="24">
+        <f t="shared" si="13"/>
+        <v>0.29606056545625092</v>
+      </c>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="24"/>
+      <c r="R33" s="24"/>
       <c r="S33" s="18"/>
-      <c r="T33" s="24">
+      <c r="T33" s="18"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="18"/>
+      <c r="W33" s="18"/>
+      <c r="X33" s="24">
         <f t="shared" si="14"/>
         <v>6.0195379749369504E-2</v>
       </c>
-      <c r="U33" s="24">
+      <c r="Y33" s="24">
         <f t="shared" si="14"/>
         <v>8.3797511376295875E-2</v>
       </c>
-      <c r="V33" s="24">
+      <c r="Z33" s="24">
         <f t="shared" si="14"/>
         <v>0.1734873429850694</v>
       </c>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
       <c r="AA33" s="4"/>
       <c r="AB33" s="4"/>
       <c r="AC33" s="4"/>
@@ -3527,10 +3755,14 @@
       <c r="AQ33" s="4"/>
       <c r="AR33" s="4"/>
       <c r="AS33" s="4"/>
-    </row>
-    <row r="34" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT33" s="4"/>
+      <c r="AU33" s="4"/>
+      <c r="AV33" s="4"/>
+      <c r="AW33" s="4"/>
+    </row>
+    <row r="34" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C34" s="20">
         <f t="shared" ref="C34:F34" si="16">+C11/C7</f>
@@ -3580,39 +3812,42 @@
         <f t="shared" si="19"/>
         <v>0.65221017514595492</v>
       </c>
-      <c r="O34" s="4"/>
-      <c r="P34" s="20" t="e">
-        <f t="shared" ref="P34:U34" si="20">+P11/P7</f>
+      <c r="O34" s="20">
+        <f t="shared" ref="O34" si="20">+O11/O7</f>
+        <v>0.60025846471956579</v>
+      </c>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="4"/>
+      <c r="T34" s="20" t="e">
+        <f t="shared" ref="T34:Y34" si="21">+T11/T7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q34" s="20" t="e">
-        <f t="shared" si="20"/>
+      <c r="U34" s="20" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R34" s="20" t="e">
-        <f t="shared" si="20"/>
+      <c r="V34" s="20" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S34" s="20">
-        <f t="shared" si="20"/>
+      <c r="W34" s="20">
+        <f t="shared" si="21"/>
         <v>0.72847019257717105</v>
       </c>
-      <c r="T34" s="20">
-        <f t="shared" si="20"/>
+      <c r="X34" s="20">
+        <f t="shared" si="21"/>
         <v>0.71407261947470779</v>
       </c>
-      <c r="U34" s="20">
-        <f t="shared" si="20"/>
+      <c r="Y34" s="20">
+        <f t="shared" si="21"/>
         <v>0.70509939197547</v>
       </c>
-      <c r="V34" s="20">
-        <f t="shared" ref="V34" si="21">+V11/V7</f>
+      <c r="Z34" s="20">
+        <f t="shared" ref="Z34" si="22">+Z11/Z7</f>
         <v>0.65822408955268197</v>
       </c>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
       <c r="AA34" s="4"/>
       <c r="AB34" s="4"/>
       <c r="AC34" s="4"/>
@@ -3632,25 +3867,29 @@
       <c r="AQ34" s="4"/>
       <c r="AR34" s="4"/>
       <c r="AS34" s="4"/>
-    </row>
-    <row r="35" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT34" s="4"/>
+      <c r="AU34" s="4"/>
+      <c r="AV34" s="4"/>
+      <c r="AW34" s="4"/>
+    </row>
+    <row r="35" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C35" s="20">
-        <f t="shared" ref="C35:F35" si="22">+C18/C7</f>
+        <f t="shared" ref="C35:F35" si="23">+C18/C7</f>
         <v>0.26467517867180601</v>
       </c>
       <c r="D35" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.27988563480411094</v>
       </c>
       <c r="E35" s="20">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.28237951807228917</v>
       </c>
       <c r="F35" s="20" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G35" s="20">
@@ -3658,66 +3897,69 @@
         <v>0.2999173367400616</v>
       </c>
       <c r="H35" s="20">
-        <f t="shared" ref="H35:J35" si="23">+H18/H7</f>
+        <f t="shared" ref="H35:J35" si="24">+H18/H7</f>
         <v>0.30016359627285011</v>
       </c>
       <c r="I35" s="20">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0.30842179759377214</v>
       </c>
       <c r="J35" s="20" t="e">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K35" s="20">
-        <f t="shared" ref="K35:L35" si="24">+K18/K7</f>
+        <f t="shared" ref="K35:L35" si="25">+K18/K7</f>
         <v>0.28654696502746885</v>
       </c>
       <c r="L35" s="20">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.29461950429692363</v>
       </c>
       <c r="M35" s="20">
-        <f t="shared" ref="M35:N35" si="25">+M18/M7</f>
+        <f t="shared" ref="M35:N35" si="26">+M18/M7</f>
         <v>0.31785922047702153</v>
       </c>
       <c r="N35" s="20">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0.31969349457881568</v>
       </c>
-      <c r="O35" s="4"/>
-      <c r="P35" s="20" t="e">
-        <f t="shared" ref="P35:U35" si="26">+P18/P7</f>
+      <c r="O35" s="20">
+        <f t="shared" ref="O35" si="27">+O18/O7</f>
+        <v>0.34779012664771258</v>
+      </c>
+      <c r="P35" s="20"/>
+      <c r="Q35" s="20"/>
+      <c r="R35" s="20"/>
+      <c r="S35" s="4"/>
+      <c r="T35" s="20" t="e">
+        <f t="shared" ref="T35:Y35" si="28">+T18/T7</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q35" s="20" t="e">
-        <f t="shared" si="26"/>
+      <c r="U35" s="20" t="e">
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R35" s="20" t="e">
-        <f t="shared" si="26"/>
+      <c r="V35" s="20" t="e">
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S35" s="20">
-        <f t="shared" si="26"/>
+      <c r="W35" s="20">
+        <f t="shared" si="28"/>
         <v>0.26210113304239901</v>
       </c>
-      <c r="T35" s="20">
-        <f t="shared" si="26"/>
+      <c r="X35" s="20">
+        <f t="shared" si="28"/>
         <v>0.28989256245161532</v>
       </c>
-      <c r="U35" s="20">
-        <f t="shared" si="26"/>
+      <c r="Y35" s="20">
+        <f t="shared" si="28"/>
         <v>0.30798445965957594</v>
       </c>
-      <c r="V35" s="20">
-        <f t="shared" ref="V35" si="27">+V18/V7</f>
+      <c r="Z35" s="20">
+        <f t="shared" ref="Z35" si="29">+Z18/Z7</f>
         <v>0.30592217586887777</v>
       </c>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
       <c r="AA35" s="4"/>
       <c r="AB35" s="4"/>
       <c r="AC35" s="4"/>
@@ -3737,25 +3979,29 @@
       <c r="AQ35" s="4"/>
       <c r="AR35" s="4"/>
       <c r="AS35" s="4"/>
-    </row>
-    <row r="36" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT35" s="4"/>
+      <c r="AU35" s="4"/>
+      <c r="AV35" s="4"/>
+      <c r="AW35" s="4"/>
+    </row>
+    <row r="36" spans="2:49" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C36" s="20">
-        <f t="shared" ref="C36:F36" si="28">+C22/C21</f>
+        <f t="shared" ref="C36:F36" si="30">+C22/C21</f>
         <v>-1.8947368421052633E-2</v>
       </c>
       <c r="D36" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>7.9779411764705876E-2</v>
       </c>
       <c r="E36" s="20">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0.16195462478184991</v>
       </c>
       <c r="F36" s="20" t="e">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G36" s="20">
@@ -3763,66 +4009,69 @@
         <v>7.5733669927421893E-2</v>
       </c>
       <c r="H36" s="20">
-        <f t="shared" ref="H36:J36" si="29">+H22/H21</f>
+        <f t="shared" ref="H36:J36" si="31">+H22/H21</f>
         <v>7.0501474926253693E-2</v>
       </c>
       <c r="I36" s="20">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.14849187935034802</v>
       </c>
       <c r="J36" s="20" t="e">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K36" s="20">
-        <f t="shared" ref="K36:L36" si="30">+K22/K21</f>
+        <f t="shared" ref="K36:L36" si="32">+K22/K21</f>
         <v>0.14590020426028597</v>
       </c>
       <c r="L36" s="20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>3.2639545884578999E-2</v>
       </c>
       <c r="M36" s="20">
-        <f t="shared" ref="M36:N36" si="31">+M22/M21</f>
+        <f t="shared" ref="M36:N36" si="33">+M22/M21</f>
         <v>0.16236413043478262</v>
       </c>
       <c r="N36" s="20">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>0.21359404096834264</v>
       </c>
-      <c r="O36" s="4"/>
-      <c r="P36" s="20" t="e">
-        <f t="shared" ref="P36:U36" si="32">+P22/P21</f>
+      <c r="O36" s="20">
+        <f t="shared" ref="O36" si="34">+O22/O21</f>
+        <v>0.16550740146245765</v>
+      </c>
+      <c r="P36" s="20"/>
+      <c r="Q36" s="20"/>
+      <c r="R36" s="20"/>
+      <c r="S36" s="4"/>
+      <c r="T36" s="20" t="e">
+        <f t="shared" ref="T36:Y36" si="35">+T22/T21</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q36" s="20" t="e">
-        <f t="shared" si="32"/>
+      <c r="U36" s="20" t="e">
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="R36" s="20" t="e">
-        <f t="shared" si="32"/>
+      <c r="V36" s="20" t="e">
+        <f t="shared" si="35"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S36" s="20">
-        <f t="shared" si="32"/>
+      <c r="W36" s="20">
+        <f t="shared" si="35"/>
         <v>6.826649134341442E-2</v>
       </c>
-      <c r="T36" s="20">
-        <f t="shared" si="32"/>
+      <c r="X36" s="20">
+        <f t="shared" si="35"/>
         <v>0.10850864491951281</v>
       </c>
-      <c r="U36" s="20">
-        <f t="shared" si="32"/>
+      <c r="Y36" s="20">
+        <f t="shared" si="35"/>
         <v>0.12125706214689265</v>
       </c>
-      <c r="V36" s="20">
-        <f t="shared" ref="V36" si="33">+V22/V21</f>
+      <c r="Z36" s="20">
+        <f t="shared" ref="Z36" si="36">+Z22/Z21</f>
         <v>0.13143090927687429</v>
       </c>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
       <c r="AA36" s="4"/>
       <c r="AB36" s="4"/>
       <c r="AC36" s="4"/>
@@ -3842,8 +4091,12 @@
       <c r="AQ36" s="4"/>
       <c r="AR36" s="4"/>
       <c r="AS36" s="4"/>
-    </row>
-    <row r="37" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT36" s="4"/>
+      <c r="AU36" s="4"/>
+      <c r="AV36" s="4"/>
+      <c r="AW36" s="4"/>
+    </row>
+    <row r="37" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -3887,8 +4140,12 @@
       <c r="AQ37" s="4"/>
       <c r="AR37" s="4"/>
       <c r="AS37" s="4"/>
-    </row>
-    <row r="38" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT37" s="4"/>
+      <c r="AU37" s="4"/>
+      <c r="AV37" s="4"/>
+      <c r="AW37" s="4"/>
+    </row>
+    <row r="38" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -3932,8 +4189,12 @@
       <c r="AQ38" s="4"/>
       <c r="AR38" s="4"/>
       <c r="AS38" s="4"/>
-    </row>
-    <row r="39" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT38" s="4"/>
+      <c r="AU38" s="4"/>
+      <c r="AV38" s="4"/>
+      <c r="AW38" s="4"/>
+    </row>
+    <row r="39" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -3977,8 +4238,12 @@
       <c r="AQ39" s="4"/>
       <c r="AR39" s="4"/>
       <c r="AS39" s="4"/>
-    </row>
-    <row r="40" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT39" s="4"/>
+      <c r="AU39" s="4"/>
+      <c r="AV39" s="4"/>
+      <c r="AW39" s="4"/>
+    </row>
+    <row r="40" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -4022,8 +4287,12 @@
       <c r="AQ40" s="4"/>
       <c r="AR40" s="4"/>
       <c r="AS40" s="4"/>
-    </row>
-    <row r="41" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT40" s="4"/>
+      <c r="AU40" s="4"/>
+      <c r="AV40" s="4"/>
+      <c r="AW40" s="4"/>
+    </row>
+    <row r="41" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -4067,8 +4336,12 @@
       <c r="AQ41" s="4"/>
       <c r="AR41" s="4"/>
       <c r="AS41" s="4"/>
-    </row>
-    <row r="42" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT41" s="4"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
+      <c r="AW41" s="4"/>
+    </row>
+    <row r="42" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -4112,8 +4385,12 @@
       <c r="AQ42" s="4"/>
       <c r="AR42" s="4"/>
       <c r="AS42" s="4"/>
-    </row>
-    <row r="43" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT42" s="4"/>
+      <c r="AU42" s="4"/>
+      <c r="AV42" s="4"/>
+      <c r="AW42" s="4"/>
+    </row>
+    <row r="43" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -4157,8 +4434,12 @@
       <c r="AQ43" s="4"/>
       <c r="AR43" s="4"/>
       <c r="AS43" s="4"/>
-    </row>
-    <row r="44" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT43" s="4"/>
+      <c r="AU43" s="4"/>
+      <c r="AV43" s="4"/>
+      <c r="AW43" s="4"/>
+    </row>
+    <row r="44" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -4202,8 +4483,12 @@
       <c r="AQ44" s="4"/>
       <c r="AR44" s="4"/>
       <c r="AS44" s="4"/>
-    </row>
-    <row r="45" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT44" s="4"/>
+      <c r="AU44" s="4"/>
+      <c r="AV44" s="4"/>
+      <c r="AW44" s="4"/>
+    </row>
+    <row r="45" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -4247,8 +4532,12 @@
       <c r="AQ45" s="4"/>
       <c r="AR45" s="4"/>
       <c r="AS45" s="4"/>
-    </row>
-    <row r="46" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT45" s="4"/>
+      <c r="AU45" s="4"/>
+      <c r="AV45" s="4"/>
+      <c r="AW45" s="4"/>
+    </row>
+    <row r="46" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -4292,8 +4581,12 @@
       <c r="AQ46" s="4"/>
       <c r="AR46" s="4"/>
       <c r="AS46" s="4"/>
-    </row>
-    <row r="47" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT46" s="4"/>
+      <c r="AU46" s="4"/>
+      <c r="AV46" s="4"/>
+      <c r="AW46" s="4"/>
+    </row>
+    <row r="47" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -4337,8 +4630,12 @@
       <c r="AQ47" s="4"/>
       <c r="AR47" s="4"/>
       <c r="AS47" s="4"/>
-    </row>
-    <row r="48" spans="2:45" x14ac:dyDescent="0.2">
+      <c r="AT47" s="4"/>
+      <c r="AU47" s="4"/>
+      <c r="AV47" s="4"/>
+      <c r="AW47" s="4"/>
+    </row>
+    <row r="48" spans="2:49" x14ac:dyDescent="0.2">
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -4382,8 +4679,12 @@
       <c r="AQ48" s="4"/>
       <c r="AR48" s="4"/>
       <c r="AS48" s="4"/>
-    </row>
-    <row r="49" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT48" s="4"/>
+      <c r="AU48" s="4"/>
+      <c r="AV48" s="4"/>
+      <c r="AW48" s="4"/>
+    </row>
+    <row r="49" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -4427,8 +4728,12 @@
       <c r="AQ49" s="4"/>
       <c r="AR49" s="4"/>
       <c r="AS49" s="4"/>
-    </row>
-    <row r="50" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT49" s="4"/>
+      <c r="AU49" s="4"/>
+      <c r="AV49" s="4"/>
+      <c r="AW49" s="4"/>
+    </row>
+    <row r="50" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -4472,8 +4777,12 @@
       <c r="AQ50" s="4"/>
       <c r="AR50" s="4"/>
       <c r="AS50" s="4"/>
-    </row>
-    <row r="51" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT50" s="4"/>
+      <c r="AU50" s="4"/>
+      <c r="AV50" s="4"/>
+      <c r="AW50" s="4"/>
+    </row>
+    <row r="51" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -4517,8 +4826,12 @@
       <c r="AQ51" s="4"/>
       <c r="AR51" s="4"/>
       <c r="AS51" s="4"/>
-    </row>
-    <row r="52" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT51" s="4"/>
+      <c r="AU51" s="4"/>
+      <c r="AV51" s="4"/>
+      <c r="AW51" s="4"/>
+    </row>
+    <row r="52" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -4562,8 +4875,12 @@
       <c r="AQ52" s="4"/>
       <c r="AR52" s="4"/>
       <c r="AS52" s="4"/>
-    </row>
-    <row r="53" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT52" s="4"/>
+      <c r="AU52" s="4"/>
+      <c r="AV52" s="4"/>
+      <c r="AW52" s="4"/>
+    </row>
+    <row r="53" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C53" s="4"/>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -4607,8 +4924,12 @@
       <c r="AQ53" s="4"/>
       <c r="AR53" s="4"/>
       <c r="AS53" s="4"/>
-    </row>
-    <row r="54" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT53" s="4"/>
+      <c r="AU53" s="4"/>
+      <c r="AV53" s="4"/>
+      <c r="AW53" s="4"/>
+    </row>
+    <row r="54" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C54" s="4"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -4652,8 +4973,12 @@
       <c r="AQ54" s="4"/>
       <c r="AR54" s="4"/>
       <c r="AS54" s="4"/>
-    </row>
-    <row r="55" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT54" s="4"/>
+      <c r="AU54" s="4"/>
+      <c r="AV54" s="4"/>
+      <c r="AW54" s="4"/>
+    </row>
+    <row r="55" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C55" s="4"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -4697,8 +5022,12 @@
       <c r="AQ55" s="4"/>
       <c r="AR55" s="4"/>
       <c r="AS55" s="4"/>
-    </row>
-    <row r="56" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT55" s="4"/>
+      <c r="AU55" s="4"/>
+      <c r="AV55" s="4"/>
+      <c r="AW55" s="4"/>
+    </row>
+    <row r="56" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -4742,8 +5071,12 @@
       <c r="AQ56" s="4"/>
       <c r="AR56" s="4"/>
       <c r="AS56" s="4"/>
-    </row>
-    <row r="57" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT56" s="4"/>
+      <c r="AU56" s="4"/>
+      <c r="AV56" s="4"/>
+      <c r="AW56" s="4"/>
+    </row>
+    <row r="57" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C57" s="4"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -4787,8 +5120,12 @@
       <c r="AQ57" s="4"/>
       <c r="AR57" s="4"/>
       <c r="AS57" s="4"/>
-    </row>
-    <row r="58" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT57" s="4"/>
+      <c r="AU57" s="4"/>
+      <c r="AV57" s="4"/>
+      <c r="AW57" s="4"/>
+    </row>
+    <row r="58" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C58" s="4"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -4832,8 +5169,12 @@
       <c r="AQ58" s="4"/>
       <c r="AR58" s="4"/>
       <c r="AS58" s="4"/>
-    </row>
-    <row r="59" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT58" s="4"/>
+      <c r="AU58" s="4"/>
+      <c r="AV58" s="4"/>
+      <c r="AW58" s="4"/>
+    </row>
+    <row r="59" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C59" s="4"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -4877,8 +5218,12 @@
       <c r="AQ59" s="4"/>
       <c r="AR59" s="4"/>
       <c r="AS59" s="4"/>
-    </row>
-    <row r="60" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT59" s="4"/>
+      <c r="AU59" s="4"/>
+      <c r="AV59" s="4"/>
+      <c r="AW59" s="4"/>
+    </row>
+    <row r="60" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C60" s="4"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -4922,8 +5267,12 @@
       <c r="AQ60" s="4"/>
       <c r="AR60" s="4"/>
       <c r="AS60" s="4"/>
-    </row>
-    <row r="61" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT60" s="4"/>
+      <c r="AU60" s="4"/>
+      <c r="AV60" s="4"/>
+      <c r="AW60" s="4"/>
+    </row>
+    <row r="61" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -4967,8 +5316,12 @@
       <c r="AQ61" s="4"/>
       <c r="AR61" s="4"/>
       <c r="AS61" s="4"/>
-    </row>
-    <row r="62" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT61" s="4"/>
+      <c r="AU61" s="4"/>
+      <c r="AV61" s="4"/>
+      <c r="AW61" s="4"/>
+    </row>
+    <row r="62" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C62" s="4"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -5012,8 +5365,12 @@
       <c r="AQ62" s="4"/>
       <c r="AR62" s="4"/>
       <c r="AS62" s="4"/>
-    </row>
-    <row r="63" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT62" s="4"/>
+      <c r="AU62" s="4"/>
+      <c r="AV62" s="4"/>
+      <c r="AW62" s="4"/>
+    </row>
+    <row r="63" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C63" s="4"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -5057,8 +5414,12 @@
       <c r="AQ63" s="4"/>
       <c r="AR63" s="4"/>
       <c r="AS63" s="4"/>
-    </row>
-    <row r="64" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT63" s="4"/>
+      <c r="AU63" s="4"/>
+      <c r="AV63" s="4"/>
+      <c r="AW63" s="4"/>
+    </row>
+    <row r="64" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C64" s="4"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -5102,8 +5463,12 @@
       <c r="AQ64" s="4"/>
       <c r="AR64" s="4"/>
       <c r="AS64" s="4"/>
-    </row>
-    <row r="65" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT64" s="4"/>
+      <c r="AU64" s="4"/>
+      <c r="AV64" s="4"/>
+      <c r="AW64" s="4"/>
+    </row>
+    <row r="65" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C65" s="4"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -5147,8 +5512,12 @@
       <c r="AQ65" s="4"/>
       <c r="AR65" s="4"/>
       <c r="AS65" s="4"/>
-    </row>
-    <row r="66" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT65" s="4"/>
+      <c r="AU65" s="4"/>
+      <c r="AV65" s="4"/>
+      <c r="AW65" s="4"/>
+    </row>
+    <row r="66" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C66" s="4"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -5192,8 +5561,12 @@
       <c r="AQ66" s="4"/>
       <c r="AR66" s="4"/>
       <c r="AS66" s="4"/>
-    </row>
-    <row r="67" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT66" s="4"/>
+      <c r="AU66" s="4"/>
+      <c r="AV66" s="4"/>
+      <c r="AW66" s="4"/>
+    </row>
+    <row r="67" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C67" s="4"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -5237,8 +5610,12 @@
       <c r="AQ67" s="4"/>
       <c r="AR67" s="4"/>
       <c r="AS67" s="4"/>
-    </row>
-    <row r="68" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT67" s="4"/>
+      <c r="AU67" s="4"/>
+      <c r="AV67" s="4"/>
+      <c r="AW67" s="4"/>
+    </row>
+    <row r="68" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C68" s="4"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -5282,8 +5659,12 @@
       <c r="AQ68" s="4"/>
       <c r="AR68" s="4"/>
       <c r="AS68" s="4"/>
-    </row>
-    <row r="69" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT68" s="4"/>
+      <c r="AU68" s="4"/>
+      <c r="AV68" s="4"/>
+      <c r="AW68" s="4"/>
+    </row>
+    <row r="69" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C69" s="4"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -5327,8 +5708,12 @@
       <c r="AQ69" s="4"/>
       <c r="AR69" s="4"/>
       <c r="AS69" s="4"/>
-    </row>
-    <row r="70" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT69" s="4"/>
+      <c r="AU69" s="4"/>
+      <c r="AV69" s="4"/>
+      <c r="AW69" s="4"/>
+    </row>
+    <row r="70" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C70" s="4"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -5372,8 +5757,12 @@
       <c r="AQ70" s="4"/>
       <c r="AR70" s="4"/>
       <c r="AS70" s="4"/>
-    </row>
-    <row r="71" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT70" s="4"/>
+      <c r="AU70" s="4"/>
+      <c r="AV70" s="4"/>
+      <c r="AW70" s="4"/>
+    </row>
+    <row r="71" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C71" s="4"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -5417,8 +5806,12 @@
       <c r="AQ71" s="4"/>
       <c r="AR71" s="4"/>
       <c r="AS71" s="4"/>
-    </row>
-    <row r="72" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT71" s="4"/>
+      <c r="AU71" s="4"/>
+      <c r="AV71" s="4"/>
+      <c r="AW71" s="4"/>
+    </row>
+    <row r="72" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -5462,8 +5855,12 @@
       <c r="AQ72" s="4"/>
       <c r="AR72" s="4"/>
       <c r="AS72" s="4"/>
-    </row>
-    <row r="73" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT72" s="4"/>
+      <c r="AU72" s="4"/>
+      <c r="AV72" s="4"/>
+      <c r="AW72" s="4"/>
+    </row>
+    <row r="73" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -5507,8 +5904,12 @@
       <c r="AQ73" s="4"/>
       <c r="AR73" s="4"/>
       <c r="AS73" s="4"/>
-    </row>
-    <row r="74" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT73" s="4"/>
+      <c r="AU73" s="4"/>
+      <c r="AV73" s="4"/>
+      <c r="AW73" s="4"/>
+    </row>
+    <row r="74" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -5552,8 +5953,12 @@
       <c r="AQ74" s="4"/>
       <c r="AR74" s="4"/>
       <c r="AS74" s="4"/>
-    </row>
-    <row r="75" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT74" s="4"/>
+      <c r="AU74" s="4"/>
+      <c r="AV74" s="4"/>
+      <c r="AW74" s="4"/>
+    </row>
+    <row r="75" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C75" s="4"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
@@ -5597,8 +6002,12 @@
       <c r="AQ75" s="4"/>
       <c r="AR75" s="4"/>
       <c r="AS75" s="4"/>
-    </row>
-    <row r="76" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT75" s="4"/>
+      <c r="AU75" s="4"/>
+      <c r="AV75" s="4"/>
+      <c r="AW75" s="4"/>
+    </row>
+    <row r="76" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C76" s="4"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -5642,8 +6051,12 @@
       <c r="AQ76" s="4"/>
       <c r="AR76" s="4"/>
       <c r="AS76" s="4"/>
-    </row>
-    <row r="77" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT76" s="4"/>
+      <c r="AU76" s="4"/>
+      <c r="AV76" s="4"/>
+      <c r="AW76" s="4"/>
+    </row>
+    <row r="77" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C77" s="4"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -5687,8 +6100,12 @@
       <c r="AQ77" s="4"/>
       <c r="AR77" s="4"/>
       <c r="AS77" s="4"/>
-    </row>
-    <row r="78" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT77" s="4"/>
+      <c r="AU77" s="4"/>
+      <c r="AV77" s="4"/>
+      <c r="AW77" s="4"/>
+    </row>
+    <row r="78" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C78" s="4"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -5732,8 +6149,12 @@
       <c r="AQ78" s="4"/>
       <c r="AR78" s="4"/>
       <c r="AS78" s="4"/>
-    </row>
-    <row r="79" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT78" s="4"/>
+      <c r="AU78" s="4"/>
+      <c r="AV78" s="4"/>
+      <c r="AW78" s="4"/>
+    </row>
+    <row r="79" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C79" s="4"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -5777,8 +6198,12 @@
       <c r="AQ79" s="4"/>
       <c r="AR79" s="4"/>
       <c r="AS79" s="4"/>
-    </row>
-    <row r="80" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT79" s="4"/>
+      <c r="AU79" s="4"/>
+      <c r="AV79" s="4"/>
+      <c r="AW79" s="4"/>
+    </row>
+    <row r="80" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C80" s="4"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -5822,8 +6247,12 @@
       <c r="AQ80" s="4"/>
       <c r="AR80" s="4"/>
       <c r="AS80" s="4"/>
-    </row>
-    <row r="81" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT80" s="4"/>
+      <c r="AU80" s="4"/>
+      <c r="AV80" s="4"/>
+      <c r="AW80" s="4"/>
+    </row>
+    <row r="81" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C81" s="4"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -5867,8 +6296,12 @@
       <c r="AQ81" s="4"/>
       <c r="AR81" s="4"/>
       <c r="AS81" s="4"/>
-    </row>
-    <row r="82" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT81" s="4"/>
+      <c r="AU81" s="4"/>
+      <c r="AV81" s="4"/>
+      <c r="AW81" s="4"/>
+    </row>
+    <row r="82" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C82" s="4"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -5912,8 +6345,12 @@
       <c r="AQ82" s="4"/>
       <c r="AR82" s="4"/>
       <c r="AS82" s="4"/>
-    </row>
-    <row r="83" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT82" s="4"/>
+      <c r="AU82" s="4"/>
+      <c r="AV82" s="4"/>
+      <c r="AW82" s="4"/>
+    </row>
+    <row r="83" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C83" s="4"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -5957,8 +6394,12 @@
       <c r="AQ83" s="4"/>
       <c r="AR83" s="4"/>
       <c r="AS83" s="4"/>
-    </row>
-    <row r="84" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT83" s="4"/>
+      <c r="AU83" s="4"/>
+      <c r="AV83" s="4"/>
+      <c r="AW83" s="4"/>
+    </row>
+    <row r="84" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C84" s="4"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -6002,8 +6443,12 @@
       <c r="AQ84" s="4"/>
       <c r="AR84" s="4"/>
       <c r="AS84" s="4"/>
-    </row>
-    <row r="85" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT84" s="4"/>
+      <c r="AU84" s="4"/>
+      <c r="AV84" s="4"/>
+      <c r="AW84" s="4"/>
+    </row>
+    <row r="85" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C85" s="4"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -6047,8 +6492,12 @@
       <c r="AQ85" s="4"/>
       <c r="AR85" s="4"/>
       <c r="AS85" s="4"/>
-    </row>
-    <row r="86" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT85" s="4"/>
+      <c r="AU85" s="4"/>
+      <c r="AV85" s="4"/>
+      <c r="AW85" s="4"/>
+    </row>
+    <row r="86" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C86" s="4"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -6092,8 +6541,12 @@
       <c r="AQ86" s="4"/>
       <c r="AR86" s="4"/>
       <c r="AS86" s="4"/>
-    </row>
-    <row r="87" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT86" s="4"/>
+      <c r="AU86" s="4"/>
+      <c r="AV86" s="4"/>
+      <c r="AW86" s="4"/>
+    </row>
+    <row r="87" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C87" s="4"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
@@ -6137,8 +6590,12 @@
       <c r="AQ87" s="4"/>
       <c r="AR87" s="4"/>
       <c r="AS87" s="4"/>
-    </row>
-    <row r="88" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT87" s="4"/>
+      <c r="AU87" s="4"/>
+      <c r="AV87" s="4"/>
+      <c r="AW87" s="4"/>
+    </row>
+    <row r="88" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C88" s="4"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -6182,8 +6639,12 @@
       <c r="AQ88" s="4"/>
       <c r="AR88" s="4"/>
       <c r="AS88" s="4"/>
-    </row>
-    <row r="89" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT88" s="4"/>
+      <c r="AU88" s="4"/>
+      <c r="AV88" s="4"/>
+      <c r="AW88" s="4"/>
+    </row>
+    <row r="89" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C89" s="4"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -6227,8 +6688,12 @@
       <c r="AQ89" s="4"/>
       <c r="AR89" s="4"/>
       <c r="AS89" s="4"/>
-    </row>
-    <row r="90" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT89" s="4"/>
+      <c r="AU89" s="4"/>
+      <c r="AV89" s="4"/>
+      <c r="AW89" s="4"/>
+    </row>
+    <row r="90" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C90" s="4"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -6272,8 +6737,12 @@
       <c r="AQ90" s="4"/>
       <c r="AR90" s="4"/>
       <c r="AS90" s="4"/>
-    </row>
-    <row r="91" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT90" s="4"/>
+      <c r="AU90" s="4"/>
+      <c r="AV90" s="4"/>
+      <c r="AW90" s="4"/>
+    </row>
+    <row r="91" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C91" s="4"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -6317,8 +6786,12 @@
       <c r="AQ91" s="4"/>
       <c r="AR91" s="4"/>
       <c r="AS91" s="4"/>
-    </row>
-    <row r="92" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT91" s="4"/>
+      <c r="AU91" s="4"/>
+      <c r="AV91" s="4"/>
+      <c r="AW91" s="4"/>
+    </row>
+    <row r="92" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C92" s="4"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -6362,8 +6835,12 @@
       <c r="AQ92" s="4"/>
       <c r="AR92" s="4"/>
       <c r="AS92" s="4"/>
-    </row>
-    <row r="93" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT92" s="4"/>
+      <c r="AU92" s="4"/>
+      <c r="AV92" s="4"/>
+      <c r="AW92" s="4"/>
+    </row>
+    <row r="93" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C93" s="4"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -6407,8 +6884,12 @@
       <c r="AQ93" s="4"/>
       <c r="AR93" s="4"/>
       <c r="AS93" s="4"/>
-    </row>
-    <row r="94" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT93" s="4"/>
+      <c r="AU93" s="4"/>
+      <c r="AV93" s="4"/>
+      <c r="AW93" s="4"/>
+    </row>
+    <row r="94" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C94" s="4"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -6452,8 +6933,12 @@
       <c r="AQ94" s="4"/>
       <c r="AR94" s="4"/>
       <c r="AS94" s="4"/>
-    </row>
-    <row r="95" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT94" s="4"/>
+      <c r="AU94" s="4"/>
+      <c r="AV94" s="4"/>
+      <c r="AW94" s="4"/>
+    </row>
+    <row r="95" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C95" s="4"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -6497,8 +6982,12 @@
       <c r="AQ95" s="4"/>
       <c r="AR95" s="4"/>
       <c r="AS95" s="4"/>
-    </row>
-    <row r="96" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT95" s="4"/>
+      <c r="AU95" s="4"/>
+      <c r="AV95" s="4"/>
+      <c r="AW95" s="4"/>
+    </row>
+    <row r="96" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C96" s="4"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -6542,8 +7031,12 @@
       <c r="AQ96" s="4"/>
       <c r="AR96" s="4"/>
       <c r="AS96" s="4"/>
-    </row>
-    <row r="97" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT96" s="4"/>
+      <c r="AU96" s="4"/>
+      <c r="AV96" s="4"/>
+      <c r="AW96" s="4"/>
+    </row>
+    <row r="97" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -6587,8 +7080,12 @@
       <c r="AQ97" s="4"/>
       <c r="AR97" s="4"/>
       <c r="AS97" s="4"/>
-    </row>
-    <row r="98" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT97" s="4"/>
+      <c r="AU97" s="4"/>
+      <c r="AV97" s="4"/>
+      <c r="AW97" s="4"/>
+    </row>
+    <row r="98" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C98" s="4"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -6632,8 +7129,12 @@
       <c r="AQ98" s="4"/>
       <c r="AR98" s="4"/>
       <c r="AS98" s="4"/>
-    </row>
-    <row r="99" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT98" s="4"/>
+      <c r="AU98" s="4"/>
+      <c r="AV98" s="4"/>
+      <c r="AW98" s="4"/>
+    </row>
+    <row r="99" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C99" s="4"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -6677,8 +7178,12 @@
       <c r="AQ99" s="4"/>
       <c r="AR99" s="4"/>
       <c r="AS99" s="4"/>
-    </row>
-    <row r="100" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT99" s="4"/>
+      <c r="AU99" s="4"/>
+      <c r="AV99" s="4"/>
+      <c r="AW99" s="4"/>
+    </row>
+    <row r="100" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C100" s="4"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -6722,8 +7227,12 @@
       <c r="AQ100" s="4"/>
       <c r="AR100" s="4"/>
       <c r="AS100" s="4"/>
-    </row>
-    <row r="101" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT100" s="4"/>
+      <c r="AU100" s="4"/>
+      <c r="AV100" s="4"/>
+      <c r="AW100" s="4"/>
+    </row>
+    <row r="101" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C101" s="4"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -6767,8 +7276,12 @@
       <c r="AQ101" s="4"/>
       <c r="AR101" s="4"/>
       <c r="AS101" s="4"/>
-    </row>
-    <row r="102" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT101" s="4"/>
+      <c r="AU101" s="4"/>
+      <c r="AV101" s="4"/>
+      <c r="AW101" s="4"/>
+    </row>
+    <row r="102" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C102" s="4"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -6812,8 +7325,12 @@
       <c r="AQ102" s="4"/>
       <c r="AR102" s="4"/>
       <c r="AS102" s="4"/>
-    </row>
-    <row r="103" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT102" s="4"/>
+      <c r="AU102" s="4"/>
+      <c r="AV102" s="4"/>
+      <c r="AW102" s="4"/>
+    </row>
+    <row r="103" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C103" s="4"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -6857,8 +7374,12 @@
       <c r="AQ103" s="4"/>
       <c r="AR103" s="4"/>
       <c r="AS103" s="4"/>
-    </row>
-    <row r="104" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT103" s="4"/>
+      <c r="AU103" s="4"/>
+      <c r="AV103" s="4"/>
+      <c r="AW103" s="4"/>
+    </row>
+    <row r="104" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C104" s="4"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -6902,8 +7423,12 @@
       <c r="AQ104" s="4"/>
       <c r="AR104" s="4"/>
       <c r="AS104" s="4"/>
-    </row>
-    <row r="105" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT104" s="4"/>
+      <c r="AU104" s="4"/>
+      <c r="AV104" s="4"/>
+      <c r="AW104" s="4"/>
+    </row>
+    <row r="105" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C105" s="4"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -6947,8 +7472,12 @@
       <c r="AQ105" s="4"/>
       <c r="AR105" s="4"/>
       <c r="AS105" s="4"/>
-    </row>
-    <row r="106" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT105" s="4"/>
+      <c r="AU105" s="4"/>
+      <c r="AV105" s="4"/>
+      <c r="AW105" s="4"/>
+    </row>
+    <row r="106" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C106" s="4"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -6992,8 +7521,12 @@
       <c r="AQ106" s="4"/>
       <c r="AR106" s="4"/>
       <c r="AS106" s="4"/>
-    </row>
-    <row r="107" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT106" s="4"/>
+      <c r="AU106" s="4"/>
+      <c r="AV106" s="4"/>
+      <c r="AW106" s="4"/>
+    </row>
+    <row r="107" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C107" s="4"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -7037,8 +7570,12 @@
       <c r="AQ107" s="4"/>
       <c r="AR107" s="4"/>
       <c r="AS107" s="4"/>
-    </row>
-    <row r="108" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT107" s="4"/>
+      <c r="AU107" s="4"/>
+      <c r="AV107" s="4"/>
+      <c r="AW107" s="4"/>
+    </row>
+    <row r="108" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C108" s="4"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -7082,8 +7619,12 @@
       <c r="AQ108" s="4"/>
       <c r="AR108" s="4"/>
       <c r="AS108" s="4"/>
-    </row>
-    <row r="109" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT108" s="4"/>
+      <c r="AU108" s="4"/>
+      <c r="AV108" s="4"/>
+      <c r="AW108" s="4"/>
+    </row>
+    <row r="109" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
@@ -7127,8 +7668,12 @@
       <c r="AQ109" s="4"/>
       <c r="AR109" s="4"/>
       <c r="AS109" s="4"/>
-    </row>
-    <row r="110" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT109" s="4"/>
+      <c r="AU109" s="4"/>
+      <c r="AV109" s="4"/>
+      <c r="AW109" s="4"/>
+    </row>
+    <row r="110" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C110" s="4"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
@@ -7172,8 +7717,12 @@
       <c r="AQ110" s="4"/>
       <c r="AR110" s="4"/>
       <c r="AS110" s="4"/>
-    </row>
-    <row r="111" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT110" s="4"/>
+      <c r="AU110" s="4"/>
+      <c r="AV110" s="4"/>
+      <c r="AW110" s="4"/>
+    </row>
+    <row r="111" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C111" s="4"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
@@ -7217,8 +7766,12 @@
       <c r="AQ111" s="4"/>
       <c r="AR111" s="4"/>
       <c r="AS111" s="4"/>
-    </row>
-    <row r="112" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT111" s="4"/>
+      <c r="AU111" s="4"/>
+      <c r="AV111" s="4"/>
+      <c r="AW111" s="4"/>
+    </row>
+    <row r="112" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C112" s="4"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -7262,8 +7815,12 @@
       <c r="AQ112" s="4"/>
       <c r="AR112" s="4"/>
       <c r="AS112" s="4"/>
-    </row>
-    <row r="113" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT112" s="4"/>
+      <c r="AU112" s="4"/>
+      <c r="AV112" s="4"/>
+      <c r="AW112" s="4"/>
+    </row>
+    <row r="113" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C113" s="4"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -7307,8 +7864,12 @@
       <c r="AQ113" s="4"/>
       <c r="AR113" s="4"/>
       <c r="AS113" s="4"/>
-    </row>
-    <row r="114" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT113" s="4"/>
+      <c r="AU113" s="4"/>
+      <c r="AV113" s="4"/>
+      <c r="AW113" s="4"/>
+    </row>
+    <row r="114" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C114" s="4"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -7352,8 +7913,12 @@
       <c r="AQ114" s="4"/>
       <c r="AR114" s="4"/>
       <c r="AS114" s="4"/>
-    </row>
-    <row r="115" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT114" s="4"/>
+      <c r="AU114" s="4"/>
+      <c r="AV114" s="4"/>
+      <c r="AW114" s="4"/>
+    </row>
+    <row r="115" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C115" s="4"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -7397,8 +7962,12 @@
       <c r="AQ115" s="4"/>
       <c r="AR115" s="4"/>
       <c r="AS115" s="4"/>
-    </row>
-    <row r="116" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT115" s="4"/>
+      <c r="AU115" s="4"/>
+      <c r="AV115" s="4"/>
+      <c r="AW115" s="4"/>
+    </row>
+    <row r="116" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -7442,8 +8011,12 @@
       <c r="AQ116" s="4"/>
       <c r="AR116" s="4"/>
       <c r="AS116" s="4"/>
-    </row>
-    <row r="117" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT116" s="4"/>
+      <c r="AU116" s="4"/>
+      <c r="AV116" s="4"/>
+      <c r="AW116" s="4"/>
+    </row>
+    <row r="117" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C117" s="4"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -7487,8 +8060,12 @@
       <c r="AQ117" s="4"/>
       <c r="AR117" s="4"/>
       <c r="AS117" s="4"/>
-    </row>
-    <row r="118" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT117" s="4"/>
+      <c r="AU117" s="4"/>
+      <c r="AV117" s="4"/>
+      <c r="AW117" s="4"/>
+    </row>
+    <row r="118" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C118" s="4"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -7532,8 +8109,12 @@
       <c r="AQ118" s="4"/>
       <c r="AR118" s="4"/>
       <c r="AS118" s="4"/>
-    </row>
-    <row r="119" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT118" s="4"/>
+      <c r="AU118" s="4"/>
+      <c r="AV118" s="4"/>
+      <c r="AW118" s="4"/>
+    </row>
+    <row r="119" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C119" s="4"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -7577,8 +8158,12 @@
       <c r="AQ119" s="4"/>
       <c r="AR119" s="4"/>
       <c r="AS119" s="4"/>
-    </row>
-    <row r="120" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT119" s="4"/>
+      <c r="AU119" s="4"/>
+      <c r="AV119" s="4"/>
+      <c r="AW119" s="4"/>
+    </row>
+    <row r="120" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C120" s="4"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -7622,8 +8207,12 @@
       <c r="AQ120" s="4"/>
       <c r="AR120" s="4"/>
       <c r="AS120" s="4"/>
-    </row>
-    <row r="121" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT120" s="4"/>
+      <c r="AU120" s="4"/>
+      <c r="AV120" s="4"/>
+      <c r="AW120" s="4"/>
+    </row>
+    <row r="121" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C121" s="4"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
@@ -7667,8 +8256,12 @@
       <c r="AQ121" s="4"/>
       <c r="AR121" s="4"/>
       <c r="AS121" s="4"/>
-    </row>
-    <row r="122" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT121" s="4"/>
+      <c r="AU121" s="4"/>
+      <c r="AV121" s="4"/>
+      <c r="AW121" s="4"/>
+    </row>
+    <row r="122" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -7712,8 +8305,12 @@
       <c r="AQ122" s="4"/>
       <c r="AR122" s="4"/>
       <c r="AS122" s="4"/>
-    </row>
-    <row r="123" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT122" s="4"/>
+      <c r="AU122" s="4"/>
+      <c r="AV122" s="4"/>
+      <c r="AW122" s="4"/>
+    </row>
+    <row r="123" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C123" s="4"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -7757,8 +8354,12 @@
       <c r="AQ123" s="4"/>
       <c r="AR123" s="4"/>
       <c r="AS123" s="4"/>
-    </row>
-    <row r="124" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT123" s="4"/>
+      <c r="AU123" s="4"/>
+      <c r="AV123" s="4"/>
+      <c r="AW123" s="4"/>
+    </row>
+    <row r="124" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C124" s="4"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -7802,8 +8403,12 @@
       <c r="AQ124" s="4"/>
       <c r="AR124" s="4"/>
       <c r="AS124" s="4"/>
-    </row>
-    <row r="125" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT124" s="4"/>
+      <c r="AU124" s="4"/>
+      <c r="AV124" s="4"/>
+      <c r="AW124" s="4"/>
+    </row>
+    <row r="125" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -7847,8 +8452,12 @@
       <c r="AQ125" s="4"/>
       <c r="AR125" s="4"/>
       <c r="AS125" s="4"/>
-    </row>
-    <row r="126" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT125" s="4"/>
+      <c r="AU125" s="4"/>
+      <c r="AV125" s="4"/>
+      <c r="AW125" s="4"/>
+    </row>
+    <row r="126" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C126" s="4"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -7892,8 +8501,12 @@
       <c r="AQ126" s="4"/>
       <c r="AR126" s="4"/>
       <c r="AS126" s="4"/>
-    </row>
-    <row r="127" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT126" s="4"/>
+      <c r="AU126" s="4"/>
+      <c r="AV126" s="4"/>
+      <c r="AW126" s="4"/>
+    </row>
+    <row r="127" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C127" s="4"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -7937,8 +8550,12 @@
       <c r="AQ127" s="4"/>
       <c r="AR127" s="4"/>
       <c r="AS127" s="4"/>
-    </row>
-    <row r="128" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT127" s="4"/>
+      <c r="AU127" s="4"/>
+      <c r="AV127" s="4"/>
+      <c r="AW127" s="4"/>
+    </row>
+    <row r="128" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C128" s="4"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -7982,8 +8599,12 @@
       <c r="AQ128" s="4"/>
       <c r="AR128" s="4"/>
       <c r="AS128" s="4"/>
-    </row>
-    <row r="129" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT128" s="4"/>
+      <c r="AU128" s="4"/>
+      <c r="AV128" s="4"/>
+      <c r="AW128" s="4"/>
+    </row>
+    <row r="129" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C129" s="4"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -8027,8 +8648,12 @@
       <c r="AQ129" s="4"/>
       <c r="AR129" s="4"/>
       <c r="AS129" s="4"/>
-    </row>
-    <row r="130" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT129" s="4"/>
+      <c r="AU129" s="4"/>
+      <c r="AV129" s="4"/>
+      <c r="AW129" s="4"/>
+    </row>
+    <row r="130" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C130" s="4"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -8072,8 +8697,12 @@
       <c r="AQ130" s="4"/>
       <c r="AR130" s="4"/>
       <c r="AS130" s="4"/>
-    </row>
-    <row r="131" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT130" s="4"/>
+      <c r="AU130" s="4"/>
+      <c r="AV130" s="4"/>
+      <c r="AW130" s="4"/>
+    </row>
+    <row r="131" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C131" s="4"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -8117,8 +8746,12 @@
       <c r="AQ131" s="4"/>
       <c r="AR131" s="4"/>
       <c r="AS131" s="4"/>
-    </row>
-    <row r="132" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT131" s="4"/>
+      <c r="AU131" s="4"/>
+      <c r="AV131" s="4"/>
+      <c r="AW131" s="4"/>
+    </row>
+    <row r="132" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C132" s="4"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -8162,8 +8795,12 @@
       <c r="AQ132" s="4"/>
       <c r="AR132" s="4"/>
       <c r="AS132" s="4"/>
-    </row>
-    <row r="133" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT132" s="4"/>
+      <c r="AU132" s="4"/>
+      <c r="AV132" s="4"/>
+      <c r="AW132" s="4"/>
+    </row>
+    <row r="133" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C133" s="4"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -8207,8 +8844,12 @@
       <c r="AQ133" s="4"/>
       <c r="AR133" s="4"/>
       <c r="AS133" s="4"/>
-    </row>
-    <row r="134" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT133" s="4"/>
+      <c r="AU133" s="4"/>
+      <c r="AV133" s="4"/>
+      <c r="AW133" s="4"/>
+    </row>
+    <row r="134" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C134" s="4"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
@@ -8252,8 +8893,12 @@
       <c r="AQ134" s="4"/>
       <c r="AR134" s="4"/>
       <c r="AS134" s="4"/>
-    </row>
-    <row r="135" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT134" s="4"/>
+      <c r="AU134" s="4"/>
+      <c r="AV134" s="4"/>
+      <c r="AW134" s="4"/>
+    </row>
+    <row r="135" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C135" s="4"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -8297,8 +8942,12 @@
       <c r="AQ135" s="4"/>
       <c r="AR135" s="4"/>
       <c r="AS135" s="4"/>
-    </row>
-    <row r="136" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT135" s="4"/>
+      <c r="AU135" s="4"/>
+      <c r="AV135" s="4"/>
+      <c r="AW135" s="4"/>
+    </row>
+    <row r="136" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C136" s="4"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
@@ -8342,8 +8991,12 @@
       <c r="AQ136" s="4"/>
       <c r="AR136" s="4"/>
       <c r="AS136" s="4"/>
-    </row>
-    <row r="137" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT136" s="4"/>
+      <c r="AU136" s="4"/>
+      <c r="AV136" s="4"/>
+      <c r="AW136" s="4"/>
+    </row>
+    <row r="137" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C137" s="4"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
@@ -8387,8 +9040,12 @@
       <c r="AQ137" s="4"/>
       <c r="AR137" s="4"/>
       <c r="AS137" s="4"/>
-    </row>
-    <row r="138" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT137" s="4"/>
+      <c r="AU137" s="4"/>
+      <c r="AV137" s="4"/>
+      <c r="AW137" s="4"/>
+    </row>
+    <row r="138" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
@@ -8432,8 +9089,12 @@
       <c r="AQ138" s="4"/>
       <c r="AR138" s="4"/>
       <c r="AS138" s="4"/>
-    </row>
-    <row r="139" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT138" s="4"/>
+      <c r="AU138" s="4"/>
+      <c r="AV138" s="4"/>
+      <c r="AW138" s="4"/>
+    </row>
+    <row r="139" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C139" s="4"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
@@ -8477,8 +9138,12 @@
       <c r="AQ139" s="4"/>
       <c r="AR139" s="4"/>
       <c r="AS139" s="4"/>
-    </row>
-    <row r="140" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT139" s="4"/>
+      <c r="AU139" s="4"/>
+      <c r="AV139" s="4"/>
+      <c r="AW139" s="4"/>
+    </row>
+    <row r="140" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C140" s="4"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
@@ -8522,8 +9187,12 @@
       <c r="AQ140" s="4"/>
       <c r="AR140" s="4"/>
       <c r="AS140" s="4"/>
-    </row>
-    <row r="141" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT140" s="4"/>
+      <c r="AU140" s="4"/>
+      <c r="AV140" s="4"/>
+      <c r="AW140" s="4"/>
+    </row>
+    <row r="141" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C141" s="4"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
@@ -8567,8 +9236,12 @@
       <c r="AQ141" s="4"/>
       <c r="AR141" s="4"/>
       <c r="AS141" s="4"/>
-    </row>
-    <row r="142" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT141" s="4"/>
+      <c r="AU141" s="4"/>
+      <c r="AV141" s="4"/>
+      <c r="AW141" s="4"/>
+    </row>
+    <row r="142" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C142" s="4"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
@@ -8612,8 +9285,12 @@
       <c r="AQ142" s="4"/>
       <c r="AR142" s="4"/>
       <c r="AS142" s="4"/>
-    </row>
-    <row r="143" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT142" s="4"/>
+      <c r="AU142" s="4"/>
+      <c r="AV142" s="4"/>
+      <c r="AW142" s="4"/>
+    </row>
+    <row r="143" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C143" s="4"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
@@ -8657,8 +9334,12 @@
       <c r="AQ143" s="4"/>
       <c r="AR143" s="4"/>
       <c r="AS143" s="4"/>
-    </row>
-    <row r="144" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT143" s="4"/>
+      <c r="AU143" s="4"/>
+      <c r="AV143" s="4"/>
+      <c r="AW143" s="4"/>
+    </row>
+    <row r="144" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C144" s="4"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
@@ -8702,8 +9383,12 @@
       <c r="AQ144" s="4"/>
       <c r="AR144" s="4"/>
       <c r="AS144" s="4"/>
-    </row>
-    <row r="145" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT144" s="4"/>
+      <c r="AU144" s="4"/>
+      <c r="AV144" s="4"/>
+      <c r="AW144" s="4"/>
+    </row>
+    <row r="145" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C145" s="4"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
@@ -8747,8 +9432,12 @@
       <c r="AQ145" s="4"/>
       <c r="AR145" s="4"/>
       <c r="AS145" s="4"/>
-    </row>
-    <row r="146" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT145" s="4"/>
+      <c r="AU145" s="4"/>
+      <c r="AV145" s="4"/>
+      <c r="AW145" s="4"/>
+    </row>
+    <row r="146" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C146" s="4"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
@@ -8792,8 +9481,12 @@
       <c r="AQ146" s="4"/>
       <c r="AR146" s="4"/>
       <c r="AS146" s="4"/>
-    </row>
-    <row r="147" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT146" s="4"/>
+      <c r="AU146" s="4"/>
+      <c r="AV146" s="4"/>
+      <c r="AW146" s="4"/>
+    </row>
+    <row r="147" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C147" s="4"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
@@ -8837,8 +9530,12 @@
       <c r="AQ147" s="4"/>
       <c r="AR147" s="4"/>
       <c r="AS147" s="4"/>
-    </row>
-    <row r="148" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT147" s="4"/>
+      <c r="AU147" s="4"/>
+      <c r="AV147" s="4"/>
+      <c r="AW147" s="4"/>
+    </row>
+    <row r="148" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C148" s="4"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
@@ -8882,8 +9579,12 @@
       <c r="AQ148" s="4"/>
       <c r="AR148" s="4"/>
       <c r="AS148" s="4"/>
-    </row>
-    <row r="149" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT148" s="4"/>
+      <c r="AU148" s="4"/>
+      <c r="AV148" s="4"/>
+      <c r="AW148" s="4"/>
+    </row>
+    <row r="149" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C149" s="4"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
@@ -8927,8 +9628,12 @@
       <c r="AQ149" s="4"/>
       <c r="AR149" s="4"/>
       <c r="AS149" s="4"/>
-    </row>
-    <row r="150" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT149" s="4"/>
+      <c r="AU149" s="4"/>
+      <c r="AV149" s="4"/>
+      <c r="AW149" s="4"/>
+    </row>
+    <row r="150" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C150" s="4"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
@@ -8972,8 +9677,12 @@
       <c r="AQ150" s="4"/>
       <c r="AR150" s="4"/>
       <c r="AS150" s="4"/>
-    </row>
-    <row r="151" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT150" s="4"/>
+      <c r="AU150" s="4"/>
+      <c r="AV150" s="4"/>
+      <c r="AW150" s="4"/>
+    </row>
+    <row r="151" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C151" s="4"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
@@ -9017,8 +9726,12 @@
       <c r="AQ151" s="4"/>
       <c r="AR151" s="4"/>
       <c r="AS151" s="4"/>
-    </row>
-    <row r="152" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT151" s="4"/>
+      <c r="AU151" s="4"/>
+      <c r="AV151" s="4"/>
+      <c r="AW151" s="4"/>
+    </row>
+    <row r="152" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -9062,8 +9775,12 @@
       <c r="AQ152" s="4"/>
       <c r="AR152" s="4"/>
       <c r="AS152" s="4"/>
-    </row>
-    <row r="153" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT152" s="4"/>
+      <c r="AU152" s="4"/>
+      <c r="AV152" s="4"/>
+      <c r="AW152" s="4"/>
+    </row>
+    <row r="153" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C153" s="4"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -9107,8 +9824,12 @@
       <c r="AQ153" s="4"/>
       <c r="AR153" s="4"/>
       <c r="AS153" s="4"/>
-    </row>
-    <row r="154" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT153" s="4"/>
+      <c r="AU153" s="4"/>
+      <c r="AV153" s="4"/>
+      <c r="AW153" s="4"/>
+    </row>
+    <row r="154" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C154" s="4"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
@@ -9152,8 +9873,12 @@
       <c r="AQ154" s="4"/>
       <c r="AR154" s="4"/>
       <c r="AS154" s="4"/>
-    </row>
-    <row r="155" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT154" s="4"/>
+      <c r="AU154" s="4"/>
+      <c r="AV154" s="4"/>
+      <c r="AW154" s="4"/>
+    </row>
+    <row r="155" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C155" s="4"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -9197,8 +9922,12 @@
       <c r="AQ155" s="4"/>
       <c r="AR155" s="4"/>
       <c r="AS155" s="4"/>
-    </row>
-    <row r="156" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT155" s="4"/>
+      <c r="AU155" s="4"/>
+      <c r="AV155" s="4"/>
+      <c r="AW155" s="4"/>
+    </row>
+    <row r="156" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C156" s="4"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
@@ -9242,8 +9971,12 @@
       <c r="AQ156" s="4"/>
       <c r="AR156" s="4"/>
       <c r="AS156" s="4"/>
-    </row>
-    <row r="157" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT156" s="4"/>
+      <c r="AU156" s="4"/>
+      <c r="AV156" s="4"/>
+      <c r="AW156" s="4"/>
+    </row>
+    <row r="157" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C157" s="4"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -9287,8 +10020,12 @@
       <c r="AQ157" s="4"/>
       <c r="AR157" s="4"/>
       <c r="AS157" s="4"/>
-    </row>
-    <row r="158" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT157" s="4"/>
+      <c r="AU157" s="4"/>
+      <c r="AV157" s="4"/>
+      <c r="AW157" s="4"/>
+    </row>
+    <row r="158" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -9332,8 +10069,12 @@
       <c r="AQ158" s="4"/>
       <c r="AR158" s="4"/>
       <c r="AS158" s="4"/>
-    </row>
-    <row r="159" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT158" s="4"/>
+      <c r="AU158" s="4"/>
+      <c r="AV158" s="4"/>
+      <c r="AW158" s="4"/>
+    </row>
+    <row r="159" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C159" s="4"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -9377,8 +10118,12 @@
       <c r="AQ159" s="4"/>
       <c r="AR159" s="4"/>
       <c r="AS159" s="4"/>
-    </row>
-    <row r="160" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT159" s="4"/>
+      <c r="AU159" s="4"/>
+      <c r="AV159" s="4"/>
+      <c r="AW159" s="4"/>
+    </row>
+    <row r="160" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C160" s="4"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
@@ -9422,8 +10167,12 @@
       <c r="AQ160" s="4"/>
       <c r="AR160" s="4"/>
       <c r="AS160" s="4"/>
-    </row>
-    <row r="161" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT160" s="4"/>
+      <c r="AU160" s="4"/>
+      <c r="AV160" s="4"/>
+      <c r="AW160" s="4"/>
+    </row>
+    <row r="161" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -9467,8 +10216,12 @@
       <c r="AQ161" s="4"/>
       <c r="AR161" s="4"/>
       <c r="AS161" s="4"/>
-    </row>
-    <row r="162" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT161" s="4"/>
+      <c r="AU161" s="4"/>
+      <c r="AV161" s="4"/>
+      <c r="AW161" s="4"/>
+    </row>
+    <row r="162" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C162" s="4"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -9512,8 +10265,12 @@
       <c r="AQ162" s="4"/>
       <c r="AR162" s="4"/>
       <c r="AS162" s="4"/>
-    </row>
-    <row r="163" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT162" s="4"/>
+      <c r="AU162" s="4"/>
+      <c r="AV162" s="4"/>
+      <c r="AW162" s="4"/>
+    </row>
+    <row r="163" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C163" s="4"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -9557,8 +10314,12 @@
       <c r="AQ163" s="4"/>
       <c r="AR163" s="4"/>
       <c r="AS163" s="4"/>
-    </row>
-    <row r="164" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT163" s="4"/>
+      <c r="AU163" s="4"/>
+      <c r="AV163" s="4"/>
+      <c r="AW163" s="4"/>
+    </row>
+    <row r="164" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C164" s="4"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
@@ -9602,8 +10363,12 @@
       <c r="AQ164" s="4"/>
       <c r="AR164" s="4"/>
       <c r="AS164" s="4"/>
-    </row>
-    <row r="165" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT164" s="4"/>
+      <c r="AU164" s="4"/>
+      <c r="AV164" s="4"/>
+      <c r="AW164" s="4"/>
+    </row>
+    <row r="165" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C165" s="4"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
@@ -9647,8 +10412,12 @@
       <c r="AQ165" s="4"/>
       <c r="AR165" s="4"/>
       <c r="AS165" s="4"/>
-    </row>
-    <row r="166" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT165" s="4"/>
+      <c r="AU165" s="4"/>
+      <c r="AV165" s="4"/>
+      <c r="AW165" s="4"/>
+    </row>
+    <row r="166" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C166" s="4"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -9692,8 +10461,12 @@
       <c r="AQ166" s="4"/>
       <c r="AR166" s="4"/>
       <c r="AS166" s="4"/>
-    </row>
-    <row r="167" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT166" s="4"/>
+      <c r="AU166" s="4"/>
+      <c r="AV166" s="4"/>
+      <c r="AW166" s="4"/>
+    </row>
+    <row r="167" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C167" s="4"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -9737,8 +10510,12 @@
       <c r="AQ167" s="4"/>
       <c r="AR167" s="4"/>
       <c r="AS167" s="4"/>
-    </row>
-    <row r="168" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT167" s="4"/>
+      <c r="AU167" s="4"/>
+      <c r="AV167" s="4"/>
+      <c r="AW167" s="4"/>
+    </row>
+    <row r="168" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C168" s="4"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -9782,8 +10559,12 @@
       <c r="AQ168" s="4"/>
       <c r="AR168" s="4"/>
       <c r="AS168" s="4"/>
-    </row>
-    <row r="169" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT168" s="4"/>
+      <c r="AU168" s="4"/>
+      <c r="AV168" s="4"/>
+      <c r="AW168" s="4"/>
+    </row>
+    <row r="169" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C169" s="4"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -9827,8 +10608,12 @@
       <c r="AQ169" s="4"/>
       <c r="AR169" s="4"/>
       <c r="AS169" s="4"/>
-    </row>
-    <row r="170" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT169" s="4"/>
+      <c r="AU169" s="4"/>
+      <c r="AV169" s="4"/>
+      <c r="AW169" s="4"/>
+    </row>
+    <row r="170" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C170" s="4"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -9872,8 +10657,12 @@
       <c r="AQ170" s="4"/>
       <c r="AR170" s="4"/>
       <c r="AS170" s="4"/>
-    </row>
-    <row r="171" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT170" s="4"/>
+      <c r="AU170" s="4"/>
+      <c r="AV170" s="4"/>
+      <c r="AW170" s="4"/>
+    </row>
+    <row r="171" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C171" s="4"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -9917,8 +10706,12 @@
       <c r="AQ171" s="4"/>
       <c r="AR171" s="4"/>
       <c r="AS171" s="4"/>
-    </row>
-    <row r="172" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT171" s="4"/>
+      <c r="AU171" s="4"/>
+      <c r="AV171" s="4"/>
+      <c r="AW171" s="4"/>
+    </row>
+    <row r="172" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C172" s="4"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -9962,8 +10755,12 @@
       <c r="AQ172" s="4"/>
       <c r="AR172" s="4"/>
       <c r="AS172" s="4"/>
-    </row>
-    <row r="173" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT172" s="4"/>
+      <c r="AU172" s="4"/>
+      <c r="AV172" s="4"/>
+      <c r="AW172" s="4"/>
+    </row>
+    <row r="173" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C173" s="4"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -10007,8 +10804,12 @@
       <c r="AQ173" s="4"/>
       <c r="AR173" s="4"/>
       <c r="AS173" s="4"/>
-    </row>
-    <row r="174" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT173" s="4"/>
+      <c r="AU173" s="4"/>
+      <c r="AV173" s="4"/>
+      <c r="AW173" s="4"/>
+    </row>
+    <row r="174" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -10052,8 +10853,12 @@
       <c r="AQ174" s="4"/>
       <c r="AR174" s="4"/>
       <c r="AS174" s="4"/>
-    </row>
-    <row r="175" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT174" s="4"/>
+      <c r="AU174" s="4"/>
+      <c r="AV174" s="4"/>
+      <c r="AW174" s="4"/>
+    </row>
+    <row r="175" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C175" s="4"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -10097,8 +10902,12 @@
       <c r="AQ175" s="4"/>
       <c r="AR175" s="4"/>
       <c r="AS175" s="4"/>
-    </row>
-    <row r="176" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT175" s="4"/>
+      <c r="AU175" s="4"/>
+      <c r="AV175" s="4"/>
+      <c r="AW175" s="4"/>
+    </row>
+    <row r="176" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C176" s="4"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -10142,8 +10951,12 @@
       <c r="AQ176" s="4"/>
       <c r="AR176" s="4"/>
       <c r="AS176" s="4"/>
-    </row>
-    <row r="177" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT176" s="4"/>
+      <c r="AU176" s="4"/>
+      <c r="AV176" s="4"/>
+      <c r="AW176" s="4"/>
+    </row>
+    <row r="177" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C177" s="4"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -10187,8 +11000,12 @@
       <c r="AQ177" s="4"/>
       <c r="AR177" s="4"/>
       <c r="AS177" s="4"/>
-    </row>
-    <row r="178" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT177" s="4"/>
+      <c r="AU177" s="4"/>
+      <c r="AV177" s="4"/>
+      <c r="AW177" s="4"/>
+    </row>
+    <row r="178" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C178" s="4"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -10232,8 +11049,12 @@
       <c r="AQ178" s="4"/>
       <c r="AR178" s="4"/>
       <c r="AS178" s="4"/>
-    </row>
-    <row r="179" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT178" s="4"/>
+      <c r="AU178" s="4"/>
+      <c r="AV178" s="4"/>
+      <c r="AW178" s="4"/>
+    </row>
+    <row r="179" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C179" s="4"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
@@ -10277,8 +11098,12 @@
       <c r="AQ179" s="4"/>
       <c r="AR179" s="4"/>
       <c r="AS179" s="4"/>
-    </row>
-    <row r="180" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT179" s="4"/>
+      <c r="AU179" s="4"/>
+      <c r="AV179" s="4"/>
+      <c r="AW179" s="4"/>
+    </row>
+    <row r="180" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C180" s="4"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
@@ -10322,8 +11147,12 @@
       <c r="AQ180" s="4"/>
       <c r="AR180" s="4"/>
       <c r="AS180" s="4"/>
-    </row>
-    <row r="181" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT180" s="4"/>
+      <c r="AU180" s="4"/>
+      <c r="AV180" s="4"/>
+      <c r="AW180" s="4"/>
+    </row>
+    <row r="181" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C181" s="4"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -10367,8 +11196,12 @@
       <c r="AQ181" s="4"/>
       <c r="AR181" s="4"/>
       <c r="AS181" s="4"/>
-    </row>
-    <row r="182" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT181" s="4"/>
+      <c r="AU181" s="4"/>
+      <c r="AV181" s="4"/>
+      <c r="AW181" s="4"/>
+    </row>
+    <row r="182" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C182" s="4"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -10412,8 +11245,12 @@
       <c r="AQ182" s="4"/>
       <c r="AR182" s="4"/>
       <c r="AS182" s="4"/>
-    </row>
-    <row r="183" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT182" s="4"/>
+      <c r="AU182" s="4"/>
+      <c r="AV182" s="4"/>
+      <c r="AW182" s="4"/>
+    </row>
+    <row r="183" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C183" s="4"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -10457,8 +11294,12 @@
       <c r="AQ183" s="4"/>
       <c r="AR183" s="4"/>
       <c r="AS183" s="4"/>
-    </row>
-    <row r="184" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT183" s="4"/>
+      <c r="AU183" s="4"/>
+      <c r="AV183" s="4"/>
+      <c r="AW183" s="4"/>
+    </row>
+    <row r="184" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C184" s="4"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
@@ -10502,8 +11343,12 @@
       <c r="AQ184" s="4"/>
       <c r="AR184" s="4"/>
       <c r="AS184" s="4"/>
-    </row>
-    <row r="185" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT184" s="4"/>
+      <c r="AU184" s="4"/>
+      <c r="AV184" s="4"/>
+      <c r="AW184" s="4"/>
+    </row>
+    <row r="185" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C185" s="4"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
@@ -10547,8 +11392,12 @@
       <c r="AQ185" s="4"/>
       <c r="AR185" s="4"/>
       <c r="AS185" s="4"/>
-    </row>
-    <row r="186" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT185" s="4"/>
+      <c r="AU185" s="4"/>
+      <c r="AV185" s="4"/>
+      <c r="AW185" s="4"/>
+    </row>
+    <row r="186" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C186" s="4"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -10592,8 +11441,12 @@
       <c r="AQ186" s="4"/>
       <c r="AR186" s="4"/>
       <c r="AS186" s="4"/>
-    </row>
-    <row r="187" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT186" s="4"/>
+      <c r="AU186" s="4"/>
+      <c r="AV186" s="4"/>
+      <c r="AW186" s="4"/>
+    </row>
+    <row r="187" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C187" s="4"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -10637,8 +11490,12 @@
       <c r="AQ187" s="4"/>
       <c r="AR187" s="4"/>
       <c r="AS187" s="4"/>
-    </row>
-    <row r="188" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT187" s="4"/>
+      <c r="AU187" s="4"/>
+      <c r="AV187" s="4"/>
+      <c r="AW187" s="4"/>
+    </row>
+    <row r="188" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C188" s="4"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -10682,8 +11539,12 @@
       <c r="AQ188" s="4"/>
       <c r="AR188" s="4"/>
       <c r="AS188" s="4"/>
-    </row>
-    <row r="189" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT188" s="4"/>
+      <c r="AU188" s="4"/>
+      <c r="AV188" s="4"/>
+      <c r="AW188" s="4"/>
+    </row>
+    <row r="189" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C189" s="4"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -10727,8 +11588,12 @@
       <c r="AQ189" s="4"/>
       <c r="AR189" s="4"/>
       <c r="AS189" s="4"/>
-    </row>
-    <row r="190" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT189" s="4"/>
+      <c r="AU189" s="4"/>
+      <c r="AV189" s="4"/>
+      <c r="AW189" s="4"/>
+    </row>
+    <row r="190" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C190" s="4"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -10772,8 +11637,12 @@
       <c r="AQ190" s="4"/>
       <c r="AR190" s="4"/>
       <c r="AS190" s="4"/>
-    </row>
-    <row r="191" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT190" s="4"/>
+      <c r="AU190" s="4"/>
+      <c r="AV190" s="4"/>
+      <c r="AW190" s="4"/>
+    </row>
+    <row r="191" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C191" s="4"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -10817,8 +11686,12 @@
       <c r="AQ191" s="4"/>
       <c r="AR191" s="4"/>
       <c r="AS191" s="4"/>
-    </row>
-    <row r="192" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT191" s="4"/>
+      <c r="AU191" s="4"/>
+      <c r="AV191" s="4"/>
+      <c r="AW191" s="4"/>
+    </row>
+    <row r="192" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C192" s="4"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -10862,8 +11735,12 @@
       <c r="AQ192" s="4"/>
       <c r="AR192" s="4"/>
       <c r="AS192" s="4"/>
-    </row>
-    <row r="193" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT192" s="4"/>
+      <c r="AU192" s="4"/>
+      <c r="AV192" s="4"/>
+      <c r="AW192" s="4"/>
+    </row>
+    <row r="193" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C193" s="4"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -10907,8 +11784,12 @@
       <c r="AQ193" s="4"/>
       <c r="AR193" s="4"/>
       <c r="AS193" s="4"/>
-    </row>
-    <row r="194" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT193" s="4"/>
+      <c r="AU193" s="4"/>
+      <c r="AV193" s="4"/>
+      <c r="AW193" s="4"/>
+    </row>
+    <row r="194" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C194" s="4"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -10952,8 +11833,12 @@
       <c r="AQ194" s="4"/>
       <c r="AR194" s="4"/>
       <c r="AS194" s="4"/>
-    </row>
-    <row r="195" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT194" s="4"/>
+      <c r="AU194" s="4"/>
+      <c r="AV194" s="4"/>
+      <c r="AW194" s="4"/>
+    </row>
+    <row r="195" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C195" s="4"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -10997,8 +11882,12 @@
       <c r="AQ195" s="4"/>
       <c r="AR195" s="4"/>
       <c r="AS195" s="4"/>
-    </row>
-    <row r="196" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT195" s="4"/>
+      <c r="AU195" s="4"/>
+      <c r="AV195" s="4"/>
+      <c r="AW195" s="4"/>
+    </row>
+    <row r="196" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C196" s="4"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
@@ -11042,8 +11931,12 @@
       <c r="AQ196" s="4"/>
       <c r="AR196" s="4"/>
       <c r="AS196" s="4"/>
-    </row>
-    <row r="197" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT196" s="4"/>
+      <c r="AU196" s="4"/>
+      <c r="AV196" s="4"/>
+      <c r="AW196" s="4"/>
+    </row>
+    <row r="197" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C197" s="4"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
@@ -11087,8 +11980,12 @@
       <c r="AQ197" s="4"/>
       <c r="AR197" s="4"/>
       <c r="AS197" s="4"/>
-    </row>
-    <row r="198" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT197" s="4"/>
+      <c r="AU197" s="4"/>
+      <c r="AV197" s="4"/>
+      <c r="AW197" s="4"/>
+    </row>
+    <row r="198" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C198" s="4"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
@@ -11132,8 +12029,12 @@
       <c r="AQ198" s="4"/>
       <c r="AR198" s="4"/>
       <c r="AS198" s="4"/>
-    </row>
-    <row r="199" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT198" s="4"/>
+      <c r="AU198" s="4"/>
+      <c r="AV198" s="4"/>
+      <c r="AW198" s="4"/>
+    </row>
+    <row r="199" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C199" s="4"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
@@ -11177,8 +12078,12 @@
       <c r="AQ199" s="4"/>
       <c r="AR199" s="4"/>
       <c r="AS199" s="4"/>
-    </row>
-    <row r="200" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT199" s="4"/>
+      <c r="AU199" s="4"/>
+      <c r="AV199" s="4"/>
+      <c r="AW199" s="4"/>
+    </row>
+    <row r="200" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C200" s="4"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
@@ -11222,8 +12127,12 @@
       <c r="AQ200" s="4"/>
       <c r="AR200" s="4"/>
       <c r="AS200" s="4"/>
-    </row>
-    <row r="201" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT200" s="4"/>
+      <c r="AU200" s="4"/>
+      <c r="AV200" s="4"/>
+      <c r="AW200" s="4"/>
+    </row>
+    <row r="201" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C201" s="4"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
@@ -11267,8 +12176,12 @@
       <c r="AQ201" s="4"/>
       <c r="AR201" s="4"/>
       <c r="AS201" s="4"/>
-    </row>
-    <row r="202" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT201" s="4"/>
+      <c r="AU201" s="4"/>
+      <c r="AV201" s="4"/>
+      <c r="AW201" s="4"/>
+    </row>
+    <row r="202" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C202" s="4"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
@@ -11312,8 +12225,12 @@
       <c r="AQ202" s="4"/>
       <c r="AR202" s="4"/>
       <c r="AS202" s="4"/>
-    </row>
-    <row r="203" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT202" s="4"/>
+      <c r="AU202" s="4"/>
+      <c r="AV202" s="4"/>
+      <c r="AW202" s="4"/>
+    </row>
+    <row r="203" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C203" s="4"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
@@ -11357,8 +12274,12 @@
       <c r="AQ203" s="4"/>
       <c r="AR203" s="4"/>
       <c r="AS203" s="4"/>
-    </row>
-    <row r="204" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT203" s="4"/>
+      <c r="AU203" s="4"/>
+      <c r="AV203" s="4"/>
+      <c r="AW203" s="4"/>
+    </row>
+    <row r="204" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C204" s="4"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
@@ -11402,8 +12323,12 @@
       <c r="AQ204" s="4"/>
       <c r="AR204" s="4"/>
       <c r="AS204" s="4"/>
-    </row>
-    <row r="205" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT204" s="4"/>
+      <c r="AU204" s="4"/>
+      <c r="AV204" s="4"/>
+      <c r="AW204" s="4"/>
+    </row>
+    <row r="205" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C205" s="4"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
@@ -11447,8 +12372,12 @@
       <c r="AQ205" s="4"/>
       <c r="AR205" s="4"/>
       <c r="AS205" s="4"/>
-    </row>
-    <row r="206" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT205" s="4"/>
+      <c r="AU205" s="4"/>
+      <c r="AV205" s="4"/>
+      <c r="AW205" s="4"/>
+    </row>
+    <row r="206" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C206" s="4"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
@@ -11492,8 +12421,12 @@
       <c r="AQ206" s="4"/>
       <c r="AR206" s="4"/>
       <c r="AS206" s="4"/>
-    </row>
-    <row r="207" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT206" s="4"/>
+      <c r="AU206" s="4"/>
+      <c r="AV206" s="4"/>
+      <c r="AW206" s="4"/>
+    </row>
+    <row r="207" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C207" s="4"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
@@ -11537,8 +12470,12 @@
       <c r="AQ207" s="4"/>
       <c r="AR207" s="4"/>
       <c r="AS207" s="4"/>
-    </row>
-    <row r="208" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT207" s="4"/>
+      <c r="AU207" s="4"/>
+      <c r="AV207" s="4"/>
+      <c r="AW207" s="4"/>
+    </row>
+    <row r="208" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C208" s="4"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
@@ -11582,8 +12519,12 @@
       <c r="AQ208" s="4"/>
       <c r="AR208" s="4"/>
       <c r="AS208" s="4"/>
-    </row>
-    <row r="209" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT208" s="4"/>
+      <c r="AU208" s="4"/>
+      <c r="AV208" s="4"/>
+      <c r="AW208" s="4"/>
+    </row>
+    <row r="209" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C209" s="4"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
@@ -11627,8 +12568,12 @@
       <c r="AQ209" s="4"/>
       <c r="AR209" s="4"/>
       <c r="AS209" s="4"/>
-    </row>
-    <row r="210" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT209" s="4"/>
+      <c r="AU209" s="4"/>
+      <c r="AV209" s="4"/>
+      <c r="AW209" s="4"/>
+    </row>
+    <row r="210" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C210" s="4"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
@@ -11672,8 +12617,12 @@
       <c r="AQ210" s="4"/>
       <c r="AR210" s="4"/>
       <c r="AS210" s="4"/>
-    </row>
-    <row r="211" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT210" s="4"/>
+      <c r="AU210" s="4"/>
+      <c r="AV210" s="4"/>
+      <c r="AW210" s="4"/>
+    </row>
+    <row r="211" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C211" s="4"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
@@ -11717,8 +12666,12 @@
       <c r="AQ211" s="4"/>
       <c r="AR211" s="4"/>
       <c r="AS211" s="4"/>
-    </row>
-    <row r="212" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT211" s="4"/>
+      <c r="AU211" s="4"/>
+      <c r="AV211" s="4"/>
+      <c r="AW211" s="4"/>
+    </row>
+    <row r="212" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C212" s="4"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
@@ -11762,8 +12715,12 @@
       <c r="AQ212" s="4"/>
       <c r="AR212" s="4"/>
       <c r="AS212" s="4"/>
-    </row>
-    <row r="213" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT212" s="4"/>
+      <c r="AU212" s="4"/>
+      <c r="AV212" s="4"/>
+      <c r="AW212" s="4"/>
+    </row>
+    <row r="213" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C213" s="4"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
@@ -11807,8 +12764,12 @@
       <c r="AQ213" s="4"/>
       <c r="AR213" s="4"/>
       <c r="AS213" s="4"/>
-    </row>
-    <row r="214" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT213" s="4"/>
+      <c r="AU213" s="4"/>
+      <c r="AV213" s="4"/>
+      <c r="AW213" s="4"/>
+    </row>
+    <row r="214" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C214" s="4"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
@@ -11852,8 +12813,12 @@
       <c r="AQ214" s="4"/>
       <c r="AR214" s="4"/>
       <c r="AS214" s="4"/>
-    </row>
-    <row r="215" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT214" s="4"/>
+      <c r="AU214" s="4"/>
+      <c r="AV214" s="4"/>
+      <c r="AW214" s="4"/>
+    </row>
+    <row r="215" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C215" s="4"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
@@ -11897,8 +12862,12 @@
       <c r="AQ215" s="4"/>
       <c r="AR215" s="4"/>
       <c r="AS215" s="4"/>
-    </row>
-    <row r="216" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT215" s="4"/>
+      <c r="AU215" s="4"/>
+      <c r="AV215" s="4"/>
+      <c r="AW215" s="4"/>
+    </row>
+    <row r="216" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C216" s="4"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
@@ -11942,8 +12911,12 @@
       <c r="AQ216" s="4"/>
       <c r="AR216" s="4"/>
       <c r="AS216" s="4"/>
-    </row>
-    <row r="217" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT216" s="4"/>
+      <c r="AU216" s="4"/>
+      <c r="AV216" s="4"/>
+      <c r="AW216" s="4"/>
+    </row>
+    <row r="217" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C217" s="4"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
@@ -11987,8 +12960,12 @@
       <c r="AQ217" s="4"/>
       <c r="AR217" s="4"/>
       <c r="AS217" s="4"/>
-    </row>
-    <row r="218" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT217" s="4"/>
+      <c r="AU217" s="4"/>
+      <c r="AV217" s="4"/>
+      <c r="AW217" s="4"/>
+    </row>
+    <row r="218" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C218" s="4"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
@@ -12032,8 +13009,12 @@
       <c r="AQ218" s="4"/>
       <c r="AR218" s="4"/>
       <c r="AS218" s="4"/>
-    </row>
-    <row r="219" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT218" s="4"/>
+      <c r="AU218" s="4"/>
+      <c r="AV218" s="4"/>
+      <c r="AW218" s="4"/>
+    </row>
+    <row r="219" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C219" s="4"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
@@ -12077,8 +13058,12 @@
       <c r="AQ219" s="4"/>
       <c r="AR219" s="4"/>
       <c r="AS219" s="4"/>
-    </row>
-    <row r="220" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT219" s="4"/>
+      <c r="AU219" s="4"/>
+      <c r="AV219" s="4"/>
+      <c r="AW219" s="4"/>
+    </row>
+    <row r="220" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C220" s="4"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
@@ -12122,8 +13107,12 @@
       <c r="AQ220" s="4"/>
       <c r="AR220" s="4"/>
       <c r="AS220" s="4"/>
-    </row>
-    <row r="221" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT220" s="4"/>
+      <c r="AU220" s="4"/>
+      <c r="AV220" s="4"/>
+      <c r="AW220" s="4"/>
+    </row>
+    <row r="221" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C221" s="4"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
@@ -12167,8 +13156,12 @@
       <c r="AQ221" s="4"/>
       <c r="AR221" s="4"/>
       <c r="AS221" s="4"/>
-    </row>
-    <row r="222" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT221" s="4"/>
+      <c r="AU221" s="4"/>
+      <c r="AV221" s="4"/>
+      <c r="AW221" s="4"/>
+    </row>
+    <row r="222" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C222" s="4"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
@@ -12212,8 +13205,12 @@
       <c r="AQ222" s="4"/>
       <c r="AR222" s="4"/>
       <c r="AS222" s="4"/>
-    </row>
-    <row r="223" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT222" s="4"/>
+      <c r="AU222" s="4"/>
+      <c r="AV222" s="4"/>
+      <c r="AW222" s="4"/>
+    </row>
+    <row r="223" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C223" s="4"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
@@ -12257,8 +13254,12 @@
       <c r="AQ223" s="4"/>
       <c r="AR223" s="4"/>
       <c r="AS223" s="4"/>
-    </row>
-    <row r="224" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT223" s="4"/>
+      <c r="AU223" s="4"/>
+      <c r="AV223" s="4"/>
+      <c r="AW223" s="4"/>
+    </row>
+    <row r="224" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C224" s="4"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
@@ -12302,8 +13303,12 @@
       <c r="AQ224" s="4"/>
       <c r="AR224" s="4"/>
       <c r="AS224" s="4"/>
-    </row>
-    <row r="225" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT224" s="4"/>
+      <c r="AU224" s="4"/>
+      <c r="AV224" s="4"/>
+      <c r="AW224" s="4"/>
+    </row>
+    <row r="225" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C225" s="4"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
@@ -12347,8 +13352,12 @@
       <c r="AQ225" s="4"/>
       <c r="AR225" s="4"/>
       <c r="AS225" s="4"/>
-    </row>
-    <row r="226" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT225" s="4"/>
+      <c r="AU225" s="4"/>
+      <c r="AV225" s="4"/>
+      <c r="AW225" s="4"/>
+    </row>
+    <row r="226" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C226" s="4"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
@@ -12392,8 +13401,12 @@
       <c r="AQ226" s="4"/>
       <c r="AR226" s="4"/>
       <c r="AS226" s="4"/>
-    </row>
-    <row r="227" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT226" s="4"/>
+      <c r="AU226" s="4"/>
+      <c r="AV226" s="4"/>
+      <c r="AW226" s="4"/>
+    </row>
+    <row r="227" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C227" s="4"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
@@ -12437,8 +13450,12 @@
       <c r="AQ227" s="4"/>
       <c r="AR227" s="4"/>
       <c r="AS227" s="4"/>
-    </row>
-    <row r="228" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT227" s="4"/>
+      <c r="AU227" s="4"/>
+      <c r="AV227" s="4"/>
+      <c r="AW227" s="4"/>
+    </row>
+    <row r="228" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C228" s="4"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
@@ -12482,8 +13499,12 @@
       <c r="AQ228" s="4"/>
       <c r="AR228" s="4"/>
       <c r="AS228" s="4"/>
-    </row>
-    <row r="229" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT228" s="4"/>
+      <c r="AU228" s="4"/>
+      <c r="AV228" s="4"/>
+      <c r="AW228" s="4"/>
+    </row>
+    <row r="229" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C229" s="4"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
@@ -12527,8 +13548,12 @@
       <c r="AQ229" s="4"/>
       <c r="AR229" s="4"/>
       <c r="AS229" s="4"/>
-    </row>
-    <row r="230" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT229" s="4"/>
+      <c r="AU229" s="4"/>
+      <c r="AV229" s="4"/>
+      <c r="AW229" s="4"/>
+    </row>
+    <row r="230" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C230" s="4"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
@@ -12572,8 +13597,12 @@
       <c r="AQ230" s="4"/>
       <c r="AR230" s="4"/>
       <c r="AS230" s="4"/>
-    </row>
-    <row r="231" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT230" s="4"/>
+      <c r="AU230" s="4"/>
+      <c r="AV230" s="4"/>
+      <c r="AW230" s="4"/>
+    </row>
+    <row r="231" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C231" s="4"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
@@ -12617,8 +13646,12 @@
       <c r="AQ231" s="4"/>
       <c r="AR231" s="4"/>
       <c r="AS231" s="4"/>
-    </row>
-    <row r="232" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT231" s="4"/>
+      <c r="AU231" s="4"/>
+      <c r="AV231" s="4"/>
+      <c r="AW231" s="4"/>
+    </row>
+    <row r="232" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C232" s="4"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
@@ -12662,8 +13695,12 @@
       <c r="AQ232" s="4"/>
       <c r="AR232" s="4"/>
       <c r="AS232" s="4"/>
-    </row>
-    <row r="233" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT232" s="4"/>
+      <c r="AU232" s="4"/>
+      <c r="AV232" s="4"/>
+      <c r="AW232" s="4"/>
+    </row>
+    <row r="233" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C233" s="4"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
@@ -12707,8 +13744,12 @@
       <c r="AQ233" s="4"/>
       <c r="AR233" s="4"/>
       <c r="AS233" s="4"/>
-    </row>
-    <row r="234" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT233" s="4"/>
+      <c r="AU233" s="4"/>
+      <c r="AV233" s="4"/>
+      <c r="AW233" s="4"/>
+    </row>
+    <row r="234" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C234" s="4"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
@@ -12752,8 +13793,12 @@
       <c r="AQ234" s="4"/>
       <c r="AR234" s="4"/>
       <c r="AS234" s="4"/>
-    </row>
-    <row r="235" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT234" s="4"/>
+      <c r="AU234" s="4"/>
+      <c r="AV234" s="4"/>
+      <c r="AW234" s="4"/>
+    </row>
+    <row r="235" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C235" s="4"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
@@ -12797,8 +13842,12 @@
       <c r="AQ235" s="4"/>
       <c r="AR235" s="4"/>
       <c r="AS235" s="4"/>
-    </row>
-    <row r="236" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT235" s="4"/>
+      <c r="AU235" s="4"/>
+      <c r="AV235" s="4"/>
+      <c r="AW235" s="4"/>
+    </row>
+    <row r="236" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C236" s="4"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
@@ -12842,8 +13891,12 @@
       <c r="AQ236" s="4"/>
       <c r="AR236" s="4"/>
       <c r="AS236" s="4"/>
-    </row>
-    <row r="237" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT236" s="4"/>
+      <c r="AU236" s="4"/>
+      <c r="AV236" s="4"/>
+      <c r="AW236" s="4"/>
+    </row>
+    <row r="237" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C237" s="4"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
@@ -12887,8 +13940,12 @@
       <c r="AQ237" s="4"/>
       <c r="AR237" s="4"/>
       <c r="AS237" s="4"/>
-    </row>
-    <row r="238" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT237" s="4"/>
+      <c r="AU237" s="4"/>
+      <c r="AV237" s="4"/>
+      <c r="AW237" s="4"/>
+    </row>
+    <row r="238" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C238" s="4"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
@@ -12932,8 +13989,12 @@
       <c r="AQ238" s="4"/>
       <c r="AR238" s="4"/>
       <c r="AS238" s="4"/>
-    </row>
-    <row r="239" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT238" s="4"/>
+      <c r="AU238" s="4"/>
+      <c r="AV238" s="4"/>
+      <c r="AW238" s="4"/>
+    </row>
+    <row r="239" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C239" s="4"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
@@ -12977,8 +14038,12 @@
       <c r="AQ239" s="4"/>
       <c r="AR239" s="4"/>
       <c r="AS239" s="4"/>
-    </row>
-    <row r="240" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT239" s="4"/>
+      <c r="AU239" s="4"/>
+      <c r="AV239" s="4"/>
+      <c r="AW239" s="4"/>
+    </row>
+    <row r="240" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C240" s="4"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
@@ -13022,8 +14087,12 @@
       <c r="AQ240" s="4"/>
       <c r="AR240" s="4"/>
       <c r="AS240" s="4"/>
-    </row>
-    <row r="241" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT240" s="4"/>
+      <c r="AU240" s="4"/>
+      <c r="AV240" s="4"/>
+      <c r="AW240" s="4"/>
+    </row>
+    <row r="241" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C241" s="4"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
@@ -13067,8 +14136,12 @@
       <c r="AQ241" s="4"/>
       <c r="AR241" s="4"/>
       <c r="AS241" s="4"/>
-    </row>
-    <row r="242" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT241" s="4"/>
+      <c r="AU241" s="4"/>
+      <c r="AV241" s="4"/>
+      <c r="AW241" s="4"/>
+    </row>
+    <row r="242" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C242" s="4"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
@@ -13112,8 +14185,12 @@
       <c r="AQ242" s="4"/>
       <c r="AR242" s="4"/>
       <c r="AS242" s="4"/>
-    </row>
-    <row r="243" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT242" s="4"/>
+      <c r="AU242" s="4"/>
+      <c r="AV242" s="4"/>
+      <c r="AW242" s="4"/>
+    </row>
+    <row r="243" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C243" s="4"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
@@ -13157,8 +14234,12 @@
       <c r="AQ243" s="4"/>
       <c r="AR243" s="4"/>
       <c r="AS243" s="4"/>
-    </row>
-    <row r="244" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT243" s="4"/>
+      <c r="AU243" s="4"/>
+      <c r="AV243" s="4"/>
+      <c r="AW243" s="4"/>
+    </row>
+    <row r="244" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C244" s="4"/>
       <c r="D244" s="4"/>
       <c r="E244" s="4"/>
@@ -13202,8 +14283,12 @@
       <c r="AQ244" s="4"/>
       <c r="AR244" s="4"/>
       <c r="AS244" s="4"/>
-    </row>
-    <row r="245" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT244" s="4"/>
+      <c r="AU244" s="4"/>
+      <c r="AV244" s="4"/>
+      <c r="AW244" s="4"/>
+    </row>
+    <row r="245" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C245" s="4"/>
       <c r="D245" s="4"/>
       <c r="E245" s="4"/>
@@ -13247,8 +14332,12 @@
       <c r="AQ245" s="4"/>
       <c r="AR245" s="4"/>
       <c r="AS245" s="4"/>
-    </row>
-    <row r="246" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT245" s="4"/>
+      <c r="AU245" s="4"/>
+      <c r="AV245" s="4"/>
+      <c r="AW245" s="4"/>
+    </row>
+    <row r="246" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C246" s="4"/>
       <c r="D246" s="4"/>
       <c r="E246" s="4"/>
@@ -13292,8 +14381,12 @@
       <c r="AQ246" s="4"/>
       <c r="AR246" s="4"/>
       <c r="AS246" s="4"/>
-    </row>
-    <row r="247" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT246" s="4"/>
+      <c r="AU246" s="4"/>
+      <c r="AV246" s="4"/>
+      <c r="AW246" s="4"/>
+    </row>
+    <row r="247" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C247" s="4"/>
       <c r="D247" s="4"/>
       <c r="E247" s="4"/>
@@ -13337,8 +14430,12 @@
       <c r="AQ247" s="4"/>
       <c r="AR247" s="4"/>
       <c r="AS247" s="4"/>
-    </row>
-    <row r="248" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT247" s="4"/>
+      <c r="AU247" s="4"/>
+      <c r="AV247" s="4"/>
+      <c r="AW247" s="4"/>
+    </row>
+    <row r="248" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C248" s="4"/>
       <c r="D248" s="4"/>
       <c r="E248" s="4"/>
@@ -13382,8 +14479,12 @@
       <c r="AQ248" s="4"/>
       <c r="AR248" s="4"/>
       <c r="AS248" s="4"/>
-    </row>
-    <row r="249" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT248" s="4"/>
+      <c r="AU248" s="4"/>
+      <c r="AV248" s="4"/>
+      <c r="AW248" s="4"/>
+    </row>
+    <row r="249" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C249" s="4"/>
       <c r="D249" s="4"/>
       <c r="E249" s="4"/>
@@ -13427,8 +14528,12 @@
       <c r="AQ249" s="4"/>
       <c r="AR249" s="4"/>
       <c r="AS249" s="4"/>
-    </row>
-    <row r="250" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT249" s="4"/>
+      <c r="AU249" s="4"/>
+      <c r="AV249" s="4"/>
+      <c r="AW249" s="4"/>
+    </row>
+    <row r="250" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C250" s="4"/>
       <c r="D250" s="4"/>
       <c r="E250" s="4"/>
@@ -13472,8 +14577,12 @@
       <c r="AQ250" s="4"/>
       <c r="AR250" s="4"/>
       <c r="AS250" s="4"/>
-    </row>
-    <row r="251" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT250" s="4"/>
+      <c r="AU250" s="4"/>
+      <c r="AV250" s="4"/>
+      <c r="AW250" s="4"/>
+    </row>
+    <row r="251" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C251" s="4"/>
       <c r="D251" s="4"/>
       <c r="E251" s="4"/>
@@ -13517,8 +14626,12 @@
       <c r="AQ251" s="4"/>
       <c r="AR251" s="4"/>
       <c r="AS251" s="4"/>
-    </row>
-    <row r="252" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT251" s="4"/>
+      <c r="AU251" s="4"/>
+      <c r="AV251" s="4"/>
+      <c r="AW251" s="4"/>
+    </row>
+    <row r="252" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C252" s="4"/>
       <c r="D252" s="4"/>
       <c r="E252" s="4"/>
@@ -13562,8 +14675,12 @@
       <c r="AQ252" s="4"/>
       <c r="AR252" s="4"/>
       <c r="AS252" s="4"/>
-    </row>
-    <row r="253" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT252" s="4"/>
+      <c r="AU252" s="4"/>
+      <c r="AV252" s="4"/>
+      <c r="AW252" s="4"/>
+    </row>
+    <row r="253" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C253" s="4"/>
       <c r="D253" s="4"/>
       <c r="E253" s="4"/>
@@ -13607,8 +14724,12 @@
       <c r="AQ253" s="4"/>
       <c r="AR253" s="4"/>
       <c r="AS253" s="4"/>
-    </row>
-    <row r="254" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT253" s="4"/>
+      <c r="AU253" s="4"/>
+      <c r="AV253" s="4"/>
+      <c r="AW253" s="4"/>
+    </row>
+    <row r="254" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C254" s="4"/>
       <c r="D254" s="4"/>
       <c r="E254" s="4"/>
@@ -13652,8 +14773,12 @@
       <c r="AQ254" s="4"/>
       <c r="AR254" s="4"/>
       <c r="AS254" s="4"/>
-    </row>
-    <row r="255" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT254" s="4"/>
+      <c r="AU254" s="4"/>
+      <c r="AV254" s="4"/>
+      <c r="AW254" s="4"/>
+    </row>
+    <row r="255" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C255" s="4"/>
       <c r="D255" s="4"/>
       <c r="E255" s="4"/>
@@ -13697,8 +14822,12 @@
       <c r="AQ255" s="4"/>
       <c r="AR255" s="4"/>
       <c r="AS255" s="4"/>
-    </row>
-    <row r="256" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT255" s="4"/>
+      <c r="AU255" s="4"/>
+      <c r="AV255" s="4"/>
+      <c r="AW255" s="4"/>
+    </row>
+    <row r="256" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C256" s="4"/>
       <c r="D256" s="4"/>
       <c r="E256" s="4"/>
@@ -13742,8 +14871,12 @@
       <c r="AQ256" s="4"/>
       <c r="AR256" s="4"/>
       <c r="AS256" s="4"/>
-    </row>
-    <row r="257" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT256" s="4"/>
+      <c r="AU256" s="4"/>
+      <c r="AV256" s="4"/>
+      <c r="AW256" s="4"/>
+    </row>
+    <row r="257" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C257" s="4"/>
       <c r="D257" s="4"/>
       <c r="E257" s="4"/>
@@ -13787,8 +14920,12 @@
       <c r="AQ257" s="4"/>
       <c r="AR257" s="4"/>
       <c r="AS257" s="4"/>
-    </row>
-    <row r="258" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT257" s="4"/>
+      <c r="AU257" s="4"/>
+      <c r="AV257" s="4"/>
+      <c r="AW257" s="4"/>
+    </row>
+    <row r="258" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C258" s="4"/>
       <c r="D258" s="4"/>
       <c r="E258" s="4"/>
@@ -13832,8 +14969,12 @@
       <c r="AQ258" s="4"/>
       <c r="AR258" s="4"/>
       <c r="AS258" s="4"/>
-    </row>
-    <row r="259" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT258" s="4"/>
+      <c r="AU258" s="4"/>
+      <c r="AV258" s="4"/>
+      <c r="AW258" s="4"/>
+    </row>
+    <row r="259" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C259" s="4"/>
       <c r="D259" s="4"/>
       <c r="E259" s="4"/>
@@ -13877,8 +15018,12 @@
       <c r="AQ259" s="4"/>
       <c r="AR259" s="4"/>
       <c r="AS259" s="4"/>
-    </row>
-    <row r="260" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT259" s="4"/>
+      <c r="AU259" s="4"/>
+      <c r="AV259" s="4"/>
+      <c r="AW259" s="4"/>
+    </row>
+    <row r="260" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C260" s="4"/>
       <c r="D260" s="4"/>
       <c r="E260" s="4"/>
@@ -13922,8 +15067,12 @@
       <c r="AQ260" s="4"/>
       <c r="AR260" s="4"/>
       <c r="AS260" s="4"/>
-    </row>
-    <row r="261" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT260" s="4"/>
+      <c r="AU260" s="4"/>
+      <c r="AV260" s="4"/>
+      <c r="AW260" s="4"/>
+    </row>
+    <row r="261" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C261" s="4"/>
       <c r="D261" s="4"/>
       <c r="E261" s="4"/>
@@ -13967,8 +15116,12 @@
       <c r="AQ261" s="4"/>
       <c r="AR261" s="4"/>
       <c r="AS261" s="4"/>
-    </row>
-    <row r="262" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT261" s="4"/>
+      <c r="AU261" s="4"/>
+      <c r="AV261" s="4"/>
+      <c r="AW261" s="4"/>
+    </row>
+    <row r="262" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C262" s="4"/>
       <c r="D262" s="4"/>
       <c r="E262" s="4"/>
@@ -14012,8 +15165,12 @@
       <c r="AQ262" s="4"/>
       <c r="AR262" s="4"/>
       <c r="AS262" s="4"/>
-    </row>
-    <row r="263" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT262" s="4"/>
+      <c r="AU262" s="4"/>
+      <c r="AV262" s="4"/>
+      <c r="AW262" s="4"/>
+    </row>
+    <row r="263" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C263" s="4"/>
       <c r="D263" s="4"/>
       <c r="E263" s="4"/>
@@ -14057,8 +15214,12 @@
       <c r="AQ263" s="4"/>
       <c r="AR263" s="4"/>
       <c r="AS263" s="4"/>
-    </row>
-    <row r="264" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT263" s="4"/>
+      <c r="AU263" s="4"/>
+      <c r="AV263" s="4"/>
+      <c r="AW263" s="4"/>
+    </row>
+    <row r="264" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C264" s="4"/>
       <c r="D264" s="4"/>
       <c r="E264" s="4"/>
@@ -14102,8 +15263,12 @@
       <c r="AQ264" s="4"/>
       <c r="AR264" s="4"/>
       <c r="AS264" s="4"/>
-    </row>
-    <row r="265" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT264" s="4"/>
+      <c r="AU264" s="4"/>
+      <c r="AV264" s="4"/>
+      <c r="AW264" s="4"/>
+    </row>
+    <row r="265" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C265" s="4"/>
       <c r="D265" s="4"/>
       <c r="E265" s="4"/>
@@ -14147,8 +15312,12 @@
       <c r="AQ265" s="4"/>
       <c r="AR265" s="4"/>
       <c r="AS265" s="4"/>
-    </row>
-    <row r="266" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT265" s="4"/>
+      <c r="AU265" s="4"/>
+      <c r="AV265" s="4"/>
+      <c r="AW265" s="4"/>
+    </row>
+    <row r="266" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C266" s="4"/>
       <c r="D266" s="4"/>
       <c r="E266" s="4"/>
@@ -14192,8 +15361,12 @@
       <c r="AQ266" s="4"/>
       <c r="AR266" s="4"/>
       <c r="AS266" s="4"/>
-    </row>
-    <row r="267" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT266" s="4"/>
+      <c r="AU266" s="4"/>
+      <c r="AV266" s="4"/>
+      <c r="AW266" s="4"/>
+    </row>
+    <row r="267" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C267" s="4"/>
       <c r="D267" s="4"/>
       <c r="E267" s="4"/>
@@ -14237,8 +15410,12 @@
       <c r="AQ267" s="4"/>
       <c r="AR267" s="4"/>
       <c r="AS267" s="4"/>
-    </row>
-    <row r="268" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT267" s="4"/>
+      <c r="AU267" s="4"/>
+      <c r="AV267" s="4"/>
+      <c r="AW267" s="4"/>
+    </row>
+    <row r="268" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C268" s="4"/>
       <c r="D268" s="4"/>
       <c r="E268" s="4"/>
@@ -14282,8 +15459,12 @@
       <c r="AQ268" s="4"/>
       <c r="AR268" s="4"/>
       <c r="AS268" s="4"/>
-    </row>
-    <row r="269" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT268" s="4"/>
+      <c r="AU268" s="4"/>
+      <c r="AV268" s="4"/>
+      <c r="AW268" s="4"/>
+    </row>
+    <row r="269" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C269" s="4"/>
       <c r="D269" s="4"/>
       <c r="E269" s="4"/>
@@ -14327,8 +15508,12 @@
       <c r="AQ269" s="4"/>
       <c r="AR269" s="4"/>
       <c r="AS269" s="4"/>
-    </row>
-    <row r="270" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT269" s="4"/>
+      <c r="AU269" s="4"/>
+      <c r="AV269" s="4"/>
+      <c r="AW269" s="4"/>
+    </row>
+    <row r="270" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C270" s="4"/>
       <c r="D270" s="4"/>
       <c r="E270" s="4"/>
@@ -14372,8 +15557,12 @@
       <c r="AQ270" s="4"/>
       <c r="AR270" s="4"/>
       <c r="AS270" s="4"/>
-    </row>
-    <row r="271" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT270" s="4"/>
+      <c r="AU270" s="4"/>
+      <c r="AV270" s="4"/>
+      <c r="AW270" s="4"/>
+    </row>
+    <row r="271" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C271" s="4"/>
       <c r="D271" s="4"/>
       <c r="E271" s="4"/>
@@ -14417,8 +15606,12 @@
       <c r="AQ271" s="4"/>
       <c r="AR271" s="4"/>
       <c r="AS271" s="4"/>
-    </row>
-    <row r="272" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT271" s="4"/>
+      <c r="AU271" s="4"/>
+      <c r="AV271" s="4"/>
+      <c r="AW271" s="4"/>
+    </row>
+    <row r="272" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C272" s="4"/>
       <c r="D272" s="4"/>
       <c r="E272" s="4"/>
@@ -14462,8 +15655,12 @@
       <c r="AQ272" s="4"/>
       <c r="AR272" s="4"/>
       <c r="AS272" s="4"/>
-    </row>
-    <row r="273" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT272" s="4"/>
+      <c r="AU272" s="4"/>
+      <c r="AV272" s="4"/>
+      <c r="AW272" s="4"/>
+    </row>
+    <row r="273" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C273" s="4"/>
       <c r="D273" s="4"/>
       <c r="E273" s="4"/>
@@ -14507,8 +15704,12 @@
       <c r="AQ273" s="4"/>
       <c r="AR273" s="4"/>
       <c r="AS273" s="4"/>
-    </row>
-    <row r="274" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT273" s="4"/>
+      <c r="AU273" s="4"/>
+      <c r="AV273" s="4"/>
+      <c r="AW273" s="4"/>
+    </row>
+    <row r="274" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C274" s="4"/>
       <c r="D274" s="4"/>
       <c r="E274" s="4"/>
@@ -14552,8 +15753,12 @@
       <c r="AQ274" s="4"/>
       <c r="AR274" s="4"/>
       <c r="AS274" s="4"/>
-    </row>
-    <row r="275" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT274" s="4"/>
+      <c r="AU274" s="4"/>
+      <c r="AV274" s="4"/>
+      <c r="AW274" s="4"/>
+    </row>
+    <row r="275" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C275" s="4"/>
       <c r="D275" s="4"/>
       <c r="E275" s="4"/>
@@ -14597,8 +15802,12 @@
       <c r="AQ275" s="4"/>
       <c r="AR275" s="4"/>
       <c r="AS275" s="4"/>
-    </row>
-    <row r="276" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT275" s="4"/>
+      <c r="AU275" s="4"/>
+      <c r="AV275" s="4"/>
+      <c r="AW275" s="4"/>
+    </row>
+    <row r="276" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C276" s="4"/>
       <c r="D276" s="4"/>
       <c r="E276" s="4"/>
@@ -14642,8 +15851,12 @@
       <c r="AQ276" s="4"/>
       <c r="AR276" s="4"/>
       <c r="AS276" s="4"/>
-    </row>
-    <row r="277" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT276" s="4"/>
+      <c r="AU276" s="4"/>
+      <c r="AV276" s="4"/>
+      <c r="AW276" s="4"/>
+    </row>
+    <row r="277" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C277" s="4"/>
       <c r="D277" s="4"/>
       <c r="E277" s="4"/>
@@ -14687,8 +15900,12 @@
       <c r="AQ277" s="4"/>
       <c r="AR277" s="4"/>
       <c r="AS277" s="4"/>
-    </row>
-    <row r="278" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT277" s="4"/>
+      <c r="AU277" s="4"/>
+      <c r="AV277" s="4"/>
+      <c r="AW277" s="4"/>
+    </row>
+    <row r="278" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C278" s="4"/>
       <c r="D278" s="4"/>
       <c r="E278" s="4"/>
@@ -14732,8 +15949,12 @@
       <c r="AQ278" s="4"/>
       <c r="AR278" s="4"/>
       <c r="AS278" s="4"/>
-    </row>
-    <row r="279" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT278" s="4"/>
+      <c r="AU278" s="4"/>
+      <c r="AV278" s="4"/>
+      <c r="AW278" s="4"/>
+    </row>
+    <row r="279" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C279" s="4"/>
       <c r="D279" s="4"/>
       <c r="E279" s="4"/>
@@ -14777,8 +15998,12 @@
       <c r="AQ279" s="4"/>
       <c r="AR279" s="4"/>
       <c r="AS279" s="4"/>
-    </row>
-    <row r="280" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT279" s="4"/>
+      <c r="AU279" s="4"/>
+      <c r="AV279" s="4"/>
+      <c r="AW279" s="4"/>
+    </row>
+    <row r="280" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C280" s="4"/>
       <c r="D280" s="4"/>
       <c r="E280" s="4"/>
@@ -14822,8 +16047,12 @@
       <c r="AQ280" s="4"/>
       <c r="AR280" s="4"/>
       <c r="AS280" s="4"/>
-    </row>
-    <row r="281" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT280" s="4"/>
+      <c r="AU280" s="4"/>
+      <c r="AV280" s="4"/>
+      <c r="AW280" s="4"/>
+    </row>
+    <row r="281" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C281" s="4"/>
       <c r="D281" s="4"/>
       <c r="E281" s="4"/>
@@ -14867,8 +16096,12 @@
       <c r="AQ281" s="4"/>
       <c r="AR281" s="4"/>
       <c r="AS281" s="4"/>
-    </row>
-    <row r="282" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT281" s="4"/>
+      <c r="AU281" s="4"/>
+      <c r="AV281" s="4"/>
+      <c r="AW281" s="4"/>
+    </row>
+    <row r="282" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C282" s="4"/>
       <c r="D282" s="4"/>
       <c r="E282" s="4"/>
@@ -14912,8 +16145,12 @@
       <c r="AQ282" s="4"/>
       <c r="AR282" s="4"/>
       <c r="AS282" s="4"/>
-    </row>
-    <row r="283" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT282" s="4"/>
+      <c r="AU282" s="4"/>
+      <c r="AV282" s="4"/>
+      <c r="AW282" s="4"/>
+    </row>
+    <row r="283" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C283" s="4"/>
       <c r="D283" s="4"/>
       <c r="E283" s="4"/>
@@ -14957,8 +16194,12 @@
       <c r="AQ283" s="4"/>
       <c r="AR283" s="4"/>
       <c r="AS283" s="4"/>
-    </row>
-    <row r="284" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT283" s="4"/>
+      <c r="AU283" s="4"/>
+      <c r="AV283" s="4"/>
+      <c r="AW283" s="4"/>
+    </row>
+    <row r="284" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C284" s="4"/>
       <c r="D284" s="4"/>
       <c r="E284" s="4"/>
@@ -15002,8 +16243,12 @@
       <c r="AQ284" s="4"/>
       <c r="AR284" s="4"/>
       <c r="AS284" s="4"/>
-    </row>
-    <row r="285" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT284" s="4"/>
+      <c r="AU284" s="4"/>
+      <c r="AV284" s="4"/>
+      <c r="AW284" s="4"/>
+    </row>
+    <row r="285" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C285" s="4"/>
       <c r="D285" s="4"/>
       <c r="E285" s="4"/>
@@ -15047,8 +16292,12 @@
       <c r="AQ285" s="4"/>
       <c r="AR285" s="4"/>
       <c r="AS285" s="4"/>
-    </row>
-    <row r="286" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT285" s="4"/>
+      <c r="AU285" s="4"/>
+      <c r="AV285" s="4"/>
+      <c r="AW285" s="4"/>
+    </row>
+    <row r="286" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C286" s="4"/>
       <c r="D286" s="4"/>
       <c r="E286" s="4"/>
@@ -15092,8 +16341,12 @@
       <c r="AQ286" s="4"/>
       <c r="AR286" s="4"/>
       <c r="AS286" s="4"/>
-    </row>
-    <row r="287" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT286" s="4"/>
+      <c r="AU286" s="4"/>
+      <c r="AV286" s="4"/>
+      <c r="AW286" s="4"/>
+    </row>
+    <row r="287" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C287" s="4"/>
       <c r="D287" s="4"/>
       <c r="E287" s="4"/>
@@ -15137,8 +16390,12 @@
       <c r="AQ287" s="4"/>
       <c r="AR287" s="4"/>
       <c r="AS287" s="4"/>
-    </row>
-    <row r="288" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT287" s="4"/>
+      <c r="AU287" s="4"/>
+      <c r="AV287" s="4"/>
+      <c r="AW287" s="4"/>
+    </row>
+    <row r="288" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C288" s="4"/>
       <c r="D288" s="4"/>
       <c r="E288" s="4"/>
@@ -15182,8 +16439,12 @@
       <c r="AQ288" s="4"/>
       <c r="AR288" s="4"/>
       <c r="AS288" s="4"/>
-    </row>
-    <row r="289" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT288" s="4"/>
+      <c r="AU288" s="4"/>
+      <c r="AV288" s="4"/>
+      <c r="AW288" s="4"/>
+    </row>
+    <row r="289" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C289" s="4"/>
       <c r="D289" s="4"/>
       <c r="E289" s="4"/>
@@ -15227,8 +16488,12 @@
       <c r="AQ289" s="4"/>
       <c r="AR289" s="4"/>
       <c r="AS289" s="4"/>
-    </row>
-    <row r="290" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT289" s="4"/>
+      <c r="AU289" s="4"/>
+      <c r="AV289" s="4"/>
+      <c r="AW289" s="4"/>
+    </row>
+    <row r="290" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C290" s="4"/>
       <c r="D290" s="4"/>
       <c r="E290" s="4"/>
@@ -15272,8 +16537,12 @@
       <c r="AQ290" s="4"/>
       <c r="AR290" s="4"/>
       <c r="AS290" s="4"/>
-    </row>
-    <row r="291" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT290" s="4"/>
+      <c r="AU290" s="4"/>
+      <c r="AV290" s="4"/>
+      <c r="AW290" s="4"/>
+    </row>
+    <row r="291" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C291" s="4"/>
       <c r="D291" s="4"/>
       <c r="E291" s="4"/>
@@ -15317,8 +16586,12 @@
       <c r="AQ291" s="4"/>
       <c r="AR291" s="4"/>
       <c r="AS291" s="4"/>
-    </row>
-    <row r="292" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT291" s="4"/>
+      <c r="AU291" s="4"/>
+      <c r="AV291" s="4"/>
+      <c r="AW291" s="4"/>
+    </row>
+    <row r="292" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C292" s="4"/>
       <c r="D292" s="4"/>
       <c r="E292" s="4"/>
@@ -15362,8 +16635,12 @@
       <c r="AQ292" s="4"/>
       <c r="AR292" s="4"/>
       <c r="AS292" s="4"/>
-    </row>
-    <row r="293" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT292" s="4"/>
+      <c r="AU292" s="4"/>
+      <c r="AV292" s="4"/>
+      <c r="AW292" s="4"/>
+    </row>
+    <row r="293" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C293" s="4"/>
       <c r="D293" s="4"/>
       <c r="E293" s="4"/>
@@ -15407,8 +16684,12 @@
       <c r="AQ293" s="4"/>
       <c r="AR293" s="4"/>
       <c r="AS293" s="4"/>
-    </row>
-    <row r="294" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT293" s="4"/>
+      <c r="AU293" s="4"/>
+      <c r="AV293" s="4"/>
+      <c r="AW293" s="4"/>
+    </row>
+    <row r="294" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C294" s="4"/>
       <c r="D294" s="4"/>
       <c r="E294" s="4"/>
@@ -15452,8 +16733,12 @@
       <c r="AQ294" s="4"/>
       <c r="AR294" s="4"/>
       <c r="AS294" s="4"/>
-    </row>
-    <row r="295" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT294" s="4"/>
+      <c r="AU294" s="4"/>
+      <c r="AV294" s="4"/>
+      <c r="AW294" s="4"/>
+    </row>
+    <row r="295" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C295" s="4"/>
       <c r="D295" s="4"/>
       <c r="E295" s="4"/>
@@ -15497,8 +16782,12 @@
       <c r="AQ295" s="4"/>
       <c r="AR295" s="4"/>
       <c r="AS295" s="4"/>
-    </row>
-    <row r="296" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT295" s="4"/>
+      <c r="AU295" s="4"/>
+      <c r="AV295" s="4"/>
+      <c r="AW295" s="4"/>
+    </row>
+    <row r="296" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C296" s="4"/>
       <c r="D296" s="4"/>
       <c r="E296" s="4"/>
@@ -15542,8 +16831,12 @@
       <c r="AQ296" s="4"/>
       <c r="AR296" s="4"/>
       <c r="AS296" s="4"/>
-    </row>
-    <row r="297" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT296" s="4"/>
+      <c r="AU296" s="4"/>
+      <c r="AV296" s="4"/>
+      <c r="AW296" s="4"/>
+    </row>
+    <row r="297" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C297" s="4"/>
       <c r="D297" s="4"/>
       <c r="E297" s="4"/>
@@ -15587,8 +16880,12 @@
       <c r="AQ297" s="4"/>
       <c r="AR297" s="4"/>
       <c r="AS297" s="4"/>
-    </row>
-    <row r="298" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT297" s="4"/>
+      <c r="AU297" s="4"/>
+      <c r="AV297" s="4"/>
+      <c r="AW297" s="4"/>
+    </row>
+    <row r="298" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C298" s="4"/>
       <c r="D298" s="4"/>
       <c r="E298" s="4"/>
@@ -15632,8 +16929,12 @@
       <c r="AQ298" s="4"/>
       <c r="AR298" s="4"/>
       <c r="AS298" s="4"/>
-    </row>
-    <row r="299" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT298" s="4"/>
+      <c r="AU298" s="4"/>
+      <c r="AV298" s="4"/>
+      <c r="AW298" s="4"/>
+    </row>
+    <row r="299" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C299" s="4"/>
       <c r="D299" s="4"/>
       <c r="E299" s="4"/>
@@ -15677,8 +16978,12 @@
       <c r="AQ299" s="4"/>
       <c r="AR299" s="4"/>
       <c r="AS299" s="4"/>
-    </row>
-    <row r="300" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT299" s="4"/>
+      <c r="AU299" s="4"/>
+      <c r="AV299" s="4"/>
+      <c r="AW299" s="4"/>
+    </row>
+    <row r="300" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C300" s="4"/>
       <c r="D300" s="4"/>
       <c r="E300" s="4"/>
@@ -15722,8 +17027,12 @@
       <c r="AQ300" s="4"/>
       <c r="AR300" s="4"/>
       <c r="AS300" s="4"/>
-    </row>
-    <row r="301" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT300" s="4"/>
+      <c r="AU300" s="4"/>
+      <c r="AV300" s="4"/>
+      <c r="AW300" s="4"/>
+    </row>
+    <row r="301" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C301" s="4"/>
       <c r="D301" s="4"/>
       <c r="E301" s="4"/>
@@ -15767,8 +17076,12 @@
       <c r="AQ301" s="4"/>
       <c r="AR301" s="4"/>
       <c r="AS301" s="4"/>
-    </row>
-    <row r="302" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT301" s="4"/>
+      <c r="AU301" s="4"/>
+      <c r="AV301" s="4"/>
+      <c r="AW301" s="4"/>
+    </row>
+    <row r="302" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C302" s="4"/>
       <c r="D302" s="4"/>
       <c r="E302" s="4"/>
@@ -15812,8 +17125,12 @@
       <c r="AQ302" s="4"/>
       <c r="AR302" s="4"/>
       <c r="AS302" s="4"/>
-    </row>
-    <row r="303" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT302" s="4"/>
+      <c r="AU302" s="4"/>
+      <c r="AV302" s="4"/>
+      <c r="AW302" s="4"/>
+    </row>
+    <row r="303" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C303" s="4"/>
       <c r="D303" s="4"/>
       <c r="E303" s="4"/>
@@ -15857,8 +17174,12 @@
       <c r="AQ303" s="4"/>
       <c r="AR303" s="4"/>
       <c r="AS303" s="4"/>
-    </row>
-    <row r="304" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT303" s="4"/>
+      <c r="AU303" s="4"/>
+      <c r="AV303" s="4"/>
+      <c r="AW303" s="4"/>
+    </row>
+    <row r="304" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C304" s="4"/>
       <c r="D304" s="4"/>
       <c r="E304" s="4"/>
@@ -15902,8 +17223,12 @@
       <c r="AQ304" s="4"/>
       <c r="AR304" s="4"/>
       <c r="AS304" s="4"/>
-    </row>
-    <row r="305" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT304" s="4"/>
+      <c r="AU304" s="4"/>
+      <c r="AV304" s="4"/>
+      <c r="AW304" s="4"/>
+    </row>
+    <row r="305" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C305" s="4"/>
       <c r="D305" s="4"/>
       <c r="E305" s="4"/>
@@ -15947,8 +17272,12 @@
       <c r="AQ305" s="4"/>
       <c r="AR305" s="4"/>
       <c r="AS305" s="4"/>
-    </row>
-    <row r="306" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT305" s="4"/>
+      <c r="AU305" s="4"/>
+      <c r="AV305" s="4"/>
+      <c r="AW305" s="4"/>
+    </row>
+    <row r="306" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C306" s="4"/>
       <c r="D306" s="4"/>
       <c r="E306" s="4"/>
@@ -15992,8 +17321,12 @@
       <c r="AQ306" s="4"/>
       <c r="AR306" s="4"/>
       <c r="AS306" s="4"/>
-    </row>
-    <row r="307" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT306" s="4"/>
+      <c r="AU306" s="4"/>
+      <c r="AV306" s="4"/>
+      <c r="AW306" s="4"/>
+    </row>
+    <row r="307" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C307" s="4"/>
       <c r="D307" s="4"/>
       <c r="E307" s="4"/>
@@ -16037,8 +17370,12 @@
       <c r="AQ307" s="4"/>
       <c r="AR307" s="4"/>
       <c r="AS307" s="4"/>
-    </row>
-    <row r="308" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT307" s="4"/>
+      <c r="AU307" s="4"/>
+      <c r="AV307" s="4"/>
+      <c r="AW307" s="4"/>
+    </row>
+    <row r="308" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C308" s="4"/>
       <c r="D308" s="4"/>
       <c r="E308" s="4"/>
@@ -16082,8 +17419,12 @@
       <c r="AQ308" s="4"/>
       <c r="AR308" s="4"/>
       <c r="AS308" s="4"/>
-    </row>
-    <row r="309" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT308" s="4"/>
+      <c r="AU308" s="4"/>
+      <c r="AV308" s="4"/>
+      <c r="AW308" s="4"/>
+    </row>
+    <row r="309" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C309" s="4"/>
       <c r="D309" s="4"/>
       <c r="E309" s="4"/>
@@ -16127,8 +17468,12 @@
       <c r="AQ309" s="4"/>
       <c r="AR309" s="4"/>
       <c r="AS309" s="4"/>
-    </row>
-    <row r="310" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT309" s="4"/>
+      <c r="AU309" s="4"/>
+      <c r="AV309" s="4"/>
+      <c r="AW309" s="4"/>
+    </row>
+    <row r="310" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C310" s="4"/>
       <c r="D310" s="4"/>
       <c r="E310" s="4"/>
@@ -16172,8 +17517,12 @@
       <c r="AQ310" s="4"/>
       <c r="AR310" s="4"/>
       <c r="AS310" s="4"/>
-    </row>
-    <row r="311" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT310" s="4"/>
+      <c r="AU310" s="4"/>
+      <c r="AV310" s="4"/>
+      <c r="AW310" s="4"/>
+    </row>
+    <row r="311" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C311" s="4"/>
       <c r="D311" s="4"/>
       <c r="E311" s="4"/>
@@ -16217,8 +17566,12 @@
       <c r="AQ311" s="4"/>
       <c r="AR311" s="4"/>
       <c r="AS311" s="4"/>
-    </row>
-    <row r="312" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT311" s="4"/>
+      <c r="AU311" s="4"/>
+      <c r="AV311" s="4"/>
+      <c r="AW311" s="4"/>
+    </row>
+    <row r="312" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C312" s="4"/>
       <c r="D312" s="4"/>
       <c r="E312" s="4"/>
@@ -16262,8 +17615,12 @@
       <c r="AQ312" s="4"/>
       <c r="AR312" s="4"/>
       <c r="AS312" s="4"/>
-    </row>
-    <row r="313" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT312" s="4"/>
+      <c r="AU312" s="4"/>
+      <c r="AV312" s="4"/>
+      <c r="AW312" s="4"/>
+    </row>
+    <row r="313" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C313" s="4"/>
       <c r="D313" s="4"/>
       <c r="E313" s="4"/>
@@ -16307,8 +17664,12 @@
       <c r="AQ313" s="4"/>
       <c r="AR313" s="4"/>
       <c r="AS313" s="4"/>
-    </row>
-    <row r="314" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT313" s="4"/>
+      <c r="AU313" s="4"/>
+      <c r="AV313" s="4"/>
+      <c r="AW313" s="4"/>
+    </row>
+    <row r="314" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C314" s="4"/>
       <c r="D314" s="4"/>
       <c r="E314" s="4"/>
@@ -16352,8 +17713,12 @@
       <c r="AQ314" s="4"/>
       <c r="AR314" s="4"/>
       <c r="AS314" s="4"/>
-    </row>
-    <row r="315" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT314" s="4"/>
+      <c r="AU314" s="4"/>
+      <c r="AV314" s="4"/>
+      <c r="AW314" s="4"/>
+    </row>
+    <row r="315" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C315" s="4"/>
       <c r="D315" s="4"/>
       <c r="E315" s="4"/>
@@ -16397,8 +17762,12 @@
       <c r="AQ315" s="4"/>
       <c r="AR315" s="4"/>
       <c r="AS315" s="4"/>
-    </row>
-    <row r="316" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT315" s="4"/>
+      <c r="AU315" s="4"/>
+      <c r="AV315" s="4"/>
+      <c r="AW315" s="4"/>
+    </row>
+    <row r="316" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C316" s="4"/>
       <c r="D316" s="4"/>
       <c r="E316" s="4"/>
@@ -16442,8 +17811,12 @@
       <c r="AQ316" s="4"/>
       <c r="AR316" s="4"/>
       <c r="AS316" s="4"/>
-    </row>
-    <row r="317" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT316" s="4"/>
+      <c r="AU316" s="4"/>
+      <c r="AV316" s="4"/>
+      <c r="AW316" s="4"/>
+    </row>
+    <row r="317" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C317" s="4"/>
       <c r="D317" s="4"/>
       <c r="E317" s="4"/>
@@ -16487,8 +17860,12 @@
       <c r="AQ317" s="4"/>
       <c r="AR317" s="4"/>
       <c r="AS317" s="4"/>
-    </row>
-    <row r="318" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT317" s="4"/>
+      <c r="AU317" s="4"/>
+      <c r="AV317" s="4"/>
+      <c r="AW317" s="4"/>
+    </row>
+    <row r="318" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C318" s="4"/>
       <c r="D318" s="4"/>
       <c r="E318" s="4"/>
@@ -16532,8 +17909,12 @@
       <c r="AQ318" s="4"/>
       <c r="AR318" s="4"/>
       <c r="AS318" s="4"/>
-    </row>
-    <row r="319" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT318" s="4"/>
+      <c r="AU318" s="4"/>
+      <c r="AV318" s="4"/>
+      <c r="AW318" s="4"/>
+    </row>
+    <row r="319" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C319" s="4"/>
       <c r="D319" s="4"/>
       <c r="E319" s="4"/>
@@ -16577,8 +17958,12 @@
       <c r="AQ319" s="4"/>
       <c r="AR319" s="4"/>
       <c r="AS319" s="4"/>
-    </row>
-    <row r="320" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT319" s="4"/>
+      <c r="AU319" s="4"/>
+      <c r="AV319" s="4"/>
+      <c r="AW319" s="4"/>
+    </row>
+    <row r="320" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C320" s="4"/>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
@@ -16622,8 +18007,12 @@
       <c r="AQ320" s="4"/>
       <c r="AR320" s="4"/>
       <c r="AS320" s="4"/>
-    </row>
-    <row r="321" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT320" s="4"/>
+      <c r="AU320" s="4"/>
+      <c r="AV320" s="4"/>
+      <c r="AW320" s="4"/>
+    </row>
+    <row r="321" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C321" s="4"/>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
@@ -16667,8 +18056,12 @@
       <c r="AQ321" s="4"/>
       <c r="AR321" s="4"/>
       <c r="AS321" s="4"/>
-    </row>
-    <row r="322" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT321" s="4"/>
+      <c r="AU321" s="4"/>
+      <c r="AV321" s="4"/>
+      <c r="AW321" s="4"/>
+    </row>
+    <row r="322" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C322" s="4"/>
       <c r="D322" s="4"/>
       <c r="E322" s="4"/>
@@ -16712,8 +18105,12 @@
       <c r="AQ322" s="4"/>
       <c r="AR322" s="4"/>
       <c r="AS322" s="4"/>
-    </row>
-    <row r="323" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT322" s="4"/>
+      <c r="AU322" s="4"/>
+      <c r="AV322" s="4"/>
+      <c r="AW322" s="4"/>
+    </row>
+    <row r="323" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C323" s="4"/>
       <c r="D323" s="4"/>
       <c r="E323" s="4"/>
@@ -16757,8 +18154,12 @@
       <c r="AQ323" s="4"/>
       <c r="AR323" s="4"/>
       <c r="AS323" s="4"/>
-    </row>
-    <row r="324" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT323" s="4"/>
+      <c r="AU323" s="4"/>
+      <c r="AV323" s="4"/>
+      <c r="AW323" s="4"/>
+    </row>
+    <row r="324" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C324" s="4"/>
       <c r="D324" s="4"/>
       <c r="E324" s="4"/>
@@ -16802,8 +18203,12 @@
       <c r="AQ324" s="4"/>
       <c r="AR324" s="4"/>
       <c r="AS324" s="4"/>
-    </row>
-    <row r="325" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT324" s="4"/>
+      <c r="AU324" s="4"/>
+      <c r="AV324" s="4"/>
+      <c r="AW324" s="4"/>
+    </row>
+    <row r="325" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C325" s="4"/>
       <c r="D325" s="4"/>
       <c r="E325" s="4"/>
@@ -16847,8 +18252,12 @@
       <c r="AQ325" s="4"/>
       <c r="AR325" s="4"/>
       <c r="AS325" s="4"/>
-    </row>
-    <row r="326" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT325" s="4"/>
+      <c r="AU325" s="4"/>
+      <c r="AV325" s="4"/>
+      <c r="AW325" s="4"/>
+    </row>
+    <row r="326" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C326" s="4"/>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -16892,8 +18301,12 @@
       <c r="AQ326" s="4"/>
       <c r="AR326" s="4"/>
       <c r="AS326" s="4"/>
-    </row>
-    <row r="327" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT326" s="4"/>
+      <c r="AU326" s="4"/>
+      <c r="AV326" s="4"/>
+      <c r="AW326" s="4"/>
+    </row>
+    <row r="327" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C327" s="4"/>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
@@ -16937,8 +18350,12 @@
       <c r="AQ327" s="4"/>
       <c r="AR327" s="4"/>
       <c r="AS327" s="4"/>
-    </row>
-    <row r="328" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT327" s="4"/>
+      <c r="AU327" s="4"/>
+      <c r="AV327" s="4"/>
+      <c r="AW327" s="4"/>
+    </row>
+    <row r="328" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C328" s="4"/>
       <c r="D328" s="4"/>
       <c r="E328" s="4"/>
@@ -16982,8 +18399,12 @@
       <c r="AQ328" s="4"/>
       <c r="AR328" s="4"/>
       <c r="AS328" s="4"/>
-    </row>
-    <row r="329" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT328" s="4"/>
+      <c r="AU328" s="4"/>
+      <c r="AV328" s="4"/>
+      <c r="AW328" s="4"/>
+    </row>
+    <row r="329" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C329" s="4"/>
       <c r="D329" s="4"/>
       <c r="E329" s="4"/>
@@ -17027,8 +18448,12 @@
       <c r="AQ329" s="4"/>
       <c r="AR329" s="4"/>
       <c r="AS329" s="4"/>
-    </row>
-    <row r="330" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT329" s="4"/>
+      <c r="AU329" s="4"/>
+      <c r="AV329" s="4"/>
+      <c r="AW329" s="4"/>
+    </row>
+    <row r="330" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C330" s="4"/>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
@@ -17072,8 +18497,12 @@
       <c r="AQ330" s="4"/>
       <c r="AR330" s="4"/>
       <c r="AS330" s="4"/>
-    </row>
-    <row r="331" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT330" s="4"/>
+      <c r="AU330" s="4"/>
+      <c r="AV330" s="4"/>
+      <c r="AW330" s="4"/>
+    </row>
+    <row r="331" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C331" s="4"/>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
@@ -17117,8 +18546,12 @@
       <c r="AQ331" s="4"/>
       <c r="AR331" s="4"/>
       <c r="AS331" s="4"/>
-    </row>
-    <row r="332" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT331" s="4"/>
+      <c r="AU331" s="4"/>
+      <c r="AV331" s="4"/>
+      <c r="AW331" s="4"/>
+    </row>
+    <row r="332" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C332" s="4"/>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
@@ -17162,8 +18595,12 @@
       <c r="AQ332" s="4"/>
       <c r="AR332" s="4"/>
       <c r="AS332" s="4"/>
-    </row>
-    <row r="333" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT332" s="4"/>
+      <c r="AU332" s="4"/>
+      <c r="AV332" s="4"/>
+      <c r="AW332" s="4"/>
+    </row>
+    <row r="333" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C333" s="4"/>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
@@ -17207,8 +18644,12 @@
       <c r="AQ333" s="4"/>
       <c r="AR333" s="4"/>
       <c r="AS333" s="4"/>
-    </row>
-    <row r="334" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT333" s="4"/>
+      <c r="AU333" s="4"/>
+      <c r="AV333" s="4"/>
+      <c r="AW333" s="4"/>
+    </row>
+    <row r="334" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C334" s="4"/>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
@@ -17252,8 +18693,12 @@
       <c r="AQ334" s="4"/>
       <c r="AR334" s="4"/>
       <c r="AS334" s="4"/>
-    </row>
-    <row r="335" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT334" s="4"/>
+      <c r="AU334" s="4"/>
+      <c r="AV334" s="4"/>
+      <c r="AW334" s="4"/>
+    </row>
+    <row r="335" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C335" s="4"/>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -17297,8 +18742,12 @@
       <c r="AQ335" s="4"/>
       <c r="AR335" s="4"/>
       <c r="AS335" s="4"/>
-    </row>
-    <row r="336" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT335" s="4"/>
+      <c r="AU335" s="4"/>
+      <c r="AV335" s="4"/>
+      <c r="AW335" s="4"/>
+    </row>
+    <row r="336" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C336" s="4"/>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
@@ -17342,8 +18791,12 @@
       <c r="AQ336" s="4"/>
       <c r="AR336" s="4"/>
       <c r="AS336" s="4"/>
-    </row>
-    <row r="337" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT336" s="4"/>
+      <c r="AU336" s="4"/>
+      <c r="AV336" s="4"/>
+      <c r="AW336" s="4"/>
+    </row>
+    <row r="337" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C337" s="4"/>
       <c r="D337" s="4"/>
       <c r="E337" s="4"/>
@@ -17387,8 +18840,12 @@
       <c r="AQ337" s="4"/>
       <c r="AR337" s="4"/>
       <c r="AS337" s="4"/>
-    </row>
-    <row r="338" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT337" s="4"/>
+      <c r="AU337" s="4"/>
+      <c r="AV337" s="4"/>
+      <c r="AW337" s="4"/>
+    </row>
+    <row r="338" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C338" s="4"/>
       <c r="D338" s="4"/>
       <c r="E338" s="4"/>
@@ -17432,8 +18889,12 @@
       <c r="AQ338" s="4"/>
       <c r="AR338" s="4"/>
       <c r="AS338" s="4"/>
-    </row>
-    <row r="339" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT338" s="4"/>
+      <c r="AU338" s="4"/>
+      <c r="AV338" s="4"/>
+      <c r="AW338" s="4"/>
+    </row>
+    <row r="339" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C339" s="4"/>
       <c r="D339" s="4"/>
       <c r="E339" s="4"/>
@@ -17477,8 +18938,12 @@
       <c r="AQ339" s="4"/>
       <c r="AR339" s="4"/>
       <c r="AS339" s="4"/>
-    </row>
-    <row r="340" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT339" s="4"/>
+      <c r="AU339" s="4"/>
+      <c r="AV339" s="4"/>
+      <c r="AW339" s="4"/>
+    </row>
+    <row r="340" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C340" s="4"/>
       <c r="D340" s="4"/>
       <c r="E340" s="4"/>
@@ -17522,8 +18987,12 @@
       <c r="AQ340" s="4"/>
       <c r="AR340" s="4"/>
       <c r="AS340" s="4"/>
-    </row>
-    <row r="341" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT340" s="4"/>
+      <c r="AU340" s="4"/>
+      <c r="AV340" s="4"/>
+      <c r="AW340" s="4"/>
+    </row>
+    <row r="341" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C341" s="4"/>
       <c r="D341" s="4"/>
       <c r="E341" s="4"/>
@@ -17567,8 +19036,12 @@
       <c r="AQ341" s="4"/>
       <c r="AR341" s="4"/>
       <c r="AS341" s="4"/>
-    </row>
-    <row r="342" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT341" s="4"/>
+      <c r="AU341" s="4"/>
+      <c r="AV341" s="4"/>
+      <c r="AW341" s="4"/>
+    </row>
+    <row r="342" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C342" s="4"/>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
@@ -17612,8 +19085,12 @@
       <c r="AQ342" s="4"/>
       <c r="AR342" s="4"/>
       <c r="AS342" s="4"/>
-    </row>
-    <row r="343" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT342" s="4"/>
+      <c r="AU342" s="4"/>
+      <c r="AV342" s="4"/>
+      <c r="AW342" s="4"/>
+    </row>
+    <row r="343" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C343" s="4"/>
       <c r="D343" s="4"/>
       <c r="E343" s="4"/>
@@ -17657,8 +19134,12 @@
       <c r="AQ343" s="4"/>
       <c r="AR343" s="4"/>
       <c r="AS343" s="4"/>
-    </row>
-    <row r="344" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT343" s="4"/>
+      <c r="AU343" s="4"/>
+      <c r="AV343" s="4"/>
+      <c r="AW343" s="4"/>
+    </row>
+    <row r="344" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C344" s="4"/>
       <c r="D344" s="4"/>
       <c r="E344" s="4"/>
@@ -17702,8 +19183,12 @@
       <c r="AQ344" s="4"/>
       <c r="AR344" s="4"/>
       <c r="AS344" s="4"/>
-    </row>
-    <row r="345" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT344" s="4"/>
+      <c r="AU344" s="4"/>
+      <c r="AV344" s="4"/>
+      <c r="AW344" s="4"/>
+    </row>
+    <row r="345" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C345" s="4"/>
       <c r="D345" s="4"/>
       <c r="E345" s="4"/>
@@ -17747,8 +19232,12 @@
       <c r="AQ345" s="4"/>
       <c r="AR345" s="4"/>
       <c r="AS345" s="4"/>
-    </row>
-    <row r="346" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT345" s="4"/>
+      <c r="AU345" s="4"/>
+      <c r="AV345" s="4"/>
+      <c r="AW345" s="4"/>
+    </row>
+    <row r="346" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C346" s="4"/>
       <c r="D346" s="4"/>
       <c r="E346" s="4"/>
@@ -17792,8 +19281,12 @@
       <c r="AQ346" s="4"/>
       <c r="AR346" s="4"/>
       <c r="AS346" s="4"/>
-    </row>
-    <row r="347" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT346" s="4"/>
+      <c r="AU346" s="4"/>
+      <c r="AV346" s="4"/>
+      <c r="AW346" s="4"/>
+    </row>
+    <row r="347" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C347" s="4"/>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
@@ -17837,8 +19330,12 @@
       <c r="AQ347" s="4"/>
       <c r="AR347" s="4"/>
       <c r="AS347" s="4"/>
-    </row>
-    <row r="348" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT347" s="4"/>
+      <c r="AU347" s="4"/>
+      <c r="AV347" s="4"/>
+      <c r="AW347" s="4"/>
+    </row>
+    <row r="348" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C348" s="4"/>
       <c r="D348" s="4"/>
       <c r="E348" s="4"/>
@@ -17882,8 +19379,12 @@
       <c r="AQ348" s="4"/>
       <c r="AR348" s="4"/>
       <c r="AS348" s="4"/>
-    </row>
-    <row r="349" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT348" s="4"/>
+      <c r="AU348" s="4"/>
+      <c r="AV348" s="4"/>
+      <c r="AW348" s="4"/>
+    </row>
+    <row r="349" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C349" s="4"/>
       <c r="D349" s="4"/>
       <c r="E349" s="4"/>
@@ -17927,8 +19428,12 @@
       <c r="AQ349" s="4"/>
       <c r="AR349" s="4"/>
       <c r="AS349" s="4"/>
-    </row>
-    <row r="350" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT349" s="4"/>
+      <c r="AU349" s="4"/>
+      <c r="AV349" s="4"/>
+      <c r="AW349" s="4"/>
+    </row>
+    <row r="350" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C350" s="4"/>
       <c r="D350" s="4"/>
       <c r="E350" s="4"/>
@@ -17972,8 +19477,12 @@
       <c r="AQ350" s="4"/>
       <c r="AR350" s="4"/>
       <c r="AS350" s="4"/>
-    </row>
-    <row r="351" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT350" s="4"/>
+      <c r="AU350" s="4"/>
+      <c r="AV350" s="4"/>
+      <c r="AW350" s="4"/>
+    </row>
+    <row r="351" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C351" s="4"/>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
@@ -18017,8 +19526,12 @@
       <c r="AQ351" s="4"/>
       <c r="AR351" s="4"/>
       <c r="AS351" s="4"/>
-    </row>
-    <row r="352" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT351" s="4"/>
+      <c r="AU351" s="4"/>
+      <c r="AV351" s="4"/>
+      <c r="AW351" s="4"/>
+    </row>
+    <row r="352" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C352" s="4"/>
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
@@ -18062,8 +19575,12 @@
       <c r="AQ352" s="4"/>
       <c r="AR352" s="4"/>
       <c r="AS352" s="4"/>
-    </row>
-    <row r="353" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT352" s="4"/>
+      <c r="AU352" s="4"/>
+      <c r="AV352" s="4"/>
+      <c r="AW352" s="4"/>
+    </row>
+    <row r="353" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C353" s="4"/>
       <c r="D353" s="4"/>
       <c r="E353" s="4"/>
@@ -18107,8 +19624,12 @@
       <c r="AQ353" s="4"/>
       <c r="AR353" s="4"/>
       <c r="AS353" s="4"/>
-    </row>
-    <row r="354" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT353" s="4"/>
+      <c r="AU353" s="4"/>
+      <c r="AV353" s="4"/>
+      <c r="AW353" s="4"/>
+    </row>
+    <row r="354" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C354" s="4"/>
       <c r="D354" s="4"/>
       <c r="E354" s="4"/>
@@ -18152,8 +19673,12 @@
       <c r="AQ354" s="4"/>
       <c r="AR354" s="4"/>
       <c r="AS354" s="4"/>
-    </row>
-    <row r="355" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT354" s="4"/>
+      <c r="AU354" s="4"/>
+      <c r="AV354" s="4"/>
+      <c r="AW354" s="4"/>
+    </row>
+    <row r="355" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C355" s="4"/>
       <c r="D355" s="4"/>
       <c r="E355" s="4"/>
@@ -18197,8 +19722,12 @@
       <c r="AQ355" s="4"/>
       <c r="AR355" s="4"/>
       <c r="AS355" s="4"/>
-    </row>
-    <row r="356" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT355" s="4"/>
+      <c r="AU355" s="4"/>
+      <c r="AV355" s="4"/>
+      <c r="AW355" s="4"/>
+    </row>
+    <row r="356" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C356" s="4"/>
       <c r="D356" s="4"/>
       <c r="E356" s="4"/>
@@ -18242,8 +19771,12 @@
       <c r="AQ356" s="4"/>
       <c r="AR356" s="4"/>
       <c r="AS356" s="4"/>
-    </row>
-    <row r="357" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT356" s="4"/>
+      <c r="AU356" s="4"/>
+      <c r="AV356" s="4"/>
+      <c r="AW356" s="4"/>
+    </row>
+    <row r="357" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C357" s="4"/>
       <c r="D357" s="4"/>
       <c r="E357" s="4"/>
@@ -18287,8 +19820,12 @@
       <c r="AQ357" s="4"/>
       <c r="AR357" s="4"/>
       <c r="AS357" s="4"/>
-    </row>
-    <row r="358" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT357" s="4"/>
+      <c r="AU357" s="4"/>
+      <c r="AV357" s="4"/>
+      <c r="AW357" s="4"/>
+    </row>
+    <row r="358" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C358" s="4"/>
       <c r="D358" s="4"/>
       <c r="E358" s="4"/>
@@ -18332,8 +19869,12 @@
       <c r="AQ358" s="4"/>
       <c r="AR358" s="4"/>
       <c r="AS358" s="4"/>
-    </row>
-    <row r="359" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT358" s="4"/>
+      <c r="AU358" s="4"/>
+      <c r="AV358" s="4"/>
+      <c r="AW358" s="4"/>
+    </row>
+    <row r="359" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C359" s="4"/>
       <c r="D359" s="4"/>
       <c r="E359" s="4"/>
@@ -18377,8 +19918,12 @@
       <c r="AQ359" s="4"/>
       <c r="AR359" s="4"/>
       <c r="AS359" s="4"/>
-    </row>
-    <row r="360" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT359" s="4"/>
+      <c r="AU359" s="4"/>
+      <c r="AV359" s="4"/>
+      <c r="AW359" s="4"/>
+    </row>
+    <row r="360" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C360" s="4"/>
       <c r="D360" s="4"/>
       <c r="E360" s="4"/>
@@ -18422,8 +19967,12 @@
       <c r="AQ360" s="4"/>
       <c r="AR360" s="4"/>
       <c r="AS360" s="4"/>
-    </row>
-    <row r="361" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT360" s="4"/>
+      <c r="AU360" s="4"/>
+      <c r="AV360" s="4"/>
+      <c r="AW360" s="4"/>
+    </row>
+    <row r="361" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C361" s="4"/>
       <c r="D361" s="4"/>
       <c r="E361" s="4"/>
@@ -18467,8 +20016,12 @@
       <c r="AQ361" s="4"/>
       <c r="AR361" s="4"/>
       <c r="AS361" s="4"/>
-    </row>
-    <row r="362" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT361" s="4"/>
+      <c r="AU361" s="4"/>
+      <c r="AV361" s="4"/>
+      <c r="AW361" s="4"/>
+    </row>
+    <row r="362" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C362" s="4"/>
       <c r="D362" s="4"/>
       <c r="E362" s="4"/>
@@ -18512,8 +20065,12 @@
       <c r="AQ362" s="4"/>
       <c r="AR362" s="4"/>
       <c r="AS362" s="4"/>
-    </row>
-    <row r="363" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT362" s="4"/>
+      <c r="AU362" s="4"/>
+      <c r="AV362" s="4"/>
+      <c r="AW362" s="4"/>
+    </row>
+    <row r="363" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C363" s="4"/>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
@@ -18557,8 +20114,12 @@
       <c r="AQ363" s="4"/>
       <c r="AR363" s="4"/>
       <c r="AS363" s="4"/>
-    </row>
-    <row r="364" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT363" s="4"/>
+      <c r="AU363" s="4"/>
+      <c r="AV363" s="4"/>
+      <c r="AW363" s="4"/>
+    </row>
+    <row r="364" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C364" s="4"/>
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
@@ -18602,8 +20163,12 @@
       <c r="AQ364" s="4"/>
       <c r="AR364" s="4"/>
       <c r="AS364" s="4"/>
-    </row>
-    <row r="365" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT364" s="4"/>
+      <c r="AU364" s="4"/>
+      <c r="AV364" s="4"/>
+      <c r="AW364" s="4"/>
+    </row>
+    <row r="365" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C365" s="4"/>
       <c r="D365" s="4"/>
       <c r="E365" s="4"/>
@@ -18647,8 +20212,12 @@
       <c r="AQ365" s="4"/>
       <c r="AR365" s="4"/>
       <c r="AS365" s="4"/>
-    </row>
-    <row r="366" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT365" s="4"/>
+      <c r="AU365" s="4"/>
+      <c r="AV365" s="4"/>
+      <c r="AW365" s="4"/>
+    </row>
+    <row r="366" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C366" s="4"/>
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
@@ -18692,8 +20261,12 @@
       <c r="AQ366" s="4"/>
       <c r="AR366" s="4"/>
       <c r="AS366" s="4"/>
-    </row>
-    <row r="367" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT366" s="4"/>
+      <c r="AU366" s="4"/>
+      <c r="AV366" s="4"/>
+      <c r="AW366" s="4"/>
+    </row>
+    <row r="367" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C367" s="4"/>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
@@ -18737,8 +20310,12 @@
       <c r="AQ367" s="4"/>
       <c r="AR367" s="4"/>
       <c r="AS367" s="4"/>
-    </row>
-    <row r="368" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT367" s="4"/>
+      <c r="AU367" s="4"/>
+      <c r="AV367" s="4"/>
+      <c r="AW367" s="4"/>
+    </row>
+    <row r="368" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C368" s="4"/>
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
@@ -18782,8 +20359,12 @@
       <c r="AQ368" s="4"/>
       <c r="AR368" s="4"/>
       <c r="AS368" s="4"/>
-    </row>
-    <row r="369" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT368" s="4"/>
+      <c r="AU368" s="4"/>
+      <c r="AV368" s="4"/>
+      <c r="AW368" s="4"/>
+    </row>
+    <row r="369" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C369" s="4"/>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
@@ -18827,8 +20408,12 @@
       <c r="AQ369" s="4"/>
       <c r="AR369" s="4"/>
       <c r="AS369" s="4"/>
-    </row>
-    <row r="370" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT369" s="4"/>
+      <c r="AU369" s="4"/>
+      <c r="AV369" s="4"/>
+      <c r="AW369" s="4"/>
+    </row>
+    <row r="370" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C370" s="4"/>
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
@@ -18872,8 +20457,12 @@
       <c r="AQ370" s="4"/>
       <c r="AR370" s="4"/>
       <c r="AS370" s="4"/>
-    </row>
-    <row r="371" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT370" s="4"/>
+      <c r="AU370" s="4"/>
+      <c r="AV370" s="4"/>
+      <c r="AW370" s="4"/>
+    </row>
+    <row r="371" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C371" s="4"/>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
@@ -18917,8 +20506,12 @@
       <c r="AQ371" s="4"/>
       <c r="AR371" s="4"/>
       <c r="AS371" s="4"/>
-    </row>
-    <row r="372" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT371" s="4"/>
+      <c r="AU371" s="4"/>
+      <c r="AV371" s="4"/>
+      <c r="AW371" s="4"/>
+    </row>
+    <row r="372" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C372" s="4"/>
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
@@ -18962,8 +20555,12 @@
       <c r="AQ372" s="4"/>
       <c r="AR372" s="4"/>
       <c r="AS372" s="4"/>
-    </row>
-    <row r="373" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT372" s="4"/>
+      <c r="AU372" s="4"/>
+      <c r="AV372" s="4"/>
+      <c r="AW372" s="4"/>
+    </row>
+    <row r="373" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C373" s="4"/>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
@@ -19007,8 +20604,12 @@
       <c r="AQ373" s="4"/>
       <c r="AR373" s="4"/>
       <c r="AS373" s="4"/>
-    </row>
-    <row r="374" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT373" s="4"/>
+      <c r="AU373" s="4"/>
+      <c r="AV373" s="4"/>
+      <c r="AW373" s="4"/>
+    </row>
+    <row r="374" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C374" s="4"/>
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
@@ -19052,8 +20653,12 @@
       <c r="AQ374" s="4"/>
       <c r="AR374" s="4"/>
       <c r="AS374" s="4"/>
-    </row>
-    <row r="375" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT374" s="4"/>
+      <c r="AU374" s="4"/>
+      <c r="AV374" s="4"/>
+      <c r="AW374" s="4"/>
+    </row>
+    <row r="375" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C375" s="4"/>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
@@ -19097,8 +20702,12 @@
       <c r="AQ375" s="4"/>
       <c r="AR375" s="4"/>
       <c r="AS375" s="4"/>
-    </row>
-    <row r="376" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT375" s="4"/>
+      <c r="AU375" s="4"/>
+      <c r="AV375" s="4"/>
+      <c r="AW375" s="4"/>
+    </row>
+    <row r="376" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C376" s="4"/>
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
@@ -19142,8 +20751,12 @@
       <c r="AQ376" s="4"/>
       <c r="AR376" s="4"/>
       <c r="AS376" s="4"/>
-    </row>
-    <row r="377" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT376" s="4"/>
+      <c r="AU376" s="4"/>
+      <c r="AV376" s="4"/>
+      <c r="AW376" s="4"/>
+    </row>
+    <row r="377" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C377" s="4"/>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -19187,8 +20800,12 @@
       <c r="AQ377" s="4"/>
       <c r="AR377" s="4"/>
       <c r="AS377" s="4"/>
-    </row>
-    <row r="378" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT377" s="4"/>
+      <c r="AU377" s="4"/>
+      <c r="AV377" s="4"/>
+      <c r="AW377" s="4"/>
+    </row>
+    <row r="378" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C378" s="4"/>
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
@@ -19232,8 +20849,12 @@
       <c r="AQ378" s="4"/>
       <c r="AR378" s="4"/>
       <c r="AS378" s="4"/>
-    </row>
-    <row r="379" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT378" s="4"/>
+      <c r="AU378" s="4"/>
+      <c r="AV378" s="4"/>
+      <c r="AW378" s="4"/>
+    </row>
+    <row r="379" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C379" s="4"/>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
@@ -19277,8 +20898,12 @@
       <c r="AQ379" s="4"/>
       <c r="AR379" s="4"/>
       <c r="AS379" s="4"/>
-    </row>
-    <row r="380" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT379" s="4"/>
+      <c r="AU379" s="4"/>
+      <c r="AV379" s="4"/>
+      <c r="AW379" s="4"/>
+    </row>
+    <row r="380" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C380" s="4"/>
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
@@ -19322,8 +20947,12 @@
       <c r="AQ380" s="4"/>
       <c r="AR380" s="4"/>
       <c r="AS380" s="4"/>
-    </row>
-    <row r="381" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT380" s="4"/>
+      <c r="AU380" s="4"/>
+      <c r="AV380" s="4"/>
+      <c r="AW380" s="4"/>
+    </row>
+    <row r="381" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C381" s="4"/>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
@@ -19367,8 +20996,12 @@
       <c r="AQ381" s="4"/>
       <c r="AR381" s="4"/>
       <c r="AS381" s="4"/>
-    </row>
-    <row r="382" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT381" s="4"/>
+      <c r="AU381" s="4"/>
+      <c r="AV381" s="4"/>
+      <c r="AW381" s="4"/>
+    </row>
+    <row r="382" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C382" s="4"/>
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
@@ -19412,8 +21045,12 @@
       <c r="AQ382" s="4"/>
       <c r="AR382" s="4"/>
       <c r="AS382" s="4"/>
-    </row>
-    <row r="383" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT382" s="4"/>
+      <c r="AU382" s="4"/>
+      <c r="AV382" s="4"/>
+      <c r="AW382" s="4"/>
+    </row>
+    <row r="383" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C383" s="4"/>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
@@ -19457,8 +21094,12 @@
       <c r="AQ383" s="4"/>
       <c r="AR383" s="4"/>
       <c r="AS383" s="4"/>
-    </row>
-    <row r="384" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT383" s="4"/>
+      <c r="AU383" s="4"/>
+      <c r="AV383" s="4"/>
+      <c r="AW383" s="4"/>
+    </row>
+    <row r="384" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C384" s="4"/>
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
@@ -19502,8 +21143,12 @@
       <c r="AQ384" s="4"/>
       <c r="AR384" s="4"/>
       <c r="AS384" s="4"/>
-    </row>
-    <row r="385" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT384" s="4"/>
+      <c r="AU384" s="4"/>
+      <c r="AV384" s="4"/>
+      <c r="AW384" s="4"/>
+    </row>
+    <row r="385" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C385" s="4"/>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
@@ -19547,8 +21192,12 @@
       <c r="AQ385" s="4"/>
       <c r="AR385" s="4"/>
       <c r="AS385" s="4"/>
-    </row>
-    <row r="386" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT385" s="4"/>
+      <c r="AU385" s="4"/>
+      <c r="AV385" s="4"/>
+      <c r="AW385" s="4"/>
+    </row>
+    <row r="386" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C386" s="4"/>
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
@@ -19592,8 +21241,12 @@
       <c r="AQ386" s="4"/>
       <c r="AR386" s="4"/>
       <c r="AS386" s="4"/>
-    </row>
-    <row r="387" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT386" s="4"/>
+      <c r="AU386" s="4"/>
+      <c r="AV386" s="4"/>
+      <c r="AW386" s="4"/>
+    </row>
+    <row r="387" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C387" s="4"/>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
@@ -19637,8 +21290,12 @@
       <c r="AQ387" s="4"/>
       <c r="AR387" s="4"/>
       <c r="AS387" s="4"/>
-    </row>
-    <row r="388" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT387" s="4"/>
+      <c r="AU387" s="4"/>
+      <c r="AV387" s="4"/>
+      <c r="AW387" s="4"/>
+    </row>
+    <row r="388" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C388" s="4"/>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
@@ -19682,8 +21339,12 @@
       <c r="AQ388" s="4"/>
       <c r="AR388" s="4"/>
       <c r="AS388" s="4"/>
-    </row>
-    <row r="389" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT388" s="4"/>
+      <c r="AU388" s="4"/>
+      <c r="AV388" s="4"/>
+      <c r="AW388" s="4"/>
+    </row>
+    <row r="389" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C389" s="4"/>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
@@ -19727,8 +21388,12 @@
       <c r="AQ389" s="4"/>
       <c r="AR389" s="4"/>
       <c r="AS389" s="4"/>
-    </row>
-    <row r="390" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT389" s="4"/>
+      <c r="AU389" s="4"/>
+      <c r="AV389" s="4"/>
+      <c r="AW389" s="4"/>
+    </row>
+    <row r="390" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C390" s="4"/>
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
@@ -19772,8 +21437,12 @@
       <c r="AQ390" s="4"/>
       <c r="AR390" s="4"/>
       <c r="AS390" s="4"/>
-    </row>
-    <row r="391" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT390" s="4"/>
+      <c r="AU390" s="4"/>
+      <c r="AV390" s="4"/>
+      <c r="AW390" s="4"/>
+    </row>
+    <row r="391" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C391" s="4"/>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
@@ -19817,8 +21486,12 @@
       <c r="AQ391" s="4"/>
       <c r="AR391" s="4"/>
       <c r="AS391" s="4"/>
-    </row>
-    <row r="392" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT391" s="4"/>
+      <c r="AU391" s="4"/>
+      <c r="AV391" s="4"/>
+      <c r="AW391" s="4"/>
+    </row>
+    <row r="392" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C392" s="4"/>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -19862,8 +21535,12 @@
       <c r="AQ392" s="4"/>
       <c r="AR392" s="4"/>
       <c r="AS392" s="4"/>
-    </row>
-    <row r="393" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT392" s="4"/>
+      <c r="AU392" s="4"/>
+      <c r="AV392" s="4"/>
+      <c r="AW392" s="4"/>
+    </row>
+    <row r="393" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C393" s="4"/>
       <c r="D393" s="4"/>
       <c r="E393" s="4"/>
@@ -19907,8 +21584,12 @@
       <c r="AQ393" s="4"/>
       <c r="AR393" s="4"/>
       <c r="AS393" s="4"/>
-    </row>
-    <row r="394" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT393" s="4"/>
+      <c r="AU393" s="4"/>
+      <c r="AV393" s="4"/>
+      <c r="AW393" s="4"/>
+    </row>
+    <row r="394" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C394" s="4"/>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -19952,8 +21633,12 @@
       <c r="AQ394" s="4"/>
       <c r="AR394" s="4"/>
       <c r="AS394" s="4"/>
-    </row>
-    <row r="395" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT394" s="4"/>
+      <c r="AU394" s="4"/>
+      <c r="AV394" s="4"/>
+      <c r="AW394" s="4"/>
+    </row>
+    <row r="395" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C395" s="4"/>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -19997,8 +21682,12 @@
       <c r="AQ395" s="4"/>
       <c r="AR395" s="4"/>
       <c r="AS395" s="4"/>
-    </row>
-    <row r="396" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT395" s="4"/>
+      <c r="AU395" s="4"/>
+      <c r="AV395" s="4"/>
+      <c r="AW395" s="4"/>
+    </row>
+    <row r="396" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C396" s="4"/>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -20042,8 +21731,12 @@
       <c r="AQ396" s="4"/>
       <c r="AR396" s="4"/>
       <c r="AS396" s="4"/>
-    </row>
-    <row r="397" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT396" s="4"/>
+      <c r="AU396" s="4"/>
+      <c r="AV396" s="4"/>
+      <c r="AW396" s="4"/>
+    </row>
+    <row r="397" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C397" s="4"/>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -20087,8 +21780,12 @@
       <c r="AQ397" s="4"/>
       <c r="AR397" s="4"/>
       <c r="AS397" s="4"/>
-    </row>
-    <row r="398" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT397" s="4"/>
+      <c r="AU397" s="4"/>
+      <c r="AV397" s="4"/>
+      <c r="AW397" s="4"/>
+    </row>
+    <row r="398" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C398" s="4"/>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -20132,8 +21829,12 @@
       <c r="AQ398" s="4"/>
       <c r="AR398" s="4"/>
       <c r="AS398" s="4"/>
-    </row>
-    <row r="399" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT398" s="4"/>
+      <c r="AU398" s="4"/>
+      <c r="AV398" s="4"/>
+      <c r="AW398" s="4"/>
+    </row>
+    <row r="399" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C399" s="4"/>
       <c r="D399" s="4"/>
       <c r="E399" s="4"/>
@@ -20177,8 +21878,12 @@
       <c r="AQ399" s="4"/>
       <c r="AR399" s="4"/>
       <c r="AS399" s="4"/>
-    </row>
-    <row r="400" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT399" s="4"/>
+      <c r="AU399" s="4"/>
+      <c r="AV399" s="4"/>
+      <c r="AW399" s="4"/>
+    </row>
+    <row r="400" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C400" s="4"/>
       <c r="D400" s="4"/>
       <c r="E400" s="4"/>
@@ -20222,8 +21927,12 @@
       <c r="AQ400" s="4"/>
       <c r="AR400" s="4"/>
       <c r="AS400" s="4"/>
-    </row>
-    <row r="401" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT400" s="4"/>
+      <c r="AU400" s="4"/>
+      <c r="AV400" s="4"/>
+      <c r="AW400" s="4"/>
+    </row>
+    <row r="401" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C401" s="4"/>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
@@ -20267,8 +21976,12 @@
       <c r="AQ401" s="4"/>
       <c r="AR401" s="4"/>
       <c r="AS401" s="4"/>
-    </row>
-    <row r="402" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT401" s="4"/>
+      <c r="AU401" s="4"/>
+      <c r="AV401" s="4"/>
+      <c r="AW401" s="4"/>
+    </row>
+    <row r="402" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C402" s="4"/>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
@@ -20312,8 +22025,12 @@
       <c r="AQ402" s="4"/>
       <c r="AR402" s="4"/>
       <c r="AS402" s="4"/>
-    </row>
-    <row r="403" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT402" s="4"/>
+      <c r="AU402" s="4"/>
+      <c r="AV402" s="4"/>
+      <c r="AW402" s="4"/>
+    </row>
+    <row r="403" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C403" s="4"/>
       <c r="D403" s="4"/>
       <c r="E403" s="4"/>
@@ -20357,8 +22074,12 @@
       <c r="AQ403" s="4"/>
       <c r="AR403" s="4"/>
       <c r="AS403" s="4"/>
-    </row>
-    <row r="404" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT403" s="4"/>
+      <c r="AU403" s="4"/>
+      <c r="AV403" s="4"/>
+      <c r="AW403" s="4"/>
+    </row>
+    <row r="404" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C404" s="4"/>
       <c r="D404" s="4"/>
       <c r="E404" s="4"/>
@@ -20402,8 +22123,12 @@
       <c r="AQ404" s="4"/>
       <c r="AR404" s="4"/>
       <c r="AS404" s="4"/>
-    </row>
-    <row r="405" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT404" s="4"/>
+      <c r="AU404" s="4"/>
+      <c r="AV404" s="4"/>
+      <c r="AW404" s="4"/>
+    </row>
+    <row r="405" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C405" s="4"/>
       <c r="D405" s="4"/>
       <c r="E405" s="4"/>
@@ -20447,8 +22172,12 @@
       <c r="AQ405" s="4"/>
       <c r="AR405" s="4"/>
       <c r="AS405" s="4"/>
-    </row>
-    <row r="406" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT405" s="4"/>
+      <c r="AU405" s="4"/>
+      <c r="AV405" s="4"/>
+      <c r="AW405" s="4"/>
+    </row>
+    <row r="406" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C406" s="4"/>
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
@@ -20492,8 +22221,12 @@
       <c r="AQ406" s="4"/>
       <c r="AR406" s="4"/>
       <c r="AS406" s="4"/>
-    </row>
-    <row r="407" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT406" s="4"/>
+      <c r="AU406" s="4"/>
+      <c r="AV406" s="4"/>
+      <c r="AW406" s="4"/>
+    </row>
+    <row r="407" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C407" s="4"/>
       <c r="D407" s="4"/>
       <c r="E407" s="4"/>
@@ -20537,8 +22270,12 @@
       <c r="AQ407" s="4"/>
       <c r="AR407" s="4"/>
       <c r="AS407" s="4"/>
-    </row>
-    <row r="408" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT407" s="4"/>
+      <c r="AU407" s="4"/>
+      <c r="AV407" s="4"/>
+      <c r="AW407" s="4"/>
+    </row>
+    <row r="408" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C408" s="4"/>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
@@ -20582,8 +22319,12 @@
       <c r="AQ408" s="4"/>
       <c r="AR408" s="4"/>
       <c r="AS408" s="4"/>
-    </row>
-    <row r="409" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT408" s="4"/>
+      <c r="AU408" s="4"/>
+      <c r="AV408" s="4"/>
+      <c r="AW408" s="4"/>
+    </row>
+    <row r="409" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C409" s="4"/>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
@@ -20627,8 +22368,12 @@
       <c r="AQ409" s="4"/>
       <c r="AR409" s="4"/>
       <c r="AS409" s="4"/>
-    </row>
-    <row r="410" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT409" s="4"/>
+      <c r="AU409" s="4"/>
+      <c r="AV409" s="4"/>
+      <c r="AW409" s="4"/>
+    </row>
+    <row r="410" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C410" s="4"/>
       <c r="D410" s="4"/>
       <c r="E410" s="4"/>
@@ -20672,8 +22417,12 @@
       <c r="AQ410" s="4"/>
       <c r="AR410" s="4"/>
       <c r="AS410" s="4"/>
-    </row>
-    <row r="411" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT410" s="4"/>
+      <c r="AU410" s="4"/>
+      <c r="AV410" s="4"/>
+      <c r="AW410" s="4"/>
+    </row>
+    <row r="411" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C411" s="4"/>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
@@ -20717,8 +22466,12 @@
       <c r="AQ411" s="4"/>
       <c r="AR411" s="4"/>
       <c r="AS411" s="4"/>
-    </row>
-    <row r="412" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT411" s="4"/>
+      <c r="AU411" s="4"/>
+      <c r="AV411" s="4"/>
+      <c r="AW411" s="4"/>
+    </row>
+    <row r="412" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C412" s="4"/>
       <c r="D412" s="4"/>
       <c r="E412" s="4"/>
@@ -20762,8 +22515,12 @@
       <c r="AQ412" s="4"/>
       <c r="AR412" s="4"/>
       <c r="AS412" s="4"/>
-    </row>
-    <row r="413" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT412" s="4"/>
+      <c r="AU412" s="4"/>
+      <c r="AV412" s="4"/>
+      <c r="AW412" s="4"/>
+    </row>
+    <row r="413" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C413" s="4"/>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
@@ -20807,8 +22564,12 @@
       <c r="AQ413" s="4"/>
       <c r="AR413" s="4"/>
       <c r="AS413" s="4"/>
-    </row>
-    <row r="414" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT413" s="4"/>
+      <c r="AU413" s="4"/>
+      <c r="AV413" s="4"/>
+      <c r="AW413" s="4"/>
+    </row>
+    <row r="414" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C414" s="4"/>
       <c r="D414" s="4"/>
       <c r="E414" s="4"/>
@@ -20852,8 +22613,12 @@
       <c r="AQ414" s="4"/>
       <c r="AR414" s="4"/>
       <c r="AS414" s="4"/>
-    </row>
-    <row r="415" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT414" s="4"/>
+      <c r="AU414" s="4"/>
+      <c r="AV414" s="4"/>
+      <c r="AW414" s="4"/>
+    </row>
+    <row r="415" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C415" s="4"/>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
@@ -20897,8 +22662,12 @@
       <c r="AQ415" s="4"/>
       <c r="AR415" s="4"/>
       <c r="AS415" s="4"/>
-    </row>
-    <row r="416" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT415" s="4"/>
+      <c r="AU415" s="4"/>
+      <c r="AV415" s="4"/>
+      <c r="AW415" s="4"/>
+    </row>
+    <row r="416" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C416" s="4"/>
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
@@ -20942,8 +22711,12 @@
       <c r="AQ416" s="4"/>
       <c r="AR416" s="4"/>
       <c r="AS416" s="4"/>
-    </row>
-    <row r="417" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT416" s="4"/>
+      <c r="AU416" s="4"/>
+      <c r="AV416" s="4"/>
+      <c r="AW416" s="4"/>
+    </row>
+    <row r="417" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C417" s="4"/>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
@@ -20987,8 +22760,12 @@
       <c r="AQ417" s="4"/>
       <c r="AR417" s="4"/>
       <c r="AS417" s="4"/>
-    </row>
-    <row r="418" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT417" s="4"/>
+      <c r="AU417" s="4"/>
+      <c r="AV417" s="4"/>
+      <c r="AW417" s="4"/>
+    </row>
+    <row r="418" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C418" s="4"/>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
@@ -21032,8 +22809,12 @@
       <c r="AQ418" s="4"/>
       <c r="AR418" s="4"/>
       <c r="AS418" s="4"/>
-    </row>
-    <row r="419" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT418" s="4"/>
+      <c r="AU418" s="4"/>
+      <c r="AV418" s="4"/>
+      <c r="AW418" s="4"/>
+    </row>
+    <row r="419" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C419" s="4"/>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
@@ -21077,8 +22858,12 @@
       <c r="AQ419" s="4"/>
       <c r="AR419" s="4"/>
       <c r="AS419" s="4"/>
-    </row>
-    <row r="420" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT419" s="4"/>
+      <c r="AU419" s="4"/>
+      <c r="AV419" s="4"/>
+      <c r="AW419" s="4"/>
+    </row>
+    <row r="420" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C420" s="4"/>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
@@ -21122,8 +22907,12 @@
       <c r="AQ420" s="4"/>
       <c r="AR420" s="4"/>
       <c r="AS420" s="4"/>
-    </row>
-    <row r="421" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT420" s="4"/>
+      <c r="AU420" s="4"/>
+      <c r="AV420" s="4"/>
+      <c r="AW420" s="4"/>
+    </row>
+    <row r="421" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C421" s="4"/>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
@@ -21167,8 +22956,12 @@
       <c r="AQ421" s="4"/>
       <c r="AR421" s="4"/>
       <c r="AS421" s="4"/>
-    </row>
-    <row r="422" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT421" s="4"/>
+      <c r="AU421" s="4"/>
+      <c r="AV421" s="4"/>
+      <c r="AW421" s="4"/>
+    </row>
+    <row r="422" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C422" s="4"/>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
@@ -21212,8 +23005,12 @@
       <c r="AQ422" s="4"/>
       <c r="AR422" s="4"/>
       <c r="AS422" s="4"/>
-    </row>
-    <row r="423" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT422" s="4"/>
+      <c r="AU422" s="4"/>
+      <c r="AV422" s="4"/>
+      <c r="AW422" s="4"/>
+    </row>
+    <row r="423" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C423" s="4"/>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
@@ -21257,8 +23054,12 @@
       <c r="AQ423" s="4"/>
       <c r="AR423" s="4"/>
       <c r="AS423" s="4"/>
-    </row>
-    <row r="424" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT423" s="4"/>
+      <c r="AU423" s="4"/>
+      <c r="AV423" s="4"/>
+      <c r="AW423" s="4"/>
+    </row>
+    <row r="424" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C424" s="4"/>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -21302,8 +23103,12 @@
       <c r="AQ424" s="4"/>
       <c r="AR424" s="4"/>
       <c r="AS424" s="4"/>
-    </row>
-    <row r="425" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT424" s="4"/>
+      <c r="AU424" s="4"/>
+      <c r="AV424" s="4"/>
+      <c r="AW424" s="4"/>
+    </row>
+    <row r="425" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C425" s="4"/>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
@@ -21347,8 +23152,12 @@
       <c r="AQ425" s="4"/>
       <c r="AR425" s="4"/>
       <c r="AS425" s="4"/>
-    </row>
-    <row r="426" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT425" s="4"/>
+      <c r="AU425" s="4"/>
+      <c r="AV425" s="4"/>
+      <c r="AW425" s="4"/>
+    </row>
+    <row r="426" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C426" s="4"/>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
@@ -21392,8 +23201,12 @@
       <c r="AQ426" s="4"/>
       <c r="AR426" s="4"/>
       <c r="AS426" s="4"/>
-    </row>
-    <row r="427" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT426" s="4"/>
+      <c r="AU426" s="4"/>
+      <c r="AV426" s="4"/>
+      <c r="AW426" s="4"/>
+    </row>
+    <row r="427" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C427" s="4"/>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
@@ -21437,8 +23250,12 @@
       <c r="AQ427" s="4"/>
       <c r="AR427" s="4"/>
       <c r="AS427" s="4"/>
-    </row>
-    <row r="428" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT427" s="4"/>
+      <c r="AU427" s="4"/>
+      <c r="AV427" s="4"/>
+      <c r="AW427" s="4"/>
+    </row>
+    <row r="428" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C428" s="4"/>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
@@ -21482,8 +23299,12 @@
       <c r="AQ428" s="4"/>
       <c r="AR428" s="4"/>
       <c r="AS428" s="4"/>
-    </row>
-    <row r="429" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT428" s="4"/>
+      <c r="AU428" s="4"/>
+      <c r="AV428" s="4"/>
+      <c r="AW428" s="4"/>
+    </row>
+    <row r="429" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C429" s="4"/>
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
@@ -21527,8 +23348,12 @@
       <c r="AQ429" s="4"/>
       <c r="AR429" s="4"/>
       <c r="AS429" s="4"/>
-    </row>
-    <row r="430" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT429" s="4"/>
+      <c r="AU429" s="4"/>
+      <c r="AV429" s="4"/>
+      <c r="AW429" s="4"/>
+    </row>
+    <row r="430" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C430" s="4"/>
       <c r="D430" s="4"/>
       <c r="E430" s="4"/>
@@ -21572,8 +23397,12 @@
       <c r="AQ430" s="4"/>
       <c r="AR430" s="4"/>
       <c r="AS430" s="4"/>
-    </row>
-    <row r="431" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT430" s="4"/>
+      <c r="AU430" s="4"/>
+      <c r="AV430" s="4"/>
+      <c r="AW430" s="4"/>
+    </row>
+    <row r="431" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C431" s="4"/>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -21617,8 +23446,12 @@
       <c r="AQ431" s="4"/>
       <c r="AR431" s="4"/>
       <c r="AS431" s="4"/>
-    </row>
-    <row r="432" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT431" s="4"/>
+      <c r="AU431" s="4"/>
+      <c r="AV431" s="4"/>
+      <c r="AW431" s="4"/>
+    </row>
+    <row r="432" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C432" s="4"/>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -21662,8 +23495,12 @@
       <c r="AQ432" s="4"/>
       <c r="AR432" s="4"/>
       <c r="AS432" s="4"/>
-    </row>
-    <row r="433" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT432" s="4"/>
+      <c r="AU432" s="4"/>
+      <c r="AV432" s="4"/>
+      <c r="AW432" s="4"/>
+    </row>
+    <row r="433" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C433" s="4"/>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -21707,8 +23544,12 @@
       <c r="AQ433" s="4"/>
       <c r="AR433" s="4"/>
       <c r="AS433" s="4"/>
-    </row>
-    <row r="434" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT433" s="4"/>
+      <c r="AU433" s="4"/>
+      <c r="AV433" s="4"/>
+      <c r="AW433" s="4"/>
+    </row>
+    <row r="434" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C434" s="4"/>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
@@ -21752,8 +23593,12 @@
       <c r="AQ434" s="4"/>
       <c r="AR434" s="4"/>
       <c r="AS434" s="4"/>
-    </row>
-    <row r="435" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT434" s="4"/>
+      <c r="AU434" s="4"/>
+      <c r="AV434" s="4"/>
+      <c r="AW434" s="4"/>
+    </row>
+    <row r="435" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C435" s="4"/>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -21797,8 +23642,12 @@
       <c r="AQ435" s="4"/>
       <c r="AR435" s="4"/>
       <c r="AS435" s="4"/>
-    </row>
-    <row r="436" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT435" s="4"/>
+      <c r="AU435" s="4"/>
+      <c r="AV435" s="4"/>
+      <c r="AW435" s="4"/>
+    </row>
+    <row r="436" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C436" s="4"/>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -21842,8 +23691,12 @@
       <c r="AQ436" s="4"/>
       <c r="AR436" s="4"/>
       <c r="AS436" s="4"/>
-    </row>
-    <row r="437" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT436" s="4"/>
+      <c r="AU436" s="4"/>
+      <c r="AV436" s="4"/>
+      <c r="AW436" s="4"/>
+    </row>
+    <row r="437" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C437" s="4"/>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -21887,8 +23740,12 @@
       <c r="AQ437" s="4"/>
       <c r="AR437" s="4"/>
       <c r="AS437" s="4"/>
-    </row>
-    <row r="438" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT437" s="4"/>
+      <c r="AU437" s="4"/>
+      <c r="AV437" s="4"/>
+      <c r="AW437" s="4"/>
+    </row>
+    <row r="438" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C438" s="4"/>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
@@ -21932,8 +23789,12 @@
       <c r="AQ438" s="4"/>
       <c r="AR438" s="4"/>
       <c r="AS438" s="4"/>
-    </row>
-    <row r="439" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT438" s="4"/>
+      <c r="AU438" s="4"/>
+      <c r="AV438" s="4"/>
+      <c r="AW438" s="4"/>
+    </row>
+    <row r="439" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C439" s="4"/>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
@@ -21977,8 +23838,12 @@
       <c r="AQ439" s="4"/>
       <c r="AR439" s="4"/>
       <c r="AS439" s="4"/>
-    </row>
-    <row r="440" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT439" s="4"/>
+      <c r="AU439" s="4"/>
+      <c r="AV439" s="4"/>
+      <c r="AW439" s="4"/>
+    </row>
+    <row r="440" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C440" s="4"/>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
@@ -22022,8 +23887,12 @@
       <c r="AQ440" s="4"/>
       <c r="AR440" s="4"/>
       <c r="AS440" s="4"/>
-    </row>
-    <row r="441" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT440" s="4"/>
+      <c r="AU440" s="4"/>
+      <c r="AV440" s="4"/>
+      <c r="AW440" s="4"/>
+    </row>
+    <row r="441" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C441" s="4"/>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
@@ -22067,8 +23936,12 @@
       <c r="AQ441" s="4"/>
       <c r="AR441" s="4"/>
       <c r="AS441" s="4"/>
-    </row>
-    <row r="442" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT441" s="4"/>
+      <c r="AU441" s="4"/>
+      <c r="AV441" s="4"/>
+      <c r="AW441" s="4"/>
+    </row>
+    <row r="442" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C442" s="4"/>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
@@ -22112,8 +23985,12 @@
       <c r="AQ442" s="4"/>
       <c r="AR442" s="4"/>
       <c r="AS442" s="4"/>
-    </row>
-    <row r="443" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT442" s="4"/>
+      <c r="AU442" s="4"/>
+      <c r="AV442" s="4"/>
+      <c r="AW442" s="4"/>
+    </row>
+    <row r="443" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C443" s="4"/>
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
@@ -22157,8 +24034,12 @@
       <c r="AQ443" s="4"/>
       <c r="AR443" s="4"/>
       <c r="AS443" s="4"/>
-    </row>
-    <row r="444" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT443" s="4"/>
+      <c r="AU443" s="4"/>
+      <c r="AV443" s="4"/>
+      <c r="AW443" s="4"/>
+    </row>
+    <row r="444" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C444" s="4"/>
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
@@ -22202,8 +24083,12 @@
       <c r="AQ444" s="4"/>
       <c r="AR444" s="4"/>
       <c r="AS444" s="4"/>
-    </row>
-    <row r="445" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT444" s="4"/>
+      <c r="AU444" s="4"/>
+      <c r="AV444" s="4"/>
+      <c r="AW444" s="4"/>
+    </row>
+    <row r="445" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C445" s="4"/>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
@@ -22247,8 +24132,12 @@
       <c r="AQ445" s="4"/>
       <c r="AR445" s="4"/>
       <c r="AS445" s="4"/>
-    </row>
-    <row r="446" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT445" s="4"/>
+      <c r="AU445" s="4"/>
+      <c r="AV445" s="4"/>
+      <c r="AW445" s="4"/>
+    </row>
+    <row r="446" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C446" s="4"/>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
@@ -22292,8 +24181,12 @@
       <c r="AQ446" s="4"/>
       <c r="AR446" s="4"/>
       <c r="AS446" s="4"/>
-    </row>
-    <row r="447" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT446" s="4"/>
+      <c r="AU446" s="4"/>
+      <c r="AV446" s="4"/>
+      <c r="AW446" s="4"/>
+    </row>
+    <row r="447" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C447" s="4"/>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
@@ -22337,8 +24230,12 @@
       <c r="AQ447" s="4"/>
       <c r="AR447" s="4"/>
       <c r="AS447" s="4"/>
-    </row>
-    <row r="448" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT447" s="4"/>
+      <c r="AU447" s="4"/>
+      <c r="AV447" s="4"/>
+      <c r="AW447" s="4"/>
+    </row>
+    <row r="448" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C448" s="4"/>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
@@ -22382,8 +24279,12 @@
       <c r="AQ448" s="4"/>
       <c r="AR448" s="4"/>
       <c r="AS448" s="4"/>
-    </row>
-    <row r="449" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT448" s="4"/>
+      <c r="AU448" s="4"/>
+      <c r="AV448" s="4"/>
+      <c r="AW448" s="4"/>
+    </row>
+    <row r="449" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C449" s="4"/>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
@@ -22427,8 +24328,12 @@
       <c r="AQ449" s="4"/>
       <c r="AR449" s="4"/>
       <c r="AS449" s="4"/>
-    </row>
-    <row r="450" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT449" s="4"/>
+      <c r="AU449" s="4"/>
+      <c r="AV449" s="4"/>
+      <c r="AW449" s="4"/>
+    </row>
+    <row r="450" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C450" s="4"/>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
@@ -22472,8 +24377,12 @@
       <c r="AQ450" s="4"/>
       <c r="AR450" s="4"/>
       <c r="AS450" s="4"/>
-    </row>
-    <row r="451" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT450" s="4"/>
+      <c r="AU450" s="4"/>
+      <c r="AV450" s="4"/>
+      <c r="AW450" s="4"/>
+    </row>
+    <row r="451" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C451" s="4"/>
       <c r="D451" s="4"/>
       <c r="E451" s="4"/>
@@ -22517,8 +24426,12 @@
       <c r="AQ451" s="4"/>
       <c r="AR451" s="4"/>
       <c r="AS451" s="4"/>
-    </row>
-    <row r="452" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT451" s="4"/>
+      <c r="AU451" s="4"/>
+      <c r="AV451" s="4"/>
+      <c r="AW451" s="4"/>
+    </row>
+    <row r="452" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C452" s="4"/>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
@@ -22562,8 +24475,12 @@
       <c r="AQ452" s="4"/>
       <c r="AR452" s="4"/>
       <c r="AS452" s="4"/>
-    </row>
-    <row r="453" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT452" s="4"/>
+      <c r="AU452" s="4"/>
+      <c r="AV452" s="4"/>
+      <c r="AW452" s="4"/>
+    </row>
+    <row r="453" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C453" s="4"/>
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
@@ -22607,8 +24524,12 @@
       <c r="AQ453" s="4"/>
       <c r="AR453" s="4"/>
       <c r="AS453" s="4"/>
-    </row>
-    <row r="454" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT453" s="4"/>
+      <c r="AU453" s="4"/>
+      <c r="AV453" s="4"/>
+      <c r="AW453" s="4"/>
+    </row>
+    <row r="454" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C454" s="4"/>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
@@ -22652,8 +24573,12 @@
       <c r="AQ454" s="4"/>
       <c r="AR454" s="4"/>
       <c r="AS454" s="4"/>
-    </row>
-    <row r="455" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT454" s="4"/>
+      <c r="AU454" s="4"/>
+      <c r="AV454" s="4"/>
+      <c r="AW454" s="4"/>
+    </row>
+    <row r="455" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C455" s="4"/>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
@@ -22697,8 +24622,12 @@
       <c r="AQ455" s="4"/>
       <c r="AR455" s="4"/>
       <c r="AS455" s="4"/>
-    </row>
-    <row r="456" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT455" s="4"/>
+      <c r="AU455" s="4"/>
+      <c r="AV455" s="4"/>
+      <c r="AW455" s="4"/>
+    </row>
+    <row r="456" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C456" s="4"/>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
@@ -22742,8 +24671,12 @@
       <c r="AQ456" s="4"/>
       <c r="AR456" s="4"/>
       <c r="AS456" s="4"/>
-    </row>
-    <row r="457" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT456" s="4"/>
+      <c r="AU456" s="4"/>
+      <c r="AV456" s="4"/>
+      <c r="AW456" s="4"/>
+    </row>
+    <row r="457" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C457" s="4"/>
       <c r="D457" s="4"/>
       <c r="E457" s="4"/>
@@ -22787,8 +24720,12 @@
       <c r="AQ457" s="4"/>
       <c r="AR457" s="4"/>
       <c r="AS457" s="4"/>
-    </row>
-    <row r="458" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT457" s="4"/>
+      <c r="AU457" s="4"/>
+      <c r="AV457" s="4"/>
+      <c r="AW457" s="4"/>
+    </row>
+    <row r="458" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C458" s="4"/>
       <c r="D458" s="4"/>
       <c r="E458" s="4"/>
@@ -22832,8 +24769,12 @@
       <c r="AQ458" s="4"/>
       <c r="AR458" s="4"/>
       <c r="AS458" s="4"/>
-    </row>
-    <row r="459" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT458" s="4"/>
+      <c r="AU458" s="4"/>
+      <c r="AV458" s="4"/>
+      <c r="AW458" s="4"/>
+    </row>
+    <row r="459" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C459" s="4"/>
       <c r="D459" s="4"/>
       <c r="E459" s="4"/>
@@ -22877,8 +24818,12 @@
       <c r="AQ459" s="4"/>
       <c r="AR459" s="4"/>
       <c r="AS459" s="4"/>
-    </row>
-    <row r="460" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT459" s="4"/>
+      <c r="AU459" s="4"/>
+      <c r="AV459" s="4"/>
+      <c r="AW459" s="4"/>
+    </row>
+    <row r="460" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C460" s="4"/>
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
@@ -22922,8 +24867,12 @@
       <c r="AQ460" s="4"/>
       <c r="AR460" s="4"/>
       <c r="AS460" s="4"/>
-    </row>
-    <row r="461" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT460" s="4"/>
+      <c r="AU460" s="4"/>
+      <c r="AV460" s="4"/>
+      <c r="AW460" s="4"/>
+    </row>
+    <row r="461" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C461" s="4"/>
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
@@ -22967,8 +24916,12 @@
       <c r="AQ461" s="4"/>
       <c r="AR461" s="4"/>
       <c r="AS461" s="4"/>
-    </row>
-    <row r="462" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT461" s="4"/>
+      <c r="AU461" s="4"/>
+      <c r="AV461" s="4"/>
+      <c r="AW461" s="4"/>
+    </row>
+    <row r="462" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C462" s="4"/>
       <c r="D462" s="4"/>
       <c r="E462" s="4"/>
@@ -23012,8 +24965,12 @@
       <c r="AQ462" s="4"/>
       <c r="AR462" s="4"/>
       <c r="AS462" s="4"/>
-    </row>
-    <row r="463" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT462" s="4"/>
+      <c r="AU462" s="4"/>
+      <c r="AV462" s="4"/>
+      <c r="AW462" s="4"/>
+    </row>
+    <row r="463" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C463" s="4"/>
       <c r="D463" s="4"/>
       <c r="E463" s="4"/>
@@ -23057,8 +25014,12 @@
       <c r="AQ463" s="4"/>
       <c r="AR463" s="4"/>
       <c r="AS463" s="4"/>
-    </row>
-    <row r="464" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT463" s="4"/>
+      <c r="AU463" s="4"/>
+      <c r="AV463" s="4"/>
+      <c r="AW463" s="4"/>
+    </row>
+    <row r="464" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C464" s="4"/>
       <c r="D464" s="4"/>
       <c r="E464" s="4"/>
@@ -23102,8 +25063,12 @@
       <c r="AQ464" s="4"/>
       <c r="AR464" s="4"/>
       <c r="AS464" s="4"/>
-    </row>
-    <row r="465" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT464" s="4"/>
+      <c r="AU464" s="4"/>
+      <c r="AV464" s="4"/>
+      <c r="AW464" s="4"/>
+    </row>
+    <row r="465" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C465" s="4"/>
       <c r="D465" s="4"/>
       <c r="E465" s="4"/>
@@ -23147,8 +25112,12 @@
       <c r="AQ465" s="4"/>
       <c r="AR465" s="4"/>
       <c r="AS465" s="4"/>
-    </row>
-    <row r="466" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT465" s="4"/>
+      <c r="AU465" s="4"/>
+      <c r="AV465" s="4"/>
+      <c r="AW465" s="4"/>
+    </row>
+    <row r="466" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C466" s="4"/>
       <c r="D466" s="4"/>
       <c r="E466" s="4"/>
@@ -23192,8 +25161,12 @@
       <c r="AQ466" s="4"/>
       <c r="AR466" s="4"/>
       <c r="AS466" s="4"/>
-    </row>
-    <row r="467" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT466" s="4"/>
+      <c r="AU466" s="4"/>
+      <c r="AV466" s="4"/>
+      <c r="AW466" s="4"/>
+    </row>
+    <row r="467" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C467" s="4"/>
       <c r="D467" s="4"/>
       <c r="E467" s="4"/>
@@ -23237,8 +25210,12 @@
       <c r="AQ467" s="4"/>
       <c r="AR467" s="4"/>
       <c r="AS467" s="4"/>
-    </row>
-    <row r="468" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT467" s="4"/>
+      <c r="AU467" s="4"/>
+      <c r="AV467" s="4"/>
+      <c r="AW467" s="4"/>
+    </row>
+    <row r="468" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C468" s="4"/>
       <c r="D468" s="4"/>
       <c r="E468" s="4"/>
@@ -23282,8 +25259,12 @@
       <c r="AQ468" s="4"/>
       <c r="AR468" s="4"/>
       <c r="AS468" s="4"/>
-    </row>
-    <row r="469" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT468" s="4"/>
+      <c r="AU468" s="4"/>
+      <c r="AV468" s="4"/>
+      <c r="AW468" s="4"/>
+    </row>
+    <row r="469" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C469" s="4"/>
       <c r="D469" s="4"/>
       <c r="E469" s="4"/>
@@ -23327,8 +25308,12 @@
       <c r="AQ469" s="4"/>
       <c r="AR469" s="4"/>
       <c r="AS469" s="4"/>
-    </row>
-    <row r="470" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT469" s="4"/>
+      <c r="AU469" s="4"/>
+      <c r="AV469" s="4"/>
+      <c r="AW469" s="4"/>
+    </row>
+    <row r="470" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C470" s="4"/>
       <c r="D470" s="4"/>
       <c r="E470" s="4"/>
@@ -23372,8 +25357,12 @@
       <c r="AQ470" s="4"/>
       <c r="AR470" s="4"/>
       <c r="AS470" s="4"/>
-    </row>
-    <row r="471" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT470" s="4"/>
+      <c r="AU470" s="4"/>
+      <c r="AV470" s="4"/>
+      <c r="AW470" s="4"/>
+    </row>
+    <row r="471" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C471" s="4"/>
       <c r="D471" s="4"/>
       <c r="E471" s="4"/>
@@ -23417,8 +25406,12 @@
       <c r="AQ471" s="4"/>
       <c r="AR471" s="4"/>
       <c r="AS471" s="4"/>
-    </row>
-    <row r="472" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT471" s="4"/>
+      <c r="AU471" s="4"/>
+      <c r="AV471" s="4"/>
+      <c r="AW471" s="4"/>
+    </row>
+    <row r="472" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C472" s="4"/>
       <c r="D472" s="4"/>
       <c r="E472" s="4"/>
@@ -23462,8 +25455,12 @@
       <c r="AQ472" s="4"/>
       <c r="AR472" s="4"/>
       <c r="AS472" s="4"/>
-    </row>
-    <row r="473" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT472" s="4"/>
+      <c r="AU472" s="4"/>
+      <c r="AV472" s="4"/>
+      <c r="AW472" s="4"/>
+    </row>
+    <row r="473" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C473" s="4"/>
       <c r="D473" s="4"/>
       <c r="E473" s="4"/>
@@ -23507,8 +25504,12 @@
       <c r="AQ473" s="4"/>
       <c r="AR473" s="4"/>
       <c r="AS473" s="4"/>
-    </row>
-    <row r="474" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT473" s="4"/>
+      <c r="AU473" s="4"/>
+      <c r="AV473" s="4"/>
+      <c r="AW473" s="4"/>
+    </row>
+    <row r="474" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C474" s="4"/>
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
@@ -23552,8 +25553,12 @@
       <c r="AQ474" s="4"/>
       <c r="AR474" s="4"/>
       <c r="AS474" s="4"/>
-    </row>
-    <row r="475" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT474" s="4"/>
+      <c r="AU474" s="4"/>
+      <c r="AV474" s="4"/>
+      <c r="AW474" s="4"/>
+    </row>
+    <row r="475" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C475" s="4"/>
       <c r="D475" s="4"/>
       <c r="E475" s="4"/>
@@ -23597,8 +25602,12 @@
       <c r="AQ475" s="4"/>
       <c r="AR475" s="4"/>
       <c r="AS475" s="4"/>
-    </row>
-    <row r="476" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT475" s="4"/>
+      <c r="AU475" s="4"/>
+      <c r="AV475" s="4"/>
+      <c r="AW475" s="4"/>
+    </row>
+    <row r="476" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C476" s="4"/>
       <c r="D476" s="4"/>
       <c r="E476" s="4"/>
@@ -23642,8 +25651,12 @@
       <c r="AQ476" s="4"/>
       <c r="AR476" s="4"/>
       <c r="AS476" s="4"/>
-    </row>
-    <row r="477" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT476" s="4"/>
+      <c r="AU476" s="4"/>
+      <c r="AV476" s="4"/>
+      <c r="AW476" s="4"/>
+    </row>
+    <row r="477" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C477" s="4"/>
       <c r="D477" s="4"/>
       <c r="E477" s="4"/>
@@ -23687,8 +25700,12 @@
       <c r="AQ477" s="4"/>
       <c r="AR477" s="4"/>
       <c r="AS477" s="4"/>
-    </row>
-    <row r="478" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT477" s="4"/>
+      <c r="AU477" s="4"/>
+      <c r="AV477" s="4"/>
+      <c r="AW477" s="4"/>
+    </row>
+    <row r="478" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C478" s="4"/>
       <c r="D478" s="4"/>
       <c r="E478" s="4"/>
@@ -23732,8 +25749,12 @@
       <c r="AQ478" s="4"/>
       <c r="AR478" s="4"/>
       <c r="AS478" s="4"/>
-    </row>
-    <row r="479" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT478" s="4"/>
+      <c r="AU478" s="4"/>
+      <c r="AV478" s="4"/>
+      <c r="AW478" s="4"/>
+    </row>
+    <row r="479" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C479" s="4"/>
       <c r="D479" s="4"/>
       <c r="E479" s="4"/>
@@ -23777,8 +25798,12 @@
       <c r="AQ479" s="4"/>
       <c r="AR479" s="4"/>
       <c r="AS479" s="4"/>
-    </row>
-    <row r="480" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT479" s="4"/>
+      <c r="AU479" s="4"/>
+      <c r="AV479" s="4"/>
+      <c r="AW479" s="4"/>
+    </row>
+    <row r="480" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C480" s="4"/>
       <c r="D480" s="4"/>
       <c r="E480" s="4"/>
@@ -23822,8 +25847,12 @@
       <c r="AQ480" s="4"/>
       <c r="AR480" s="4"/>
       <c r="AS480" s="4"/>
-    </row>
-    <row r="481" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT480" s="4"/>
+      <c r="AU480" s="4"/>
+      <c r="AV480" s="4"/>
+      <c r="AW480" s="4"/>
+    </row>
+    <row r="481" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C481" s="4"/>
       <c r="D481" s="4"/>
       <c r="E481" s="4"/>
@@ -23867,8 +25896,12 @@
       <c r="AQ481" s="4"/>
       <c r="AR481" s="4"/>
       <c r="AS481" s="4"/>
-    </row>
-    <row r="482" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT481" s="4"/>
+      <c r="AU481" s="4"/>
+      <c r="AV481" s="4"/>
+      <c r="AW481" s="4"/>
+    </row>
+    <row r="482" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C482" s="4"/>
       <c r="D482" s="4"/>
       <c r="E482" s="4"/>
@@ -23912,8 +25945,12 @@
       <c r="AQ482" s="4"/>
       <c r="AR482" s="4"/>
       <c r="AS482" s="4"/>
-    </row>
-    <row r="483" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT482" s="4"/>
+      <c r="AU482" s="4"/>
+      <c r="AV482" s="4"/>
+      <c r="AW482" s="4"/>
+    </row>
+    <row r="483" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C483" s="4"/>
       <c r="D483" s="4"/>
       <c r="E483" s="4"/>
@@ -23957,8 +25994,12 @@
       <c r="AQ483" s="4"/>
       <c r="AR483" s="4"/>
       <c r="AS483" s="4"/>
-    </row>
-    <row r="484" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT483" s="4"/>
+      <c r="AU483" s="4"/>
+      <c r="AV483" s="4"/>
+      <c r="AW483" s="4"/>
+    </row>
+    <row r="484" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C484" s="4"/>
       <c r="D484" s="4"/>
       <c r="E484" s="4"/>
@@ -24002,8 +26043,12 @@
       <c r="AQ484" s="4"/>
       <c r="AR484" s="4"/>
       <c r="AS484" s="4"/>
-    </row>
-    <row r="485" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT484" s="4"/>
+      <c r="AU484" s="4"/>
+      <c r="AV484" s="4"/>
+      <c r="AW484" s="4"/>
+    </row>
+    <row r="485" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C485" s="4"/>
       <c r="D485" s="4"/>
       <c r="E485" s="4"/>
@@ -24047,8 +26092,12 @@
       <c r="AQ485" s="4"/>
       <c r="AR485" s="4"/>
       <c r="AS485" s="4"/>
-    </row>
-    <row r="486" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT485" s="4"/>
+      <c r="AU485" s="4"/>
+      <c r="AV485" s="4"/>
+      <c r="AW485" s="4"/>
+    </row>
+    <row r="486" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C486" s="4"/>
       <c r="D486" s="4"/>
       <c r="E486" s="4"/>
@@ -24092,8 +26141,12 @@
       <c r="AQ486" s="4"/>
       <c r="AR486" s="4"/>
       <c r="AS486" s="4"/>
-    </row>
-    <row r="487" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT486" s="4"/>
+      <c r="AU486" s="4"/>
+      <c r="AV486" s="4"/>
+      <c r="AW486" s="4"/>
+    </row>
+    <row r="487" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C487" s="4"/>
       <c r="D487" s="4"/>
       <c r="E487" s="4"/>
@@ -24137,8 +26190,12 @@
       <c r="AQ487" s="4"/>
       <c r="AR487" s="4"/>
       <c r="AS487" s="4"/>
-    </row>
-    <row r="488" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT487" s="4"/>
+      <c r="AU487" s="4"/>
+      <c r="AV487" s="4"/>
+      <c r="AW487" s="4"/>
+    </row>
+    <row r="488" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C488" s="4"/>
       <c r="D488" s="4"/>
       <c r="E488" s="4"/>
@@ -24182,8 +26239,12 @@
       <c r="AQ488" s="4"/>
       <c r="AR488" s="4"/>
       <c r="AS488" s="4"/>
-    </row>
-    <row r="489" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT488" s="4"/>
+      <c r="AU488" s="4"/>
+      <c r="AV488" s="4"/>
+      <c r="AW488" s="4"/>
+    </row>
+    <row r="489" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C489" s="4"/>
       <c r="D489" s="4"/>
       <c r="E489" s="4"/>
@@ -24227,8 +26288,12 @@
       <c r="AQ489" s="4"/>
       <c r="AR489" s="4"/>
       <c r="AS489" s="4"/>
-    </row>
-    <row r="490" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT489" s="4"/>
+      <c r="AU489" s="4"/>
+      <c r="AV489" s="4"/>
+      <c r="AW489" s="4"/>
+    </row>
+    <row r="490" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C490" s="4"/>
       <c r="D490" s="4"/>
       <c r="E490" s="4"/>
@@ -24272,8 +26337,12 @@
       <c r="AQ490" s="4"/>
       <c r="AR490" s="4"/>
       <c r="AS490" s="4"/>
-    </row>
-    <row r="491" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT490" s="4"/>
+      <c r="AU490" s="4"/>
+      <c r="AV490" s="4"/>
+      <c r="AW490" s="4"/>
+    </row>
+    <row r="491" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C491" s="4"/>
       <c r="D491" s="4"/>
       <c r="E491" s="4"/>
@@ -24317,8 +26386,12 @@
       <c r="AQ491" s="4"/>
       <c r="AR491" s="4"/>
       <c r="AS491" s="4"/>
-    </row>
-    <row r="492" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT491" s="4"/>
+      <c r="AU491" s="4"/>
+      <c r="AV491" s="4"/>
+      <c r="AW491" s="4"/>
+    </row>
+    <row r="492" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C492" s="4"/>
       <c r="D492" s="4"/>
       <c r="E492" s="4"/>
@@ -24362,8 +26435,12 @@
       <c r="AQ492" s="4"/>
       <c r="AR492" s="4"/>
       <c r="AS492" s="4"/>
-    </row>
-    <row r="493" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT492" s="4"/>
+      <c r="AU492" s="4"/>
+      <c r="AV492" s="4"/>
+      <c r="AW492" s="4"/>
+    </row>
+    <row r="493" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C493" s="4"/>
       <c r="D493" s="4"/>
       <c r="E493" s="4"/>
@@ -24407,8 +26484,12 @@
       <c r="AQ493" s="4"/>
       <c r="AR493" s="4"/>
       <c r="AS493" s="4"/>
-    </row>
-    <row r="494" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT493" s="4"/>
+      <c r="AU493" s="4"/>
+      <c r="AV493" s="4"/>
+      <c r="AW493" s="4"/>
+    </row>
+    <row r="494" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C494" s="4"/>
       <c r="D494" s="4"/>
       <c r="E494" s="4"/>
@@ -24452,8 +26533,12 @@
       <c r="AQ494" s="4"/>
       <c r="AR494" s="4"/>
       <c r="AS494" s="4"/>
-    </row>
-    <row r="495" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT494" s="4"/>
+      <c r="AU494" s="4"/>
+      <c r="AV494" s="4"/>
+      <c r="AW494" s="4"/>
+    </row>
+    <row r="495" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C495" s="4"/>
       <c r="D495" s="4"/>
       <c r="E495" s="4"/>
@@ -24497,8 +26582,12 @@
       <c r="AQ495" s="4"/>
       <c r="AR495" s="4"/>
       <c r="AS495" s="4"/>
-    </row>
-    <row r="496" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT495" s="4"/>
+      <c r="AU495" s="4"/>
+      <c r="AV495" s="4"/>
+      <c r="AW495" s="4"/>
+    </row>
+    <row r="496" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C496" s="4"/>
       <c r="D496" s="4"/>
       <c r="E496" s="4"/>
@@ -24542,8 +26631,12 @@
       <c r="AQ496" s="4"/>
       <c r="AR496" s="4"/>
       <c r="AS496" s="4"/>
-    </row>
-    <row r="497" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT496" s="4"/>
+      <c r="AU496" s="4"/>
+      <c r="AV496" s="4"/>
+      <c r="AW496" s="4"/>
+    </row>
+    <row r="497" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C497" s="4"/>
       <c r="D497" s="4"/>
       <c r="E497" s="4"/>
@@ -24587,8 +26680,12 @@
       <c r="AQ497" s="4"/>
       <c r="AR497" s="4"/>
       <c r="AS497" s="4"/>
-    </row>
-    <row r="498" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT497" s="4"/>
+      <c r="AU497" s="4"/>
+      <c r="AV497" s="4"/>
+      <c r="AW497" s="4"/>
+    </row>
+    <row r="498" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C498" s="4"/>
       <c r="D498" s="4"/>
       <c r="E498" s="4"/>
@@ -24632,8 +26729,12 @@
       <c r="AQ498" s="4"/>
       <c r="AR498" s="4"/>
       <c r="AS498" s="4"/>
-    </row>
-    <row r="499" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT498" s="4"/>
+      <c r="AU498" s="4"/>
+      <c r="AV498" s="4"/>
+      <c r="AW498" s="4"/>
+    </row>
+    <row r="499" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C499" s="4"/>
       <c r="D499" s="4"/>
       <c r="E499" s="4"/>
@@ -24677,8 +26778,12 @@
       <c r="AQ499" s="4"/>
       <c r="AR499" s="4"/>
       <c r="AS499" s="4"/>
-    </row>
-    <row r="500" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT499" s="4"/>
+      <c r="AU499" s="4"/>
+      <c r="AV499" s="4"/>
+      <c r="AW499" s="4"/>
+    </row>
+    <row r="500" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C500" s="4"/>
       <c r="D500" s="4"/>
       <c r="E500" s="4"/>
@@ -24722,8 +26827,12 @@
       <c r="AQ500" s="4"/>
       <c r="AR500" s="4"/>
       <c r="AS500" s="4"/>
-    </row>
-    <row r="501" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT500" s="4"/>
+      <c r="AU500" s="4"/>
+      <c r="AV500" s="4"/>
+      <c r="AW500" s="4"/>
+    </row>
+    <row r="501" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C501" s="4"/>
       <c r="D501" s="4"/>
       <c r="E501" s="4"/>
@@ -24767,8 +26876,12 @@
       <c r="AQ501" s="4"/>
       <c r="AR501" s="4"/>
       <c r="AS501" s="4"/>
-    </row>
-    <row r="502" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT501" s="4"/>
+      <c r="AU501" s="4"/>
+      <c r="AV501" s="4"/>
+      <c r="AW501" s="4"/>
+    </row>
+    <row r="502" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C502" s="4"/>
       <c r="D502" s="4"/>
       <c r="E502" s="4"/>
@@ -24812,8 +26925,12 @@
       <c r="AQ502" s="4"/>
       <c r="AR502" s="4"/>
       <c r="AS502" s="4"/>
-    </row>
-    <row r="503" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT502" s="4"/>
+      <c r="AU502" s="4"/>
+      <c r="AV502" s="4"/>
+      <c r="AW502" s="4"/>
+    </row>
+    <row r="503" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C503" s="4"/>
       <c r="D503" s="4"/>
       <c r="E503" s="4"/>
@@ -24857,8 +26974,12 @@
       <c r="AQ503" s="4"/>
       <c r="AR503" s="4"/>
       <c r="AS503" s="4"/>
-    </row>
-    <row r="504" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT503" s="4"/>
+      <c r="AU503" s="4"/>
+      <c r="AV503" s="4"/>
+      <c r="AW503" s="4"/>
+    </row>
+    <row r="504" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C504" s="4"/>
       <c r="D504" s="4"/>
       <c r="E504" s="4"/>
@@ -24902,8 +27023,12 @@
       <c r="AQ504" s="4"/>
       <c r="AR504" s="4"/>
       <c r="AS504" s="4"/>
-    </row>
-    <row r="505" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT504" s="4"/>
+      <c r="AU504" s="4"/>
+      <c r="AV504" s="4"/>
+      <c r="AW504" s="4"/>
+    </row>
+    <row r="505" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C505" s="4"/>
       <c r="D505" s="4"/>
       <c r="E505" s="4"/>
@@ -24947,8 +27072,12 @@
       <c r="AQ505" s="4"/>
       <c r="AR505" s="4"/>
       <c r="AS505" s="4"/>
-    </row>
-    <row r="506" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT505" s="4"/>
+      <c r="AU505" s="4"/>
+      <c r="AV505" s="4"/>
+      <c r="AW505" s="4"/>
+    </row>
+    <row r="506" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C506" s="4"/>
       <c r="D506" s="4"/>
       <c r="E506" s="4"/>
@@ -24992,8 +27121,12 @@
       <c r="AQ506" s="4"/>
       <c r="AR506" s="4"/>
       <c r="AS506" s="4"/>
-    </row>
-    <row r="507" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT506" s="4"/>
+      <c r="AU506" s="4"/>
+      <c r="AV506" s="4"/>
+      <c r="AW506" s="4"/>
+    </row>
+    <row r="507" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C507" s="4"/>
       <c r="D507" s="4"/>
       <c r="E507" s="4"/>
@@ -25037,8 +27170,12 @@
       <c r="AQ507" s="4"/>
       <c r="AR507" s="4"/>
       <c r="AS507" s="4"/>
-    </row>
-    <row r="508" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT507" s="4"/>
+      <c r="AU507" s="4"/>
+      <c r="AV507" s="4"/>
+      <c r="AW507" s="4"/>
+    </row>
+    <row r="508" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C508" s="4"/>
       <c r="D508" s="4"/>
       <c r="E508" s="4"/>
@@ -25082,8 +27219,12 @@
       <c r="AQ508" s="4"/>
       <c r="AR508" s="4"/>
       <c r="AS508" s="4"/>
-    </row>
-    <row r="509" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT508" s="4"/>
+      <c r="AU508" s="4"/>
+      <c r="AV508" s="4"/>
+      <c r="AW508" s="4"/>
+    </row>
+    <row r="509" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C509" s="4"/>
       <c r="D509" s="4"/>
       <c r="E509" s="4"/>
@@ -25127,8 +27268,12 @@
       <c r="AQ509" s="4"/>
       <c r="AR509" s="4"/>
       <c r="AS509" s="4"/>
-    </row>
-    <row r="510" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT509" s="4"/>
+      <c r="AU509" s="4"/>
+      <c r="AV509" s="4"/>
+      <c r="AW509" s="4"/>
+    </row>
+    <row r="510" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C510" s="4"/>
       <c r="D510" s="4"/>
       <c r="E510" s="4"/>
@@ -25172,8 +27317,12 @@
       <c r="AQ510" s="4"/>
       <c r="AR510" s="4"/>
       <c r="AS510" s="4"/>
-    </row>
-    <row r="511" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT510" s="4"/>
+      <c r="AU510" s="4"/>
+      <c r="AV510" s="4"/>
+      <c r="AW510" s="4"/>
+    </row>
+    <row r="511" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C511" s="4"/>
       <c r="D511" s="4"/>
       <c r="E511" s="4"/>
@@ -25217,8 +27366,12 @@
       <c r="AQ511" s="4"/>
       <c r="AR511" s="4"/>
       <c r="AS511" s="4"/>
-    </row>
-    <row r="512" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT511" s="4"/>
+      <c r="AU511" s="4"/>
+      <c r="AV511" s="4"/>
+      <c r="AW511" s="4"/>
+    </row>
+    <row r="512" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C512" s="4"/>
       <c r="D512" s="4"/>
       <c r="E512" s="4"/>
@@ -25262,8 +27415,12 @@
       <c r="AQ512" s="4"/>
       <c r="AR512" s="4"/>
       <c r="AS512" s="4"/>
-    </row>
-    <row r="513" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT512" s="4"/>
+      <c r="AU512" s="4"/>
+      <c r="AV512" s="4"/>
+      <c r="AW512" s="4"/>
+    </row>
+    <row r="513" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C513" s="4"/>
       <c r="D513" s="4"/>
       <c r="E513" s="4"/>
@@ -25307,8 +27464,12 @@
       <c r="AQ513" s="4"/>
       <c r="AR513" s="4"/>
       <c r="AS513" s="4"/>
-    </row>
-    <row r="514" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT513" s="4"/>
+      <c r="AU513" s="4"/>
+      <c r="AV513" s="4"/>
+      <c r="AW513" s="4"/>
+    </row>
+    <row r="514" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C514" s="4"/>
       <c r="D514" s="4"/>
       <c r="E514" s="4"/>
@@ -25352,8 +27513,12 @@
       <c r="AQ514" s="4"/>
       <c r="AR514" s="4"/>
       <c r="AS514" s="4"/>
-    </row>
-    <row r="515" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT514" s="4"/>
+      <c r="AU514" s="4"/>
+      <c r="AV514" s="4"/>
+      <c r="AW514" s="4"/>
+    </row>
+    <row r="515" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C515" s="4"/>
       <c r="D515" s="4"/>
       <c r="E515" s="4"/>
@@ -25397,8 +27562,12 @@
       <c r="AQ515" s="4"/>
       <c r="AR515" s="4"/>
       <c r="AS515" s="4"/>
-    </row>
-    <row r="516" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT515" s="4"/>
+      <c r="AU515" s="4"/>
+      <c r="AV515" s="4"/>
+      <c r="AW515" s="4"/>
+    </row>
+    <row r="516" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C516" s="4"/>
       <c r="D516" s="4"/>
       <c r="E516" s="4"/>
@@ -25442,8 +27611,12 @@
       <c r="AQ516" s="4"/>
       <c r="AR516" s="4"/>
       <c r="AS516" s="4"/>
-    </row>
-    <row r="517" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT516" s="4"/>
+      <c r="AU516" s="4"/>
+      <c r="AV516" s="4"/>
+      <c r="AW516" s="4"/>
+    </row>
+    <row r="517" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C517" s="4"/>
       <c r="D517" s="4"/>
       <c r="E517" s="4"/>
@@ -25487,8 +27660,12 @@
       <c r="AQ517" s="4"/>
       <c r="AR517" s="4"/>
       <c r="AS517" s="4"/>
-    </row>
-    <row r="518" spans="3:45" x14ac:dyDescent="0.2">
+      <c r="AT517" s="4"/>
+      <c r="AU517" s="4"/>
+      <c r="AV517" s="4"/>
+      <c r="AW517" s="4"/>
+    </row>
+    <row r="518" spans="3:49" x14ac:dyDescent="0.2">
       <c r="C518" s="4"/>
       <c r="D518" s="4"/>
       <c r="E518" s="4"/>
@@ -25532,6 +27709,10 @@
       <c r="AQ518" s="4"/>
       <c r="AR518" s="4"/>
       <c r="AS518" s="4"/>
+      <c r="AT518" s="4"/>
+      <c r="AU518" s="4"/>
+      <c r="AV518" s="4"/>
+      <c r="AW518" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
